--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -168,6 +168,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -781,20 +790,20 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="13" t="n">
         <v>28.4</v>
       </c>
-      <c r="E4" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F4" s="12" t="n">
+      <c r="E4" s="13" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F4" s="13" t="n">
         <v>22.1</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="13" t="n">
         <v>12.5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>12.5</v>
+        <v>23.5</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>3.8</v>
@@ -803,37 +812,43 @@
         <v>5.5</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>26.6</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n"/>
+      <c r="Q4" s="3" t="n">
+        <v>43.1</v>
+      </c>
       <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="T4" s="3" t="n"/>
+      <c r="T4" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>20.3</v>
+        <v>80.3</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="X4" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>26.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>3.3</v>
@@ -852,55 +867,58 @@
         </is>
       </c>
       <c r="C5" s="3" t="n"/>
-      <c r="D5" s="12" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>438</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J5" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 5
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>18.3</v>
-      </c>
+          <t xml:space="preserve">99
+211
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n">
-        <v>18.6</v>
+        <v>1.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P5" s="8" t="n">
-        <v>41.6</v>
+        <v>90</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>0.3</v>
+        <v>21.3</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>74.3</v>
+        <v>94.3</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>8</v>
@@ -936,15 +954,15 @@
       <c r="C6" s="3" t="n">
         <v>484.4</v>
       </c>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="9" t="n">
-        <v>87</v>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>11.9</v>
+      <c r="G6" s="15" t="n">
+        <v>18.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>15.2</v>
@@ -953,25 +971,28 @@
         <v>3.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <v>72.5</v>
+        <v>5.2</v>
+      </c>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16495171
+178
+2 2 4221
+</t>
+        </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>17.9</v>
+        <v>16.8</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>18.1</v>
+        <v>1.4</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P6" s="8" t="n">
-        <v>41.6</v>
+        <v>25.1</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1.6</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>26.8</v>
@@ -980,25 +1001,25 @@
         <v>22.3</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>20.2</v>
+        <v>20.8</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>21.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Z6" s="3" t="n">
         <v>2.1</v>
@@ -1017,22 +1038,20 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>274.4</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>3.3</v>
-      </c>
+        <v>34.4</v>
+      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n">
-        <v>16.2</v>
+        <v>16.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>22.8</v>
+        <v>18.8</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>12.8</v>
+        <v>18.8</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>3</v>
@@ -1041,28 +1060,28 @@
         <v>4.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.2</v>
+        <v>2.2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M7" s="3" t="n">
-        <v>17.9</v>
+      <c r="M7" s="15" t="n">
+        <v>72.90000000000001</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>882.1</v>
+        <v>94</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>21.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>22.7</v>
+      <c r="R7" s="15" t="n">
+        <v>28.7</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>24.9</v>
@@ -1080,13 +1099,13 @@
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>22.1</v>
+        <v>18.1</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>90</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>12.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1102,18 +1121,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>260.2</v>
+        <v>1602.4</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>17</v>
+        <v>2.4</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G8" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1123,28 +1142,24 @@
         <v>2.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>16.6</v>
-      </c>
+        <v>13.3</v>
+      </c>
+      <c r="K8" s="3" t="n"/>
       <c r="L8" s="3" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>458</v>
-      </c>
-      <c r="N8" s="8" t="n">
-        <v>1862.8</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="n">
-        <v>882.1</v>
+        <v>89.8</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="Q8" s="8" t="n">
-        <v>46.5</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>445.1</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>22.8</v>
@@ -1153,10 +1168,10 @@
         <v>26.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>19.6</v>
@@ -1167,8 +1182,12 @@
       <c r="X8" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
+      <c r="Y8" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1183,22 +1202,16 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2240.4</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>77.8</v>
-      </c>
+        <v>1602.4</v>
+      </c>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
       <c r="G9" s="3" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.7</v>
+        <v>62.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.8</v>
@@ -1207,51 +1220,49 @@
         <v>28.8</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>37.1</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>814.5</v>
+        <v>15.8</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>98.2</v>
+        <v>7.5</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>23.1</v>
+        <v>88.2</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>3.7</v>
+        <v>127.1</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n">
-        <v>184.2</v>
+        <v>389.2</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>38.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>2.5</v>
-      </c>
+        <v>12.7</v>
+      </c>
+      <c r="Z9" s="3" t="n"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1266,75 +1277,85 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2240.4</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>13.5</v>
-      </c>
+        <v>146.4</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4465227
+8179171
+</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2282891
+181
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82828
+199812
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>3.4</v>
+      </c>
+      <c r="J10" s="3" t="n"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792871272
+1
+</t>
+        </is>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>17</v>
+        <v>84.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>98</v>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">94
+2
+</t>
+        </is>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>25.1</v>
+        <v>2.5</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>39</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v>98.09999999999999</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7424
+1111
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" s="3" t="n"/>
+      <c r="V10" s="3" t="n"/>
       <c r="W10" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X10" s="8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>7.7</v>
+      </c>
+      <c r="X10" s="15" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="Y10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1349,76 +1370,68 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>128.9</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>29.5</v>
-      </c>
+        <v>498.5</v>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
       <c r="G11" s="3" t="n">
-        <v>11.8</v>
+        <v>11.2</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>16.9</v>
+        <v>4.6</v>
+      </c>
+      <c r="K11" s="3" t="n"/>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77718
+6222
+</t>
+        </is>
+      </c>
+      <c r="M11" s="15" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>190.6</v>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>22.2</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231
+24721195
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n"/>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n">
-        <v>76.8</v>
+        <v>6.8</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="V11" s="8" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>6.6</v>
+      <c r="V11" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="W11" s="15" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>26.6</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>89</v>
+        <v>896</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1434,7 +1447,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>299.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>26.5</v>
@@ -1446,43 +1459,39 @@
         <v>31.3</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>97.7</v>
+      </c>
+      <c r="H12" s="3" t="n"/>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="n">
-        <v>31.9</v>
+        <v>5.9</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>10.4</v>
+        <v>6.4</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>17</v>
+        <v>17.8</v>
+      </c>
+      <c r="M12" s="15" t="n">
+        <v>91.09999999999999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>98</v>
+        <v>166.1</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="S12" s="8" t="n">
-        <v>39</v>
+        <v>6.4</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="R12" s="15" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>29</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>68.40000000000001</v>
@@ -1491,19 +1500,19 @@
         <v>10.6</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W12" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="X12" s="8" t="n">
-        <v>22</v>
+      <c r="X12" s="15" t="n">
+        <v>28</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>84.5</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1521,39 +1530,43 @@
       <c r="C13" s="3" t="n">
         <v>343.6</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="13" t="n">
         <v>26.8</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="13" t="n">
         <v>17.7</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="13" t="n">
         <v>22.4</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="13" t="n">
         <v>9.1</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>15</v>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+1109
+</t>
+        </is>
       </c>
       <c r="I13" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="J13" s="8" t="n">
-        <v>39.4</v>
+      <c r="J13" s="3" t="n">
+        <v>3.4</v>
       </c>
       <c r="K13" s="3" t="n"/>
       <c r="L13" s="3" t="n">
-        <v>17.2</v>
+        <v>18.4</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>17.6</v>
+        <v>17</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>1.6</v>
@@ -1565,22 +1578,22 @@
         <v>19.5</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>22.2</v>
+        <v>2.5</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>93</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>14.6</v>
+        <v>1.6</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
+      </c>
+      <c r="X13" s="15" t="n">
+        <v>21.9</v>
       </c>
       <c r="Y13" s="3" t="n">
         <v>89.09999999999999</v>
@@ -1602,58 +1615,50 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>223.8</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>72.84999999999999</v>
+        <v>323.8</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>27.5</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F14" s="9" t="n">
-        <v>92.25</v>
-      </c>
+      <c r="F14" s="10" t="n"/>
       <c r="G14" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>14.8</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="3" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>18.4</v>
+        <v>2.6</v>
+      </c>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="15" t="n">
+        <v>77.09999999999999</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>18.9</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>22.1</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="R14" s="8" t="n">
-        <v>11.4</v>
+      <c r="R14" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>427.1</v>
+        <v>23.7</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="U14" s="3" t="n">
         <v>6.8</v>
@@ -1665,11 +1670,9 @@
         <v>19.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Y14" s="3" t="n">
-        <v>95.8</v>
-      </c>
+        <v>2.2</v>
+      </c>
+      <c r="Y14" s="3" t="n"/>
       <c r="Z14" s="3" t="n">
         <v>0.9</v>
       </c>
@@ -1687,7 +1690,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>260</v>
+        <v>266.6</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>24.8</v>
@@ -1695,49 +1698,41 @@
       <c r="E15" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="F15" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="15" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K15" s="3" t="n"/>
+        <v>22.2</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="L15" s="3" t="n">
         <v>18.3</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>89.59999999999999</v>
-      </c>
+        <v>6.1</v>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>21</v>
+        <v>2.6</v>
+      </c>
+      <c r="Q15" s="15" t="n">
+        <v>41</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>20.5</v>
+        <v>6.5</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="V15" s="3" t="n">
         <v>19.7</v>
@@ -1746,10 +1741,10 @@
         <v>19.4</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>0.7</v>
@@ -1768,7 +1763,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8934.799999999999</v>
+        <v>34.8</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>28.3</v>
@@ -1776,11 +1771,11 @@
       <c r="E16" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="13" t="n">
         <v>22.5</v>
       </c>
-      <c r="G16" s="12" t="n">
-        <v>11.7</v>
+      <c r="G16" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>14.4</v>
@@ -1791,38 +1786,38 @@
       <c r="J16" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K16" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n">
-        <v>17.2</v>
+        <v>12.2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>16.6</v>
+        <v>82.8</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>94</v>
+        <v>2.6</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>22.1</v>
+        <v>158.4</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>229.1</v>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>1.1</v>
+        <v>41.4</v>
+      </c>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21214
+7922
+</t>
+        </is>
       </c>
       <c r="U16" s="3" t="n">
-        <v>15</v>
+        <v>15.7</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>19.2</v>
@@ -1831,13 +1826,13 @@
         <v>18.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>80.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>91</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1852,74 +1847,70 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>15646.8</v>
-      </c>
+      <c r="C17" s="3" t="n"/>
       <c r="D17" s="11" t="n">
-        <v>137.2</v>
+        <v>3.3</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>9.9</v>
-      </c>
+        <v>66.59999999999999</v>
+      </c>
+      <c r="F17" s="9" t="n"/>
       <c r="G17" s="3" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="I17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="K17" s="3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="L17" s="3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="M17" s="3" t="n">
-        <v>85.3</v>
+        <v>16.6</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>86559.39999999999</v>
-      </c>
+        <v>9.5</v>
+      </c>
+      <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="n">
         <v>61.4</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q17" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="R17" s="3" t="n">
-        <v>21.8</v>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">744
+981
+</t>
+        </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="V17" s="8" t="n">
+        <v>755.6</v>
+      </c>
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V17" s="15" t="n">
         <v>1.9</v>
       </c>
-      <c r="W17" s="3" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>9.699999999999999</v>
+      <c r="W17" s="15" t="n">
+        <v>612.1</v>
+      </c>
+      <c r="X17" s="15" t="n">
+        <v>20.3</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>10.4</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="3" t="n"/>
       <c r="AA17" s="3" t="inlineStr">
@@ -1938,74 +1929,67 @@
       <c r="C18" s="3" t="n">
         <v>312.4</v>
       </c>
-      <c r="D18" s="9" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="F18" s="9" t="n">
+      <c r="D18" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>91.7</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G18" s="3" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>44.6</v>
+        <v>0.1</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K18" s="3" t="n">
-        <v>2.3</v>
-      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 99
-</t>
-        </is>
+      <c r="M18" s="15" t="n">
+        <v>534.1</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0.9</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>93.2</v>
+        <v>23.8</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>1.4</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S18" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>188.1</v>
+        <v>185.1</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>7</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X18" s="8" t="n">
-        <v>57.4</v>
+        <v>2</v>
+      </c>
+      <c r="W18" s="15" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>21.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>2.1</v>
@@ -2023,44 +2007,42 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>1253.4</v>
-      </c>
-      <c r="D19" s="9" t="n">
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="12" t="n">
         <v>3.3</v>
       </c>
       <c r="E19" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="F19" s="9" t="n">
-        <v>0.1</v>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77718
+273
+</t>
+        </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>16.4</v>
-      </c>
+        <v>7.7</v>
+      </c>
+      <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n">
-        <v>3</v>
+        <v>30.3</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>14.1</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>2.7</v>
@@ -2072,29 +2054,27 @@
         <v>21.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>29.3</v>
+        <v>23.5</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>66.5</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>20.9</v>
+        <v>1.7</v>
+      </c>
+      <c r="V19" s="15" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>18.9</v>
+        <v>19.4</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>21.9</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="Z19" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2108,24 +2088,22 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>6.7</v>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>11.2</v>
       </c>
       <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n">
-        <v>12.2</v>
+      <c r="I20" s="15" t="n">
+        <v>45482.4</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>3.3</v>
@@ -2137,43 +2115,41 @@
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S20" s="3" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="R20" s="15" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>23.4</v>
+        <v>3.1</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="V20" s="15" t="n">
+        <v>34.1</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>19.9</v>
+        <v>18.9</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>20.7</v>
+        <v>2.8</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>14.1</v>
+        <v>83.5</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>7.6</v>
@@ -2192,46 +2168,47 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1253.4</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E21" s="12" t="n">
+        <v>253.4</v>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>16.8</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>12.8</v>
+      </c>
       <c r="F21" s="12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>11.9</v>
-      </c>
+        <v>88.3</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">828127
+160
+745414119
+</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n"/>
       <c r="J21" s="3" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="K21" s="3" t="n"/>
       <c r="L21" s="3" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>17.9</v>
+        <v>1.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>2.3</v>
+        <v>28.3</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0.7</v>
+        <v>6.7</v>
       </c>
       <c r="Q21" s="3" t="n">
         <v>22.8</v>
@@ -2239,26 +2216,30 @@
       <c r="R21" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S21" s="8" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>14</v>
+      <c r="S21" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+1 1
+</t>
+        </is>
       </c>
       <c r="U21" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="15" t="n">
         <v>20.9</v>
       </c>
-      <c r="W21" s="3" t="n">
-        <v>20.2</v>
+      <c r="W21" s="15" t="n">
+        <v>99.09999999999999</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>21.2</v>
+        <v>12.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>1.5</v>
@@ -2277,46 +2258,50 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>5334.9</v>
+        <v>266.1</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="E22" s="9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F22" s="9" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>12.6</v>
+      <c r="E22" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+      <c r="I22" s="15" t="n">
+        <v>428.2</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0</v>
+        <v>3.2</v>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+77
+</t>
+        </is>
       </c>
       <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="P22" s="3" t="n">
-        <v>12.2</v>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+2
+</t>
+        </is>
       </c>
       <c r="Q22" s="3" t="n">
         <v>20.9</v>
@@ -2324,23 +2309,27 @@
       <c r="R22" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="S22" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="T22" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>11.2</v>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W22" s="8" t="n">
-        <v>89</v>
-      </c>
-      <c r="X22" s="8" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">449
+190
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+1856
+</t>
+        </is>
       </c>
       <c r="Y22" s="3" t="n">
         <v>96.8</v>
@@ -2362,58 +2351,54 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1548.6</v>
+        <v>39.2</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>27.6</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="11" t="n">
         <v>17</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9.199999999999999</v>
+        <v>310.6</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>74.90000000000001</v>
-      </c>
+        <v>6.6</v>
+      </c>
+      <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n">
-        <v>12.6</v>
+        <v>0.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>616.3</v>
-      </c>
+        <v>4.7</v>
+      </c>
+      <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>117.1</v>
+        <v>17.4</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.5</v>
+        <v>21</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>10.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>25.1</v>
+        <v>251.2</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.5</v>
+        <v>21.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>0.5</v>
+        <v>23.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>393.1</v>
+        <v>40</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>8.300000000000001</v>
@@ -2421,8 +2406,12 @@
       <c r="V23" s="3" t="n">
         <v>23.1</v>
       </c>
-      <c r="W23" s="3" t="n">
-        <v>99.8</v>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">449
+190
+</t>
+        </is>
       </c>
       <c r="X23" s="3" t="n">
         <v>19.6</v>
@@ -2447,77 +2436,69 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>737.6</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>85</v>
+        <v>58.6</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>851</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>115.9</v>
+        <v>22.3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>57.6</v>
+        <v>57.2</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>14.8</v>
+        <v>6.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>19.3</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="J24" s="3" t="n"/>
       <c r="K24" s="3" t="n">
-        <v>1.4</v>
+        <v>6.6</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>87.90000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>869.2</v>
+        <v>49.1</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>6.3</v>
+        <v>63.3</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>14.3</v>
+        <v>1</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="S24" s="8" t="n">
-        <v>38.1</v>
+        <v>10.7</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>75.2</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>78.7</v>
+        <v>93.7</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>19.9</v>
-      </c>
+        <v>37.1</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="W24" s="3" t="n"/>
       <c r="X24" s="3" t="n">
-        <v>170.5</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>6.3</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="Y24" s="3" t="n"/>
+      <c r="Z24" s="3" t="n"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2532,76 +2513,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>279.8</v>
+        <v>39.7</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>27.5</v>
       </c>
-      <c r="E25" s="9" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>29.8</v>
+      <c r="E25" s="12" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>14.48</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10.5</v>
+        <v>1.5</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>24.1</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>74.09999999999999</v>
+        <v>18.1</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>87.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>938</v>
+        <v>38.1</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="Q25" s="15" t="n">
         <v>39.1</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>82.5</v>
+        <v>6.4</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>20.1</v>
+        <v>2.8</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>18</v>
+        <v>0.2</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>75</v>
-      </c>
+        <v>21.1</v>
+      </c>
+      <c r="Y25" s="3" t="n"/>
       <c r="Z25" s="3" t="n">
-        <v>16.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2617,73 +2596,63 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>341.4</v>
-      </c>
-      <c r="D26" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>17.4</v>
-      </c>
+        <v>279.8</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="E26" s="10" t="n"/>
       <c r="F26" s="3" t="n">
-        <v>21.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>12</v>
-      </c>
+        <v>2.3</v>
+      </c>
+      <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="J26" s="3" t="n"/>
+      <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>18.2</v>
+        <v>17.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>94</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>12.1</v>
+        <v>1.2</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="S26" s="8" t="n">
-        <v>14.6</v>
+        <v>20</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="U26" s="3" t="n">
-        <v>9.9</v>
-      </c>
+        <v>86.5</v>
+      </c>
+      <c r="U26" s="3" t="n"/>
       <c r="V26" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>19.7</v>
+        <v>21.1</v>
+      </c>
+      <c r="W26" s="15" t="n">
+        <v>802</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>18.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>6.3</v>
@@ -2702,73 +2671,81 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>343.6</v>
-      </c>
-      <c r="D27" s="12" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E27" s="12" t="n">
-        <v>15.8</v>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792
+67
+</t>
+        </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>20.3</v>
+        <v>0.3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>149.9</v>
+        <v>9</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+1119
+</t>
+        </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>18.5</v>
+        <v>25.2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.9</v>
+        <v>2.6</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>16.7</v>
+        <v>1.2</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>11.8</v>
+        <v>2.5</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>22.7</v>
+        <v>41.1</v>
       </c>
       <c r="R27" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X27" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="S27" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>82.40000000000001</v>
-      </c>
       <c r="Y27" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>1.9</v>
@@ -2787,76 +2764,74 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G28" s="12" t="n">
+        <v>370</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">792
+67
+</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="H28" s="3" t="n">
-        <v>70.7</v>
-      </c>
+      <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n">
         <v>2.5</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K28" s="3" t="n">
-        <v>7.9</v>
-      </c>
+      <c r="K28" s="3" t="n"/>
       <c r="L28" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>4.6</v>
+        <v>16.7</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>12.3</v>
+        <v>1.3</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>18.8</v>
+        <v>25.5</v>
+      </c>
+      <c r="R28" s="15" t="n">
+        <v>18.1</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>18.4</v>
+        <v>89.7</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>746.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>19</v>
+        <v>20.9</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>20.8</v>
+        <v>2.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>78.5</v>
+        <v>8383.6</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>22.4</v>
+        <v>4</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2872,43 +2847,49 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>343.6</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>21.9</v>
+        <v>453.6</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4007
+263
+</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="12" t="n">
+        <v>41.4</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>149.9</v>
+        <v>14.1</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>33.1</v>
+        <v>33.5</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>5.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10.9</v>
+        <v>26.9</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="M29" s="3" t="n">
-        <v>15</v>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6041
+151
+</t>
+        </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.4</v>
+        <v>7.1</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>84.8</v>
+        <v>584</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>3.1</v>
@@ -2916,29 +2897,29 @@
       <c r="Q29" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>12.7</v>
+      <c r="R29" s="15" t="n">
+        <v>727.2</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v>61.2</v>
+        <v>74.7</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>6.2</v>
       </c>
       <c r="V29" s="3" t="n">
-        <v>20.8</v>
+        <v>1</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>18.8</v>
+        <v>16.4</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>18.1</v>
+        <v>1.1</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>88</v>
+        <v>75.2</v>
       </c>
       <c r="Z29" s="3" t="n">
         <v>5</v>
@@ -2957,22 +2938,22 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>178.8</v>
+        <v>343.6</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>121.1</v>
+        <v>13.7</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>81.40000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>21.4</v>
+        <v>6.4</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>70.7</v>
+        <v>7</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>2.8</v>
@@ -2981,49 +2962,49 @@
         <v>4.1</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>16.8</v>
+        <v>55.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>86.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>21</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>22</v>
+        <v>228</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>18</v>
+        <v>18.7</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>109.4</v>
+        <v>4.6</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>1.2</v>
+        <v>81.5</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>161.8</v>
+        <v>20.8</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>91.8</v>
+        <v>18.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>20.9</v>
+        <v>26.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>2.8</v>
@@ -3042,76 +3023,80 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2357.7</v>
+        <v>1788.4</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>22.6</v>
+        <v>26.3</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>16.3</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>511.1</v>
-      </c>
-      <c r="H31" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="H31" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I31" s="8" t="n">
-        <v>83</v>
+      <c r="I31" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K31" s="8" t="n">
-        <v>29.7</v>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 3
+</t>
+        </is>
       </c>
       <c r="L31" s="3" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="N31" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N31" s="3" t="n"/>
+      <c r="O31" s="3" t="n">
+        <v>4584.5</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 48
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="O31" s="3" t="n">
-        <v>8543.1</v>
-      </c>
-      <c r="P31" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q31" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="S31" s="8" t="n">
-        <v>19.1</v>
+      <c r="S31" s="3" t="n">
+        <v>2.4</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>20.4</v>
+        <v>0.2</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>18.4</v>
+        <v>91.8</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>99.90000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>83.2</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>7</v>
+        <v>0.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3127,19 +3112,23 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>266.6</v>
-      </c>
-      <c r="D32" s="12" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="E32" s="12" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>26.7</v>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+77
+</t>
+        </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>13.4</v>
@@ -3150,53 +3139,53 @@
       <c r="J32" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K32" s="3" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>681.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+777
+</t>
+        </is>
       </c>
       <c r="O32" s="3" t="n">
-        <v>9</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>18.3</v>
+        <v>22.8</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>20.4</v>
+        <v>49.1</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>978</v>
+        <v>8.4</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>6.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>17.5</v>
+        <v>0.1</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>20.6</v>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="X32" s="3" t="n"/>
       <c r="Y32" s="3" t="n">
-        <v>94</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3212,16 +3201,16 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1400.8</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>21.3</v>
+        <v>266.6</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>9.300000000000001</v>
@@ -3232,56 +3221,52 @@
       <c r="I33" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K33" s="8" t="n">
-        <v>29.7</v>
-      </c>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>4.5</v>
+        <v>15.7</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>1.1</v>
+        <v>12.4</v>
+      </c>
+      <c r="P33" s="15" t="n">
+        <v>61.6</v>
       </c>
       <c r="Q33" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="S33" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="R33" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>19.8</v>
-      </c>
       <c r="T33" s="3" t="n">
-        <v>77.40000000000001</v>
+        <v>9</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="W33" s="8" t="n">
-        <v>28</v>
+        <v>17.5</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>12.7</v>
+        <v>18.7</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>86.8</v>
+        <v>946.1</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>30.2</v>
+        <v>12.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3297,73 +3282,75 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1250.2</v>
-      </c>
-      <c r="D34" s="12" t="n">
+        <v>406.8</v>
+      </c>
+      <c r="D34" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="3" t="n">
         <v>17</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>20.9</v>
+        <v>41.7</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H34" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="I34" s="8" t="n">
-        <v>12</v>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7777
+262
+</t>
+        </is>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>15.8</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="K34" s="3" t="n"/>
       <c r="L34" s="3" t="n">
-        <v>17.1</v>
+        <v>12.1</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.8</v>
+        <v>13.2</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>78</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>23.3</v>
+        <v>21.4</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>21.4</v>
+        <v>19.8</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>74.8</v>
+        <v>7.4</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>20.8</v>
+        <v>5.7</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>20.6</v>
+        <v>18.7</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>3.8</v>
@@ -3382,76 +3369,74 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>268.8</v>
-      </c>
-      <c r="D35" s="12" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D35" s="13" t="n">
         <v>24.8</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="13" t="n">
         <v>16.6</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="13" t="n">
         <v>20.7</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>8.199999999999999</v>
+      <c r="G35" s="3" t="n">
+        <v>7.8</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="I35" s="8" t="n">
-        <v>12</v>
+      <c r="I35" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10.8</v>
+        <v>0.1</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>11</v>
+        <v>1.7</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>820</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="N35" s="15" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="3" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>22.8</v>
+        <v>0.5</v>
       </c>
       <c r="R35" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S35" s="15" t="n">
         <v>19.8</v>
       </c>
-      <c r="S35" s="3" t="n">
-        <v>21.1</v>
-      </c>
       <c r="T35" s="3" t="n">
-        <v>76</v>
+        <v>4.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>13.9</v>
+        <v>7.8</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>20.1</v>
+        <v>10.7</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>1.1</v>
+        <v>60.6</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>89.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3467,76 +3452,70 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>356.8</v>
-      </c>
-      <c r="D36" s="12" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>8.4</v>
+        <v>468.8</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>13.4</v>
+        <v>13.9</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>14.9</v>
+        <v>2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="M36" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N36" s="3" t="n">
-        <v>15.4</v>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="M36" s="3" t="n"/>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="n">
-        <v>898</v>
+        <v>800.6</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>14.3</v>
+        <v>4</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>964.1</v>
+        <v>22.8</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>20.8</v>
+        <v>19.2</v>
       </c>
       <c r="S36" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="U36" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>80.8</v>
+        <v>76</v>
+      </c>
+      <c r="U36" s="3" t="n"/>
+      <c r="V36" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>19.8</v>
+        <v>18.9</v>
       </c>
       <c r="X36" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="Z36" s="3" t="n">
         <v>0.6</v>
-      </c>
-      <c r="Y36" s="3" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="Z36" s="3" t="n">
-        <v>1.1</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3552,71 +3531,75 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>164.3</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>111.7</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
+        <v>35.8</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>10.5</v>
+        <v>1.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.5</v>
+        <v>31.3</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>736.1</v>
+        <v>1.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
+        <v>88.3</v>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n">
+        <v>28.4</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>898</v>
+        <v>7</v>
       </c>
       <c r="P37" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>961.1</v>
+      </c>
+      <c r="R37" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="Q37" s="3" t="n">
-        <v>112.3</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>99.09999999999999</v>
-      </c>
       <c r="S37" s="3" t="n">
-        <v>3.8</v>
+        <v>21.1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>289.4</v>
-      </c>
-      <c r="U37" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>6.2</v>
+      </c>
+      <c r="U37" s="3" t="n"/>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
+2248
+</t>
+        </is>
       </c>
       <c r="W37" s="3" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>111.4</v>
+        <v>19.2</v>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+181 1
+</t>
+        </is>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>0.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>1.8</v>
@@ -3635,73 +3618,78 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>22.3</v>
+        <v>643.2</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>17.1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>97</v>
+        <v>8.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I38" s="8" t="n">
+      <c r="I38" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J38" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="J38" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>1.4</v>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5247
+2272
+1
+</t>
+        </is>
       </c>
       <c r="L38" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>0.6</v>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="P38" s="3" t="n"/>
+        <v>7.8</v>
+      </c>
+      <c r="P38" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Q38" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S38" s="8" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
+      </c>
+      <c r="R38" s="3" t="n"/>
+      <c r="S38" s="3" t="n">
+        <v>63.8</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>55.8</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>15</v>
+        <v>6.8</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="W38" s="8" t="n">
-        <v>92.09999999999999</v>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14441
+346
+</t>
+        </is>
       </c>
       <c r="X38" s="3" t="n"/>
       <c r="Y38" s="3" t="n">
-        <v>122.9</v>
-      </c>
-      <c r="Z38" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>4.4</v>
+      </c>
+      <c r="Z38" s="3" t="n"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3716,65 +3704,65 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E39" s="12" t="n">
-        <v>16</v>
+        <v>0.2</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+1 23
+</t>
+        </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>20.7</v>
+        <v>41.4</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n">
-        <v>20.9</v>
+        <v>2.1</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>3.7</v>
+      </c>
+      <c r="K39" s="3" t="n"/>
       <c r="L39" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>7.6</v>
+        <v>17.1</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>0.6</v>
+        <v>18.2</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>88</v>
+        <v>10.1</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>13.6</v>
+        <v>0.9</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>23.1</v>
+        <v>12.5</v>
+      </c>
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" s="15" t="n">
+        <v>18.1</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>80.8</v>
+        <v>7.1</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="W39" s="3" t="n">
-        <v>80.90000000000001</v>
+      <c r="W39" s="15" t="n">
+        <v>85.09999999999999</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>18.5</v>
@@ -3782,9 +3770,7 @@
       <c r="Y39" s="3" t="n">
         <v>88.90000000000001</v>
       </c>
-      <c r="Z39" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="Z39" s="3" t="n"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3801,23 +3787,19 @@
       <c r="C40" s="3" t="n">
         <v>264.4</v>
       </c>
-      <c r="D40" s="12" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="D40" s="13" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n">
-        <v>12.6</v>
+        <v>9.4</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>3.8</v>
@@ -3825,35 +3807,34 @@
       <c r="K40" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L40" s="3" t="n">
-        <v>43.8</v>
-      </c>
+      <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="N40" s="3" t="n">
-        <v>1.8</v>
-      </c>
+        <v>15.8</v>
+      </c>
+      <c r="N40" s="3" t="n"/>
       <c r="O40" s="3" t="n">
-        <v>88</v>
+        <v>285.2</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R40" s="8" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>6</v>
+        <v>23.1</v>
+      </c>
+      <c r="R40" s="15" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">231 1
+</t>
+        </is>
       </c>
       <c r="T40" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>1.2</v>
+        <v>72.09999999999999</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>20</v>
@@ -3868,7 +3849,7 @@
         <v>89.7</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3884,61 +3865,61 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>359</v>
+        <v>286.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>1.5</v>
+        <v>15.8</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>29.7</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H41" s="3" t="n">
         <v>1.8</v>
       </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+111
+</t>
+        </is>
+      </c>
       <c r="I41" s="3" t="n">
-        <v>7.1</v>
+        <v>2.6</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="8" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>18.6</v>
+        <v>9</v>
+      </c>
+      <c r="L41" s="3" t="n"/>
+      <c r="M41" s="3" t="n"/>
+      <c r="N41" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>76.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S41" s="8" t="n">
-        <v>20.4</v>
+        <v>26.8</v>
+      </c>
+      <c r="R41" s="15" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>4.2</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v>12.8</v>
+        <v>744.4</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>23.3</v>
@@ -3947,10 +3928,10 @@
         <v>19.6</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>80.5</v>
+        <v>70.5</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>8.4</v>
@@ -3969,71 +3950,79 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G42" s="3" t="n"/>
+        <v>359</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>4.3</v>
+      </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n">
-        <v>7.1</v>
+        <v>3.9</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>15.7</v>
+        <v>16.3</v>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+2
+</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n"/>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9271249
+157
+</t>
+        </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>18.7</v>
+        <v>1.8</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="P42" s="8" t="n">
-        <v>31.6</v>
+        <v>6.6</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>3.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>14.1</v>
-      </c>
+        <v>57.9</v>
+      </c>
+      <c r="U42" s="3" t="n"/>
       <c r="V42" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X42" s="3" t="n">
         <v>19.4</v>
+      </c>
+      <c r="X42" s="15" t="n">
+        <v>13.4</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Z42" s="3" t="n"/>
+      <c r="Z42" s="3" t="n">
+        <v>72.09999999999999</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4048,63 +4037,79 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>73.45</v>
-      </c>
-      <c r="E43" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E43" s="13" t="n">
         <v>17.5</v>
       </c>
-      <c r="F43" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="8" t="n">
-        <v>161.5</v>
+      <c r="F43" s="13" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="N43" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711797
+127
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+118
+</t>
+        </is>
+      </c>
       <c r="O43" s="3" t="n">
-        <v>0.5</v>
+        <v>79.8</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>28.1</v>
+        <v>4.4</v>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S43" s="3" t="n"/>
+        <v>22.1</v>
+      </c>
+      <c r="R43" s="15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>19.9</v>
+      </c>
       <c r="T43" s="3" t="n">
-        <v>77.7</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>55.5</v>
+      </c>
+      <c r="U43" s="15" t="n">
+        <v>1686.8</v>
       </c>
       <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n">
-        <v>21.7</v>
-      </c>
+      <c r="W43" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X43" s="3" t="n"/>
       <c r="Y43" s="3" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+        <v>23.6</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>57.7</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4119,71 +4124,79 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="8" t="n">
-        <v>92.5</v>
+        <v>0.2</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+60292929572
+</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>5.5</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>69.7</v>
       </c>
-      <c r="I44" s="8" t="n">
-        <v>61.4</v>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1642
+24749414
+</t>
+        </is>
       </c>
       <c r="J44" s="3" t="n">
-        <v>26.1</v>
+        <v>2.1</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>90.2</v>
+        <v>7.7</v>
+      </c>
+      <c r="L44" s="15" t="n">
+        <v>87.8</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="N44" s="3" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
+118
+</t>
+        </is>
       </c>
       <c r="O44" s="3" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>29.1</v>
-      </c>
+        <v>72.7</v>
+      </c>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
       <c r="R44" s="3" t="n">
-        <v>80.8</v>
+        <v>7.1</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>80.8</v>
+        <v>72.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v>556.6</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>21</v>
-      </c>
+        <v>777.3</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V44" s="3" t="n"/>
       <c r="W44" s="3" t="n">
-        <v>18.7</v>
+        <v>98.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>21.7</v>
+        <v>0.8</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
@@ -4200,69 +4213,85 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>367.9</v>
+        <v>0.1</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>26.8</v>
+        <v>39.7</v>
       </c>
       <c r="E45" s="11" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>45.1</v>
+        <v>4.6</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>17912.9</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>13.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>8.5</v>
+        <v>17.9</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.2</v>
+        <v>26.1</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N45" s="3" t="n"/>
+        <v>7.9</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+1
+</t>
+        </is>
+      </c>
       <c r="O45" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>34.1</v>
+        <v>52.1</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>29.1</v>
+        <v>25.1</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>80.8</v>
+        <v>262.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>80.8</v>
+        <v>26.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>66</v>
+        <v>0.6</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>1.4</v>
+        <v>463.8</v>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4224574
+1
+</t>
+        </is>
       </c>
       <c r="W45" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X45" s="3" t="n"/>
+        <v>6.2</v>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+1
+</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>4.7</v>
+        <v>0.1</v>
       </c>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4279,51 +4308,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
-      <c r="F46" s="13" t="n"/>
-      <c r="G46" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1817857
+1 1
+1
+3
+6
+</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H46" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N46" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>1.6</v>
-      </c>
+        <v>11.1</v>
+      </c>
+      <c r="P46" s="3" t="n"/>
       <c r="Q46" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="R46" s="3" t="n"/>
       <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n"/>
       <c r="U46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V46" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="V46" s="15" t="n">
+        <v>18.9</v>
+      </c>
       <c r="W46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>11.1</v>
+        <v>6.2</v>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+1
+</t>
+        </is>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1.6</v>
+        <v>114.5</v>
       </c>
       <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,8 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -55,18 +61,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +146,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,13 +161,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -790,60 +778,64 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2389.8</v>
-      </c>
-      <c r="D4" s="11" t="n">
+        <v>389.8</v>
+      </c>
+      <c r="D4" s="12" t="n">
         <v>28.4</v>
       </c>
-      <c r="E4" s="11" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>22.1</v>
+      <c r="E4" s="12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>22.4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
+        <v>12.5</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="J4" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M4" s="14" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>195.1</v>
+      <c r="N4" s="13" t="n">
+        <v>88.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S4" s="3" t="inlineStr"/>
+        <v>21.8</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="T4" s="3" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="V4" s="14" t="n">
-        <v>820.8</v>
+      <c r="V4" s="13" t="n">
+        <v>20.3</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.7</v>
@@ -852,10 +844,10 @@
         <v>20.6</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>286.1</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>3.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -871,63 +863,67 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1428.6</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H5" s="14" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr"/>
+        <v>438.6</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>2214.4</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="J5" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K5" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="n">
+        <v>18.3</v>
+      </c>
       <c r="M5" s="3" t="n">
-        <v>17.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>193.1</v>
-      </c>
-      <c r="P5" s="14" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="Q5" s="14" t="n">
-        <v>224.8</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" s="14" t="n">
-        <v>1101.2</v>
+        <v>93.09999999999999</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="R5" s="13" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>23.3</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>13.1</v>
+        <v>84.3</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>1.4</v>
+        <v>17.2</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>19.1</v>
@@ -935,9 +931,7 @@
       <c r="Y5" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="Z5" s="3" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="Z5" s="3" t="inlineStr"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -954,50 +948,56 @@
       <c r="C6" s="3" t="n">
         <v>484.4</v>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <v>26.9</v>
+      <c r="D6" s="12" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>11.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>10.7</v>
+        <v>15.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+        <v>0.8</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>17.2</v>
+      </c>
       <c r="M6" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
+      </c>
+      <c r="N6" s="13" t="n">
+        <v>65.09999999999999</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="Q6" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="R6" s="14" t="n">
-        <v>20.3</v>
+      <c r="R6" s="3" t="n">
+        <v>22.3</v>
       </c>
       <c r="S6" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>6.4</v>
+        <v>69</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>10.9</v>
@@ -1005,17 +1005,17 @@
       <c r="V6" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="W6" s="14" t="n">
+      <c r="W6" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="X6" s="14" t="n">
+      <c r="X6" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>91</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1030,18 +1030,20 @@
           <t>4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="11" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="E7" s="11" t="n">
+      <c r="C7" s="3" t="n">
+        <v>274.4</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="E7" s="12" t="n">
         <v>16.2</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>12</v>
+      <c r="F7" s="9" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>12.8</v>
@@ -1049,18 +1051,18 @@
       <c r="I7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="14" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="N7" s="14" t="n">
-        <v>69.8</v>
+      <c r="L7" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>89.8</v>
@@ -1068,19 +1070,25 @@
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="Q7" s="13" t="n">
+        <v>88.2</v>
+      </c>
       <c r="R7" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="S7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="n">
+        <v>24.9</v>
+      </c>
       <c r="T7" s="3" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="U7" s="3" t="inlineStr"/>
-      <c r="V7" s="14" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="V7" s="13" t="n">
         <v>20.8</v>
       </c>
-      <c r="W7" s="14" t="n">
+      <c r="W7" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1090,7 +1098,7 @@
         <v>90</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>12.5</v>
+        <v>2.1</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1105,18 +1113,20 @@
           <t>5</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="n">
+        <v>1260.2</v>
+      </c>
       <c r="D8" s="12" t="n">
         <v>28.4</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="12" t="n">
         <v>17</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>12.4</v>
+        <v>22.7</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>11.4</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>14.2</v>
@@ -1125,10 +1135,10 @@
         <v>2.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>17</v>
@@ -1136,28 +1146,32 @@
       <c r="M8" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="N8" s="14" t="n">
-        <v>8.199999999999999</v>
+      <c r="N8" s="13" t="n">
+        <v>69.2</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>88.2</v>
       </c>
-      <c r="P8" s="14" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>24.5</v>
+      </c>
       <c r="R8" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="S8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="n">
+        <v>26.8</v>
+      </c>
       <c r="T8" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="V8" s="14" t="n">
-        <v>9.6</v>
+      <c r="V8" s="13" t="n">
+        <v>29.6</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>18</v>
@@ -1184,54 +1198,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="12" t="n">
-        <v>26</v>
+      <c r="C9" s="3" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>39.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>722.1</v>
+        <v>61.7</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>22.8</v>
+        <v>221.8</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>116.6</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>31</v>
+        <v>81.8</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>84.5</v>
       </c>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="n">
+        <v>212.3</v>
+      </c>
       <c r="O9" s="3" t="n">
-        <v>34220.1</v>
+        <v>22</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
+        <v>9.4</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>412.4</v>
+      </c>
       <c r="T9" s="3" t="n">
         <v>384.2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1938.5</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
+        <v>28.5</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>928.9</v>
+      </c>
       <c r="W9" s="3" t="n">
-        <v>927103.1</v>
-      </c>
-      <c r="X9" s="3" t="inlineStr"/>
+        <v>12.7</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>1120.1</v>
+      </c>
       <c r="Y9" s="3" t="n">
-        <v>19445.1</v>
+        <v>9445.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>12.8</v>
@@ -1252,46 +1286,72 @@
       <c r="C10" s="3" t="n">
         <v>428.1</v>
       </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="12" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="G10" s="14" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="D10" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>141.1</v>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M10" s="14" t="n">
-        <v>22017.1</v>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
+        <v>17.9</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>821.1</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>906.1</v>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
+        <v>90.59999999999999</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="Q10" s="13" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="S10" s="13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>76.8</v>
+      </c>
       <c r="U10" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="V10" s="3" t="inlineStr"/>
+      <c r="V10" s="3" t="n">
+        <v>89.8</v>
+      </c>
       <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr"/>
-      <c r="Y10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>89</v>
+      </c>
       <c r="Z10" s="3" t="n">
-        <v>25.1</v>
+        <v>215.1</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1307,70 +1367,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1299.6</v>
-      </c>
-      <c r="D11" s="11" t="n">
+        <v>299.6</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q11" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>416.8</v>
-      </c>
-      <c r="M11" s="14" t="n">
-        <v>27</v>
-      </c>
-      <c r="N11" s="14" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q11" s="14" t="n">
-        <v>66</v>
-      </c>
       <c r="R11" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S11" s="14" t="n">
-        <v>29</v>
+        <v>20.5</v>
+      </c>
+      <c r="S11" s="13" t="n">
+        <v>22</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U11" s="3" t="n">
+      <c r="U11" s="13" t="n">
         <v>10.6</v>
       </c>
-      <c r="V11" s="14" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W11" s="3" t="n">
+      <c r="V11" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="W11" s="13" t="n">
         <v>19.8</v>
       </c>
-      <c r="X11" s="3" t="inlineStr"/>
-      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>84.5</v>
+      </c>
       <c r="Z11" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1386,19 +1452,19 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2343.6</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>22.4</v>
+        <v>343.6</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>22.5</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>29.1</v>
+        <v>9.1</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>15</v>
@@ -1407,10 +1473,10 @@
         <v>2.4</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K12" s="14" t="n">
-        <v>28.4</v>
+        <v>8.4</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.4</v>
@@ -1418,42 +1484,44 @@
       <c r="M12" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="N12" s="14" t="n">
-        <v>3.6</v>
+      <c r="N12" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>192.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.6</v>
+        <v>16.6</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0.9</v>
+        <v>22.2</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V12" s="14" t="n">
+      <c r="V12" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>82.90000000000001</v>
-      </c>
-      <c r="Y12" s="3" t="inlineStr"/>
+        <v>20.2</v>
+      </c>
+      <c r="X12" s="13" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
       <c r="Z12" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1469,43 +1537,45 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2323.8</v>
-      </c>
-      <c r="D13" s="11" t="n">
+        <v>29323.8</v>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>27.6</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="G13" s="12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="I13" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M13" s="14" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="M13" s="13" t="n">
         <v>16.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.8</v>
+        <v>14.8</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>92.2</v>
       </c>
-      <c r="P13" s="14" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="Q13" s="14" t="n">
-        <v>16.4</v>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="n">
+        <v>24.4</v>
       </c>
       <c r="R13" s="3" t="n">
         <v>21.4</v>
@@ -1514,25 +1584,25 @@
         <v>23.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>17.5</v>
+        <v>27.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V13" s="14" t="n">
+      <c r="V13" s="13" t="n">
         <v>19.8</v>
       </c>
-      <c r="W13" s="14" t="n">
-        <v>99.40000000000001</v>
+      <c r="W13" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>10.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1548,55 +1618,61 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="D14" s="11" t="n">
+        <v>8600.4</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>24.8</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
+        <v>17.4</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="I14" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="J14" s="14" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="14" t="n">
-        <v>18.3</v>
+      <c r="J14" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="N14" s="14" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="N14" s="3" t="n">
         <v>18.9</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.59999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>11.2</v>
+        <v>12.4</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="S14" s="14" t="n">
+      <c r="S14" s="13" t="n">
         <v>23.8</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>195.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>16.1</v>
+        <v>1.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>19.7</v>
@@ -1605,11 +1681,13 @@
         <v>19.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y14" s="3" t="inlineStr"/>
+        <v>22.5</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="Z14" s="3" t="n">
-        <v>10.7</v>
+        <v>0.7</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1625,33 +1703,37 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2334.8</v>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G15" s="14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H15" s="14" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="14" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="14" t="n">
+        <v>934.8</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>18.5</v>
@@ -1660,35 +1742,37 @@
         <v>94</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q15" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R15" s="14" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R15" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>199.3</v>
-      </c>
-      <c r="U15" s="14" t="n">
+        <v>995.3</v>
+      </c>
+      <c r="U15" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="13" t="n">
         <v>19.2</v>
       </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="14" t="n">
-        <v>6</v>
+      <c r="W15" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="X15" s="13" t="n">
+        <v>2.3</v>
       </c>
       <c r="Y15" s="3" t="n">
         <v>91</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1704,65 +1788,73 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>10161.8</v>
+        <v>268.8</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>134.2</v>
-      </c>
-      <c r="E16" s="16" t="n">
+        <v>1428.1</v>
+      </c>
+      <c r="E16" s="11" t="n">
         <v>82</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="11" t="n">
         <v>109.9</v>
       </c>
-      <c r="G16" s="12" t="n">
-        <v>148.1</v>
+      <c r="G16" s="9" t="n">
+        <v>48.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>72</v>
+        <v>190.8</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>110.8</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>14.9</v>
+        <v>114.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>11812.6</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>88.8</v>
       </c>
-      <c r="M16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="n">
+        <v>85.3</v>
+      </c>
       <c r="N16" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>8653.1</v>
+        <v>1465.9</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+        <v>6.9</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>311.4</v>
+      </c>
       <c r="T16" s="3" t="n">
-        <v>419.6</v>
+        <v>9920.799999999999</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>13359.1</v>
+        <v>35.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1101.8</v>
+        <v>101.8</v>
       </c>
       <c r="W16" s="3" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>109.7</v>
+        <v>108.7</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>457.4</v>
+        <v>4658.4</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>10.4</v>
@@ -1780,46 +1872,76 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>911.3</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <v>17.1</v>
-      </c>
+      <c r="C17" s="3" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>2011.7</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr"/>
-      <c r="P17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="P17" s="13" t="n">
+        <v>11.1</v>
+      </c>
       <c r="Q17" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr"/>
-      <c r="U17" s="3" t="inlineStr"/>
+      <c r="R17" s="13" t="n">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="S17" s="13" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>788.4</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="V17" s="3" t="n">
         <v>20.4</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X17" s="3" t="inlineStr"/>
-      <c r="Y17" s="3" t="inlineStr"/>
-      <c r="Z17" s="3" t="inlineStr"/>
+        <v>29.4</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>21.1</v>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1834,61 +1956,73 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>954.6</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F18" s="14" t="n">
+        <v>2954.6</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>20.9</v>
       </c>
-      <c r="G18" s="14" t="n">
+      <c r="G18" s="13" t="n">
         <v>16.7</v>
       </c>
-      <c r="H18" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>18.3</v>
+      <c r="H18" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L18" s="13" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>88.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="P18" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q18" s="14" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="P18" s="13" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Q18" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="R18" s="14" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="S18" s="14" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="T18" s="3" t="inlineStr"/>
-      <c r="U18" s="14" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="V18" s="14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="S18" s="13" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U18" s="13" t="n">
+        <v>4148.7</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="X18" s="13" t="n">
+        <v>26.7</v>
+      </c>
       <c r="Y18" s="3" t="n">
-        <v>83.5</v>
+        <v>80</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>14.1</v>
@@ -1906,39 +2040,47 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="11" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="E19" s="11" t="n">
+      <c r="C19" s="3" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="E19" s="12" t="n">
         <v>16.2</v>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
+      <c r="F19" s="13" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K19" s="3" t="n">
-        <v>2.3</v>
+        <v>25.3</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>27.9</v>
+      <c r="M19" s="13" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>8.9</v>
+        <v>15.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="P19" s="3" t="n">
-        <v>12.2</v>
+      <c r="P19" s="13" t="n">
+        <v>21.8</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>23.8</v>
@@ -1946,25 +2088,29 @@
       <c r="R19" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="T19" s="3" t="inlineStr"/>
+      <c r="S19" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>13.1</v>
+      </c>
       <c r="U19" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="W19" s="3" t="inlineStr"/>
+        <v>23.4</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>19.9</v>
+      </c>
       <c r="X19" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>13.6</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -1979,35 +2125,47 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="n">
+      <c r="C20" s="3" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="D20" s="12" t="n">
         <v>26.8</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>17.8</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
+        <v>22.3</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>21.9</v>
+      </c>
       <c r="K20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O20" s="3" t="inlineStr"/>
+        <v>21.2</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>97</v>
+      </c>
       <c r="P20" s="3" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>22.8</v>
@@ -2015,25 +2173,29 @@
       <c r="R20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S20" s="14" t="n">
+      <c r="S20" s="13" t="n">
         <v>24.7</v>
       </c>
-      <c r="T20" s="3" t="inlineStr"/>
-      <c r="U20" s="14" t="n">
-        <v>23.1</v>
+      <c r="T20" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>3.1</v>
       </c>
       <c r="V20" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W20" s="3" t="inlineStr"/>
+      <c r="W20" s="3" t="n">
+        <v>20.2</v>
+      </c>
       <c r="X20" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>23.2</v>
       </c>
       <c r="Y20" s="3" t="n">
         <v>93.8</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2049,34 +2211,44 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1284.8</v>
-      </c>
-      <c r="D21" s="11" t="n">
+        <v>1824.6</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F21" s="11" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
+      <c r="F21" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>71.09999999999999</v>
+      </c>
       <c r="H21" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+        <v>87</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="K21" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="L21" s="14" t="n">
-        <v>18</v>
+        <v>3.5</v>
+      </c>
+      <c r="L21" s="13" t="n">
+        <v>68</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr"/>
+      <c r="N21" s="13" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>94</v>
+      </c>
       <c r="P21" s="3" t="n">
         <v>18.2</v>
       </c>
@@ -2086,27 +2258,29 @@
       <c r="R21" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="S21" s="14" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="T21" s="3" t="inlineStr"/>
-      <c r="U21" s="14" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="V21" s="14" t="n">
+      <c r="S21" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W21" s="14" t="n">
-        <v>20.6</v>
+      <c r="W21" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>10.8</v>
+        <v>0.8</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2122,65 +2296,67 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2339.2</v>
-      </c>
-      <c r="D22" s="11" t="n">
+        <v>339.2</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>27.6</v>
       </c>
-      <c r="E22" s="11" t="n">
+      <c r="E22" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <v>22.3</v>
       </c>
-      <c r="G22" s="11" t="n">
-        <v>10.8</v>
+      <c r="G22" s="12" t="n">
+        <v>10.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>21.6</v>
+        <v>84.59999999999999</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>16.2</v>
+        <v>4.2</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="14" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="M22" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>21.4</v>
+      </c>
       <c r="O22" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>0.5</v>
+        <v>25.1</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="S22" s="14" t="n">
+      <c r="S22" s="13" t="n">
         <v>23.6</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>19</v>
+        <v>23.6</v>
+      </c>
+      <c r="W22" s="13" t="n">
+        <v>219</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>19.6</v>
@@ -2189,7 +2365,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2204,56 +2380,76 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="9" t="inlineStr"/>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="9" t="inlineStr"/>
-      <c r="G23" s="12" t="n">
-        <v>51.6</v>
+      <c r="C23" s="3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>74.8</v>
+        <v>14.2</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1121.2</v>
+        <v>12.2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>169.9</v>
+        <v>129.9</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>66.09999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>889.4</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>81.8</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>1469.1</v>
+        <v>269.1</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>8115.8</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>393.8</v>
+        <v>299.1</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>2399.2</v>
+        <v>99.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>110.3</v>
-      </c>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr"/>
-      <c r="Y23" s="3" t="inlineStr"/>
-      <c r="Z23" s="3" t="inlineStr"/>
+        <v>110</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>199.6</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>406.8</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>122.9</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2271,69 +2467,69 @@
         <v>2309.7</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>17.4</v>
+        <v>27.5</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>17</v>
       </c>
       <c r="F24" s="11" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I24" s="13" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="M24" s="13" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>938.1</v>
+      </c>
+      <c r="P24" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="L24" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="N24" s="3" t="inlineStr"/>
-      <c r="O24" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Q24" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R24" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="S24" s="3" t="n">
+      <c r="Q24" s="13" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="R24" s="13" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="S24" s="13" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V24" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="T24" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>28.1</v>
-      </c>
       <c r="W24" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="X24" s="3" t="inlineStr"/>
-      <c r="Y24" s="3" t="n">
-        <v>713</v>
-      </c>
+        <v>29.9</v>
+      </c>
+      <c r="X24" s="13" t="n">
+        <v>1183.4</v>
+      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
       <c r="Z24" s="3" t="n">
-        <v>16.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2348,73 +2544,77 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="11" t="n">
+      <c r="C25" s="3" t="n">
+        <v>279.8</v>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>24.8</v>
       </c>
-      <c r="E25" s="11" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>22.9</v>
+      <c r="E25" s="12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H25" s="13" t="n">
+        <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>89.5</v>
+        <v>11.9</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>10.1</v>
+        <v>2.7</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="M25" s="14" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="N25" s="14" t="n">
-        <v>88.8</v>
+        <v>0.4</v>
+      </c>
+      <c r="L25" s="13" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>4.5</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q25" s="14" t="n">
-        <v>22.7</v>
+        <v>1.9</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S25" s="3" t="inlineStr"/>
+        <v>20.1</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="T25" s="3" t="n">
-        <v>83.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="V25" s="14" t="n">
-        <v>20.6</v>
+      <c r="V25" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="W25" s="3" t="n">
-        <v>19.8</v>
+        <v>18</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>22.4</v>
+        <v>18.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2430,66 +2630,76 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>370</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G26" s="11" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>2.5</v>
+        <v>341.4</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I26" s="13" t="n">
+        <v>25.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>39.5</v>
+        <v>3.7</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>168.1</v>
-      </c>
-      <c r="M26" s="14" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="N26" s="3" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
+      <c r="L26" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>82.8</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>12.3</v>
+        <v>10.7</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="3" t="inlineStr"/>
-      <c r="T26" s="3" t="inlineStr"/>
+        <v>22.7</v>
+      </c>
+      <c r="R26" s="13" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>83.90000000000001</v>
+      </c>
       <c r="U26" s="3" t="n">
-        <v>9.9</v>
+        <v>4.7</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="W26" s="3" t="inlineStr"/>
-      <c r="X26" s="14" t="n">
-        <v>14.1</v>
+        <v>20.6</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>16</v>
+        <v>1.9</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2505,66 +2715,76 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1453.6</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F27" s="11" t="n">
+        <v>370</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="R27" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H27" s="14" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="M27" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
-      <c r="P27" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q27" s="14" t="n">
-        <v>206.8</v>
-      </c>
-      <c r="R27" s="14" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="S27" s="3" t="inlineStr"/>
-      <c r="T27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>636.4</v>
+      </c>
       <c r="U27" s="3" t="n">
-        <v>6.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr"/>
+        <v>20.9</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="X27" s="3" t="n">
-        <v>12.1</v>
+        <v>20.8</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>78.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2580,72 +2800,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2343.6</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H28" s="14" t="n">
-        <v>14</v>
+        <v>453.6</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>2.8</v>
+        <v>93.3</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>18.6</v>
+        <v>28.8</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.9</v>
+        <v>26.8</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>15.8</v>
+        <v>16.7</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>15</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="O28" s="3" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>84</v>
+      </c>
       <c r="P28" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Q28" s="14" t="n">
-        <v>292</v>
+        <v>3.1</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="S28" s="14" t="n">
-        <v>3811.6</v>
-      </c>
-      <c r="T28" s="3" t="inlineStr"/>
+        <v>17.8</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="U28" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V28" s="14" t="n">
-        <v>20.8</v>
+        <v>6.8</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X28" s="14" t="n">
-        <v>20.9</v>
+        <v>26.4</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>13.1</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>88</v>
+        <v>78.5</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>10.8</v>
+        <v>2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2661,59 +2885,73 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1788.4</v>
+        <v>343.6</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
+        <v>26.6</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>21.4</v>
+      </c>
       <c r="G29" s="3" t="n">
-        <v>50</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>702.3</v>
-      </c>
-      <c r="I29" s="14" t="n">
-        <v>63</v>
+        <v>14</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>4.8</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="L29" s="13" t="n">
+        <v>16.6</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>81.8</v>
+        <v>15.5</v>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="n">
-        <v>454.5</v>
-      </c>
+      <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
+        <v>2.6</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>81.59999999999999</v>
+      </c>
       <c r="T29" s="3" t="n">
-        <v>392.2</v>
-      </c>
-      <c r="U29" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="V29" s="14" t="n">
-        <v>11.8</v>
+        <v>81.5</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="X29" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>20.9</v>
+      </c>
       <c r="Y29" s="3" t="n">
-        <v>12008</v>
-      </c>
-      <c r="Z29" s="3" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2727,38 +2965,76 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="16" t="n">
-        <v>8010.1</v>
-      </c>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="9" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>131.8</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>20</v>
+      </c>
       <c r="H30" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
+        <v>700.9</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>893.9</v>
+      </c>
       <c r="M30" s="3" t="n">
-        <v>10181.1</v>
-      </c>
-      <c r="N30" s="3" t="inlineStr"/>
-      <c r="O30" s="3" t="inlineStr"/>
-      <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="inlineStr"/>
+        <v>81.2</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>1424.9</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>111.2</v>
+      </c>
       <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr"/>
-      <c r="T30" s="3" t="inlineStr"/>
-      <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="inlineStr"/>
-      <c r="W30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="n">
+        <v>8109.4</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>222.2</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>91.8</v>
+      </c>
       <c r="X30" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
-      <c r="Z30" s="3" t="inlineStr"/>
+        <v>999.8</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>120</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2773,70 +3049,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1266.6</v>
+        <v>2357.7</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>19.1</v>
+        <v>26.4</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>16.2</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>21.3</v>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>110</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="I31" s="14" t="n">
-        <v>82.2</v>
+        <v>14.1</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M31" s="3" t="inlineStr"/>
+        <v>9.9</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="13" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>120810.1</v>
+      </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>792</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="R31" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>20.4</v>
+        <v>22.8</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>126.6</v>
+      </c>
+      <c r="S31" s="13" t="n">
+        <v>19.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>98</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>0.7</v>
+        <v>61.1</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W31" s="14" t="n">
-        <v>16.9</v>
+        <v>10.4</v>
+      </c>
+      <c r="W31" s="13" t="n">
+        <v>84.09999999999999</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>18.9</v>
+        <v>10</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>1940.6</v>
+        <v>83.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1.2</v>
+        <v>40.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2852,60 +3132,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1400.8</v>
-      </c>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F32" s="14" t="n">
+        <v>266.6</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>21.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H32" s="14" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="I32" s="13" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="J32" s="13" t="n">
+        <v>1.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>15.4</v>
+      </c>
       <c r="N32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
+        <v>12.9</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>92</v>
+      </c>
       <c r="P32" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr"/>
-      <c r="S32" s="3" t="n">
-        <v>19.8</v>
+        <v>1</v>
+      </c>
+      <c r="Q32" s="13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="R32" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="S32" s="13" t="n">
+        <v>206.4</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>279.4</v>
+        <v>91</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>5.7</v>
+        <v>10.4</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="W32" s="3" t="inlineStr"/>
-      <c r="X32" s="3" t="n">
-        <v>12.7</v>
+        <v>17.5</v>
+      </c>
+      <c r="W32" s="13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X32" s="13" t="n">
+        <v>8.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>86.5</v>
+        <v>94</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>29.2</v>
+        <v>182</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -2921,62 +3217,76 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1350.2</v>
-      </c>
-      <c r="D33" s="11" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="F33" s="11" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G33" s="11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H33" s="14" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
+        <v>1400.8</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>12.6</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>29.7</v>
+        <v>24.1</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="L33" s="3" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>17.1</v>
+      </c>
       <c r="M33" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
       <c r="P33" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q33" s="3" t="inlineStr"/>
+        <v>14.8</v>
+      </c>
+      <c r="Q33" s="13" t="n">
+        <v>18.4</v>
+      </c>
       <c r="R33" s="3" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>11.8</v>
+        <v>19.8</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>74.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="V33" s="14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W33" s="3" t="inlineStr"/>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>5.7</v>
+      </c>
+      <c r="V33" s="13" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="W33" s="13" t="n">
+        <v>88</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>84</v>
+        <v>86.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>293.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -2992,57 +3302,77 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1268.8</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="n">
+        <v>2350.2</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M34" s="13" t="n">
         <v>16.6</v>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
+      <c r="N34" s="13" t="n">
+        <v>11.9</v>
+      </c>
       <c r="O34" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
+        <v>91.8</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="Q34" s="3" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>19.1</v>
+        <v>20</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>28.1</v>
+        <v>21.4</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>86</v>
+        <v>74.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="V34" s="14" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="W34" s="3" t="inlineStr"/>
+        <v>7.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="X34" s="3" t="n">
-        <v>8.1</v>
+        <v>20.6</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -3057,62 +3387,76 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1356.8</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr"/>
+        <v>268.8</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>20.7</v>
+      </c>
       <c r="G35" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H35" s="3" t="inlineStr"/>
+        <v>8.9</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="I35" s="3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="K35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="P35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="14" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="O35" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
       <c r="Q35" s="3" t="n">
-        <v>26.7</v>
+        <v>22.8</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>6.8</v>
+        <v>19.1</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>160.2</v>
+        <v>86</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>12.9</v>
+        <v>1.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="X35" s="14" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="Y35" s="3" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>89.2</v>
+      </c>
       <c r="Z35" s="3" t="n">
-        <v>1.1</v>
+        <v>244.1</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3127,60 +3471,76 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="n">
+        <v>356.8</v>
+      </c>
       <c r="D36" s="12" t="n">
-        <v>131.3</v>
+        <v>28.2</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>82.90000000000001</v>
+        <v>16.1</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>107.1</v>
-      </c>
-      <c r="G36" s="11" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="H36" s="14" t="n">
-        <v>710.6</v>
+        <v>22.1</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J36" s="14" t="n">
-        <v>166.7</v>
-      </c>
-      <c r="K36" s="14" t="n">
-        <v>60.6</v>
+        <v>1.9</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>88.3</v>
+        <v>17.1</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>18</v>
+        <v>14.6</v>
       </c>
       <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>18298</v>
-      </c>
-      <c r="P36" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="P36" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="R36" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
+      <c r="S36" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="T36" s="3" t="n">
-        <v>20859.4</v>
-      </c>
-      <c r="U36" s="14" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="V36" s="14" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="W36" s="3" t="inlineStr"/>
-      <c r="X36" s="3" t="inlineStr"/>
-      <c r="Y36" s="3" t="inlineStr"/>
-      <c r="Z36" s="3" t="inlineStr"/>
+        <v>60.2</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3194,48 +3554,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="9" t="inlineStr"/>
-      <c r="E37" s="9" t="inlineStr"/>
-      <c r="F37" s="9" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="n">
+        <v>1640.2</v>
+      </c>
+      <c r="D37" s="12" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="E37" s="12" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>48.5</v>
+      </c>
       <c r="H37" s="3" t="n">
-        <v>114.1</v>
-      </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>10.6</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>1600.6</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="M37" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>86</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>796.1</v>
+        <v>298</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>4.2</v>
+        <v>180.8</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>22.8</v>
+        <v>122.9</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>19.4</v>
+        <v>146.1</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="T37" s="3" t="inlineStr"/>
-      <c r="U37" s="3" t="inlineStr"/>
+        <v>100.8</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>680.5</v>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>194.2</v>
+      </c>
       <c r="V37" s="3" t="n">
-        <v>29.6</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>206.1</v>
-      </c>
+        <v>921.2</v>
+      </c>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>89.7</v>
+        <v>4481.7</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3251,62 +3635,72 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
-        <v>12264.4</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="F38" s="3" t="inlineStr"/>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="n">
-        <v>13.2</v>
+      <c r="C38" s="3" t="inlineStr"/>
+      <c r="D38" s="12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>14.1</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="J38" s="13" t="n">
+        <v>23.1</v>
+      </c>
       <c r="K38" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L38" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M38" s="3" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>15.4</v>
+      </c>
       <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>185</v>
+        <v>796.1</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q38" s="14" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R38" s="14" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="S38" s="14" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="3" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="Q38" s="13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>117.8</v>
+      </c>
+      <c r="S38" s="13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>771.1</v>
+      </c>
+      <c r="U38" s="13" t="n">
+        <v>46.4</v>
+      </c>
       <c r="V38" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="W38" s="14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="X38" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W38" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="Y38" s="3" t="inlineStr"/>
-      <c r="Z38" s="3" t="n">
-        <v>211.4</v>
-      </c>
+      <c r="X38" s="13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3321,23 +3715,23 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1286.4</v>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>95.64</v>
-      </c>
-      <c r="E39" s="3" t="n">
+        <v>286.4</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="E39" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="F39" s="12" t="n">
-        <v>80.7</v>
+      <c r="F39" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="J39" s="3" t="n">
         <v>3.8</v>
@@ -3345,45 +3739,41 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="14" t="n">
-        <v>87.7</v>
+      <c r="L39" s="13" t="n">
+        <v>7.7</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>19.8</v>
+        <v>11.1</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>846.6</v>
-      </c>
-      <c r="P39" s="14" t="n">
-        <v>23.6</v>
+        <v>88.5</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>3.6</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="R39" s="3" t="n">
-        <v>19.5</v>
+      <c r="R39" s="13" t="n">
+        <v>20.9</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
       <c r="U39" s="3" t="inlineStr"/>
-      <c r="V39" s="14" t="n">
+      <c r="V39" s="3" t="n">
         <v>20</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X39" s="3" t="n">
-        <v>21</v>
-      </c>
+      <c r="X39" s="3" t="inlineStr"/>
       <c r="Y39" s="3" t="inlineStr"/>
-      <c r="Z39" s="3" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3398,40 +3788,44 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>12359</v>
-      </c>
-      <c r="D40" s="11" t="n">
+        <v>5359</v>
+      </c>
+      <c r="D40" s="12" t="n">
         <v>27.5</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="12" t="n">
         <v>15.6</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="G40" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H40" s="14" t="n">
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="13" t="n">
         <v>13.8</v>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="n">
+        <v>85.90000000000001</v>
+      </c>
       <c r="J40" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="K40" s="3" t="inlineStr"/>
       <c r="L40" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+      <c r="M40" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="14" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="R40" s="3" t="n">
@@ -3446,17 +3840,21 @@
       <c r="U40" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V40" s="14" t="n">
-        <v>1.2</v>
+      <c r="V40" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="Y40" s="3" t="inlineStr"/>
-      <c r="Z40" s="3" t="inlineStr"/>
+        <v>21.8</v>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="Z40" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3471,33 +3869,43 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1486.6</v>
+        <v>8866.4</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="E41" s="13" t="inlineStr"/>
-      <c r="F41" s="13" t="inlineStr"/>
-      <c r="G41" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H41" s="14" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="I41" s="3" t="inlineStr"/>
+      <c r="E41" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F41" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="J41" s="3" t="n">
-        <v>6.3</v>
+        <v>16.3</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="14" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
-      <c r="O41" s="3" t="inlineStr"/>
-      <c r="P41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>50</v>
+      </c>
       <c r="Q41" s="3" t="n">
         <v>26</v>
       </c>
@@ -3507,21 +3915,25 @@
       <c r="S41" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="T41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="n">
+        <v>57.9</v>
+      </c>
       <c r="U41" s="3" t="n">
-        <v>16.8</v>
+        <v>14.1</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="W41" s="3" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="W41" s="3" t="inlineStr"/>
       <c r="X41" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="Y41" s="3" t="inlineStr"/>
-      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>8.4</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3536,52 +3948,60 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1942.6</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E42" s="13" t="inlineStr"/>
+        <v>942.6</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>17.5</v>
+      </c>
       <c r="F42" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G42" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G42" s="12" t="n">
         <v>10.1</v>
       </c>
-      <c r="H42" s="3" t="n">
+      <c r="H42" s="13" t="n">
         <v>14.8</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="14" t="n">
-        <v>92.8</v>
+      <c r="J42" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L42" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M42" s="14" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="N42" s="3" t="inlineStr"/>
-      <c r="O42" s="3" t="inlineStr"/>
+      <c r="M42" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>79.8</v>
+      </c>
       <c r="P42" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Q42" s="14" t="n">
-        <v>78.09999999999999</v>
+        <v>14.2</v>
+      </c>
+      <c r="Q42" s="13" t="n">
+        <v>84.09999999999999</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>19.9</v>
+      <c r="S42" s="13" t="n">
+        <v>29.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="U42" s="3" t="inlineStr"/>
+        <v>55.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="V42" s="3" t="n">
         <v>22.2</v>
       </c>
@@ -3589,12 +4009,14 @@
         <v>18.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>19.7</v>
+        <v>89.7</v>
       </c>
       <c r="Y42" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="Z42" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3609,53 +4031,69 @@
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="13" t="inlineStr"/>
-      <c r="E43" s="12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H43" s="14" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J43" s="14" t="n">
-        <v>68.09999999999999</v>
+      <c r="D43" s="9" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H43" s="13" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="I43" s="13" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="J43" s="13" t="n">
+        <v>26.1</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>90.8</v>
+        <v>90.2</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="n">
-        <v>1205.5</v>
-      </c>
-      <c r="P43" s="14" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="P43" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
-      <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr"/>
-      <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="14" t="n">
+      <c r="Q43" s="13" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="V43" s="13" t="n">
         <v>4.8</v>
       </c>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="inlineStr"/>
+      <c r="W43" s="13" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>2011</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>22</v>
+        <v>406.7</v>
       </c>
       <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
@@ -3671,10 +4109,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="13" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr"/>
-      <c r="F44" s="13" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="14" t="inlineStr"/>
+      <c r="E44" s="14" t="inlineStr"/>
+      <c r="F44" s="14" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -3709,20 +4149,22 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2368.9</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
+        <v>362.9</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>10.5</v>
+      </c>
       <c r="H45" s="3" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>9.5</v>
@@ -3730,31 +4172,51 @@
       <c r="J45" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K45" s="3" t="inlineStr"/>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>15.9</v>
+      </c>
       <c r="N45" s="3" t="n">
-        <v>16.4</v>
+        <v>11.6</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>29.9</v>
+        <v>9.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>25.1</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr"/>
-      <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
-      <c r="Y45" s="3" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -3770,35 +4232,65 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="9" t="inlineStr"/>
-      <c r="E46" s="9" t="inlineStr"/>
-      <c r="F46" s="9" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
+      <c r="D46" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="H46" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
-      <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
-      <c r="P46" s="3" t="inlineStr"/>
+        <v>1.4</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>410.7</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="Q46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>28.5</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="R46" s="3" t="inlineStr"/>
       <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr"/>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="X46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,10 +152,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,10 +167,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -784,13 +793,13 @@
         <v>28.4</v>
       </c>
       <c r="E4" s="12" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12.5</v>
+        <v>82.5</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>12.5</v>
@@ -802,22 +811,22 @@
         <v>5.5</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10.8</v>
+        <v>0.6</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>27.9</v>
+        <v>17.9</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="N4" s="13" t="n">
+      <c r="N4" s="8" t="n">
         <v>88.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>90</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>23.7</v>
@@ -825,7 +834,7 @@
       <c r="R4" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="8" t="n">
         <v>25</v>
       </c>
       <c r="T4" s="3" t="n">
@@ -834,8 +843,8 @@
       <c r="U4" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="V4" s="13" t="n">
-        <v>20.3</v>
+      <c r="V4" s="3" t="n">
+        <v>80.3</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>18.7</v>
@@ -847,7 +856,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>33.6</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -863,7 +872,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>438.6</v>
+        <v>9432.6</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>40.1</v>
@@ -874,11 +883,11 @@
       <c r="F5" s="3" t="n">
         <v>28.5</v>
       </c>
-      <c r="G5" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>2214.4</v>
+      <c r="G5" s="9" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>21.1</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>2.8</v>
@@ -886,20 +895,20 @@
       <c r="J5" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="8" t="n">
         <v>22.3</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>87.59999999999999</v>
+      <c r="M5" s="8" t="n">
+        <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>93.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>11.4</v>
@@ -907,14 +916,14 @@
       <c r="Q5" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="R5" s="13" t="n">
+      <c r="R5" s="3" t="n">
         <v>21.3</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>84.3</v>
+        <v>74.3</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>81.09999999999999</v>
@@ -976,14 +985,12 @@
         <v>17.2</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="N6" s="13" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>92</v>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="n">
         <v>1.6</v>
       </c>
@@ -1031,19 +1038,19 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>274.4</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>54.2</v>
+        <v>384.4</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>28.2</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>1.1</v>
+        <v>16.3</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>12</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>12.8</v>
@@ -1051,7 +1058,9 @@
       <c r="I7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="K7" s="3" t="n">
         <v>0.2</v>
       </c>
@@ -1062,16 +1071,16 @@
         <v>17.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>17.8</v>
+        <v>12.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>89.8</v>
+        <v>0.8</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="13" t="n">
-        <v>88.2</v>
+      <c r="Q7" s="3" t="n">
+        <v>27.3</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>22.7</v>
@@ -1080,12 +1089,12 @@
         <v>24.9</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>18.7</v>
+        <v>68.7</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V7" s="13" t="n">
+      <c r="V7" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="W7" s="3" t="n">
@@ -1114,7 +1123,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1260.2</v>
+        <v>260.2</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>28.4</v>
@@ -1135,7 +1144,7 @@
         <v>2.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>4.1</v>
@@ -1146,14 +1155,14 @@
       <c r="M8" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="N8" s="13" t="n">
-        <v>69.2</v>
+      <c r="N8" s="8" t="n">
+        <v>67.2</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>88.2</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q8" s="3" t="n">
         <v>24.5</v>
@@ -1170,8 +1179,8 @@
       <c r="U8" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="V8" s="13" t="n">
-        <v>29.6</v>
+      <c r="V8" s="3" t="n">
+        <v>19.6</v>
       </c>
       <c r="W8" s="3" t="n">
         <v>18</v>
@@ -1199,43 +1208,43 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>140.4</v>
+        <v>3440.5</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>82</v>
+        <v>1824.8</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>82.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>112.4</v>
+        <v>12.4</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>39.1</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>221.8</v>
+        <v>22.8</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>81.8</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>84.5</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>212.3</v>
+        <v>12.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.4</v>
@@ -1244,31 +1253,29 @@
         <v>127.1</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>110.9</v>
-      </c>
-      <c r="S9" s="3" t="n">
-        <v>412.4</v>
-      </c>
+        <v>91.2</v>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="n">
         <v>384.2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>28.5</v>
+        <v>38.5</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>928.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>12.7</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>1120.1</v>
+        <v>162.8</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>9445.1</v>
+        <v>445.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>12.8</v>
+        <v>122.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1287,52 +1294,52 @@
         <v>428.1</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="E10" s="12" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="E10" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="I10" s="3" t="n">
+      <c r="F10" s="9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I10" s="8" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>141.1</v>
+        <v>14.6</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>17.9</v>
+        <v>19.9</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="N10" s="13" t="n">
-        <v>821.1</v>
+        <v>4.3</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>687.8</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="Q10" s="13" t="n">
-        <v>25.4</v>
+        <v>18.9</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>2.9</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="S10" s="13" t="n">
-        <v>12.4</v>
+        <v>22.1</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>24.9</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>76.8</v>
@@ -1340,8 +1347,8 @@
       <c r="U10" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="V10" s="3" t="n">
-        <v>89.8</v>
+      <c r="V10" s="8" t="n">
+        <v>98.09999999999999</v>
       </c>
       <c r="W10" s="3" t="inlineStr"/>
       <c r="X10" s="3" t="n">
@@ -1351,7 +1358,7 @@
         <v>89</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>215.1</v>
+        <v>2.5</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1369,68 +1376,68 @@
       <c r="C11" s="3" t="n">
         <v>299.6</v>
       </c>
-      <c r="D11" s="12" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>5.1</v>
+      <c r="D11" s="9" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>31.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>81</v>
+        <v>0.4</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>17</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>28.1</v>
+        <v>41.4</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>98</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>26.6</v>
       </c>
-      <c r="R11" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="S11" s="13" t="n">
-        <v>22</v>
+      <c r="R11" s="8" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>23</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U11" s="13" t="n">
+      <c r="U11" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="W11" s="13" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="W11" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>84.5</v>
@@ -1454,16 +1461,16 @@
       <c r="C12" s="3" t="n">
         <v>343.6</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="G12" s="3" t="n">
+      <c r="D12" s="12" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G12" s="12" t="n">
         <v>9.1</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1476,7 +1483,7 @@
         <v>8.4</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8.4</v>
+        <v>28.4</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.4</v>
@@ -1488,22 +1495,22 @@
         <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>16.6</v>
+        <v>1.6</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>22.2</v>
+        <v>8.6</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>93</v>
+        <v>923</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>1.6</v>
@@ -1514,14 +1521,14 @@
       <c r="W12" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="X12" s="13" t="n">
-        <v>12.9</v>
+      <c r="X12" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="Y12" s="3" t="n">
         <v>89.09999999999999</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1537,16 +1544,16 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>29323.8</v>
+        <v>2323.8</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>27.6</v>
+        <v>27.5</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>17.1</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>10.5</v>
@@ -1559,20 +1566,18 @@
       </c>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="M13" s="13" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M13" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>92.2</v>
-      </c>
+        <v>13.8</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="3" t="n">
         <v>24.4</v>
@@ -1584,18 +1589,18 @@
         <v>23.7</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>27.5</v>
+        <v>17.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V13" s="13" t="n">
+      <c r="V13" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="X13" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="Y13" s="3" t="n">
@@ -1618,7 +1623,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>8600.4</v>
+        <v>260</v>
       </c>
       <c r="D14" s="12" t="n">
         <v>24.8</v>
@@ -1630,34 +1635,34 @@
         <v>21.1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>91.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>11.8</v>
+        <v>14.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="J14" s="3" t="n">
-        <v>18.2</v>
+      <c r="J14" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="N14" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="N14" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.59999999999999</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>21</v>
@@ -1665,14 +1670,14 @@
       <c r="R14" s="3" t="n">
         <v>20.5</v>
       </c>
-      <c r="S14" s="13" t="n">
+      <c r="S14" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>95.59999999999999</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>1.1</v>
+        <v>11.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>19.7</v>
@@ -1684,7 +1689,7 @@
         <v>22.5</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>9</v>
+        <v>97</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>0.7</v>
@@ -1703,25 +1708,25 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>934.8</v>
-      </c>
-      <c r="D15" s="3" t="n">
+        <v>234.8</v>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>28.3</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="F15" s="9" t="n">
-        <v>2.9</v>
+      <c r="F15" s="12" t="n">
+        <v>22.5</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>144.1</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>21.1</v>
+        <v>2.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
@@ -1733,7 +1738,7 @@
         <v>17.2</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>10.6</v>
+        <v>16.6</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>18.5</v>
@@ -1754,22 +1759,22 @@
         <v>21.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>995.3</v>
+        <v>59.3</v>
       </c>
       <c r="U15" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V15" s="13" t="n">
+      <c r="V15" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="X15" s="13" t="n">
-        <v>2.3</v>
+      <c r="X15" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>10</v>
@@ -1788,10 +1793,10 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>268.8</v>
+        <v>361.8</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>1428.1</v>
+        <v>14.6</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>82</v>
@@ -1800,61 +1805,59 @@
         <v>109.9</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>48.1</v>
+        <v>248.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>190.8</v>
+        <v>19</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>110.8</v>
       </c>
-      <c r="J16" s="3" t="n">
-        <v>114.9</v>
-      </c>
+      <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>98.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>88.8</v>
+        <v>68.8</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>85.3</v>
+        <v>83.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>95.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1465.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>10.9</v>
+        <v>16.9</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>16.9</v>
+        <v>7160.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>311.4</v>
+        <v>112.9</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>9920.799999999999</v>
+        <v>41.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>35.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="V16" s="3" t="n">
         <v>101.8</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>96.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>108.7</v>
+        <v>10.9</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>4658.4</v>
+        <v>458.4</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>10.4</v>
@@ -1875,54 +1878,54 @@
       <c r="C17" s="3" t="n">
         <v>312.4</v>
       </c>
-      <c r="D17" s="9" t="n">
-        <v>31.6</v>
+      <c r="D17" s="11" t="n">
+        <v>60.1</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>2011.7</v>
+        <v>17.1</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>20.9</v>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>28.1</v>
+        <v>481.6</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="M17" s="13" t="n">
+      <c r="M17" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="N17" s="13" t="n">
-        <v>19</v>
+      <c r="N17" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>93.2</v>
       </c>
-      <c r="P17" s="13" t="n">
-        <v>11.1</v>
+      <c r="P17" s="3" t="n">
+        <v>14.1</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="R17" s="13" t="n">
+      <c r="R17" s="8" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="S17" s="13" t="n">
+      <c r="S17" s="8" t="n">
         <v>29.8</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>788.4</v>
+        <v>188.7</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
@@ -1930,17 +1933,17 @@
       <c r="V17" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="8" t="n">
         <v>29.4</v>
       </c>
       <c r="X17" s="3" t="n">
         <v>21.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>91.5</v>
+        <v>21.5</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>21.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1956,61 +1959,61 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2954.6</v>
+        <v>254.6</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>24.8</v>
+        <v>27.7</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>17</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>13</v>
+        <v>22.4</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>3</v>
+        <v>50.6</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L18" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L18" s="8" t="n">
         <v>18.2</v>
       </c>
-      <c r="M18" s="13" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="N18" s="13" t="n">
-        <v>88.3</v>
+      <c r="M18" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>87.09999999999999</v>
-      </c>
-      <c r="P18" s="13" t="n">
-        <v>18.6</v>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S18" s="13" t="n">
-        <v>22.8</v>
+        <v>849.1</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="U18" s="13" t="n">
-        <v>4148.7</v>
+        <v>166.5</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>41.8</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>20.9</v>
@@ -2018,14 +2021,14 @@
       <c r="W18" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X18" s="13" t="n">
+      <c r="X18" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2041,46 +2044,46 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>119.4</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>41.4</v>
+        <v>19.4</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>27.4</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>16.2</v>
       </c>
-      <c r="F19" s="13" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>21.2</v>
+      <c r="F19" s="12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>11.2</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>14.6</v>
+        <v>12.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>25.3</v>
+        <v>2.3</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M19" s="13" t="n">
-        <v>87.40000000000001</v>
+      <c r="M19" s="3" t="n">
+        <v>27.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="P19" s="13" t="n">
-        <v>21.8</v>
+      <c r="P19" s="8" t="n">
+        <v>88.09999999999999</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>23.8</v>
@@ -2088,14 +2091,14 @@
       <c r="R19" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="S19" s="13" t="n">
-        <v>8</v>
+      <c r="S19" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="V19" s="3" t="n">
         <v>23.4</v>
@@ -2110,7 +2113,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>7.1</v>
+        <v>21.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2125,9 +2128,7 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>53.4</v>
-      </c>
+      <c r="C20" s="3" t="inlineStr"/>
       <c r="D20" s="12" t="n">
         <v>26.8</v>
       </c>
@@ -2138,7 +2139,7 @@
         <v>22.3</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>16</v>
@@ -2146,20 +2147,20 @@
       <c r="I20" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J20" s="13" t="n">
-        <v>21.9</v>
+      <c r="J20" s="3" t="n">
+        <v>91.09999999999999</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>8</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>18.2</v>
+        <v>49.1</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2173,12 +2174,10 @@
       <c r="R20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S20" s="13" t="n">
+      <c r="S20" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="T20" s="3" t="n">
-        <v>24</v>
-      </c>
+      <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
         <v>3.1</v>
       </c>
@@ -2211,7 +2210,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1824.6</v>
+        <v>1254.6</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>28</v>
@@ -2222,29 +2221,29 @@
       <c r="F21" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="G21" s="13" t="n">
-        <v>71.09999999999999</v>
+      <c r="G21" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L21" s="13" t="n">
-        <v>68</v>
+        <v>23.5</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="N21" s="13" t="n">
-        <v>28.9</v>
+      <c r="N21" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
@@ -2262,10 +2261,10 @@
         <v>28.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>22</v>
@@ -2311,28 +2310,28 @@
         <v>10.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>14.6</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>4.2</v>
+        <v>16.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="13" t="n">
+      <c r="L22" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>17.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>0.7</v>
@@ -2343,20 +2342,20 @@
       <c r="R22" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="S22" s="13" t="n">
+      <c r="S22" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="W22" s="13" t="n">
-        <v>219</v>
+        <v>23.1</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>19.6</v>
@@ -2365,7 +2364,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2380,17 +2379,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>21.6</v>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="12" t="n">
+        <v>137.5</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>12.1</v>
+      <c r="F23" s="12" t="n">
+        <v>111.3</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>92.59999999999999</v>
@@ -2402,54 +2399,52 @@
         <v>12.2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>129.9</v>
+        <v>129</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.6</v>
+        <v>60.6</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>907.6</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>81.8</v>
+        <v>81.2</v>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>269.1</v>
+        <v>46.9</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>62</v>
+        <v>6.5</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>18.8</v>
+        <v>24.8</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>8115.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>299.1</v>
+        <v>393.1</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>99.2</v>
+        <v>93.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>110</v>
+        <v>110.3</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>199.6</v>
+        <v>28.6</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>210</v>
+        <v>771.3</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>406.8</v>
-      </c>
-      <c r="Z23" s="3" t="n">
-        <v>122.9</v>
-      </c>
+        <v>41.6</v>
+      </c>
+      <c r="Z23" s="3" t="inlineStr"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2464,38 +2459,38 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2309.7</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>309.7</v>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>27.5</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F24" s="11" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>180.5</v>
-      </c>
-      <c r="H24" s="13" t="n">
+      <c r="F24" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H24" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I24" s="13" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="J24" s="3" t="n">
+      <c r="I24" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J24" s="8" t="n">
         <v>29.1</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="M24" s="13" t="n">
+      <c r="M24" s="8" t="n">
         <v>74.09999999999999</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>26.8</v>
+        <v>26.2</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>938.1</v>
@@ -2503,33 +2498,33 @@
       <c r="P24" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q24" s="13" t="n">
+      <c r="Q24" s="8" t="n">
         <v>39.1</v>
       </c>
-      <c r="R24" s="13" t="n">
+      <c r="R24" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="S24" s="13" t="n">
-        <v>32.1</v>
+      <c r="S24" s="3" t="n">
+        <v>23.2</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>18.2</v>
+        <v>874.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="X24" s="13" t="n">
-        <v>1183.4</v>
+        <v>19.9</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>21183.4</v>
       </c>
       <c r="Y24" s="3" t="inlineStr"/>
       <c r="Z24" s="3" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2556,41 +2551,33 @@
       <c r="F25" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H25" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>2.7</v>
-      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L25" s="13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L25" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="M25" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="N25" s="3" t="n">
-        <v>4.5</v>
-      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>94</v>
+        <v>9.4</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q25" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="Q25" s="8" t="n">
         <v>22.2</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>22.1</v>
@@ -2611,10 +2598,10 @@
         <v>18.8</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>6.3</v>
+        <v>16.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2630,7 +2617,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>341.4</v>
+        <v>371.4</v>
       </c>
       <c r="D26" s="12" t="n">
         <v>24.8</v>
@@ -2642,40 +2629,40 @@
         <v>20.3</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="I26" s="13" t="n">
-        <v>25.3</v>
+      <c r="I26" s="3" t="n">
+        <v>8.5</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>3.7</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L26" s="13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L26" s="3" t="n">
         <v>17</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="N26" s="13" t="n">
-        <v>82.8</v>
+      <c r="N26" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="R26" s="13" t="n">
-        <v>41.6</v>
+        <v>0.7</v>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>24.6</v>
@@ -2686,7 +2673,7 @@
       <c r="U26" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2730,7 +2717,7 @@
         <v>10.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>16</v>
+        <v>460.5</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2.5</v>
@@ -2739,37 +2726,33 @@
         <v>3.5</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="L27" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>25.1</v>
-      </c>
+        <v>16.1</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.3</v>
+        <v>11.3</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="S27" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="T27" s="3" t="n">
-        <v>636.4</v>
-      </c>
+      <c r="T27" s="3" t="inlineStr"/>
       <c r="U27" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>20.9</v>
@@ -2781,7 +2764,7 @@
         <v>20.8</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>838.6</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>14</v>
@@ -2812,37 +2795,37 @@
         <v>21.9</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H28" s="13" t="n">
-        <v>12.8</v>
+        <v>15.8</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>2.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>93.3</v>
+        <v>3.3</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>28.8</v>
+        <v>5.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>26.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="M28" s="13" t="n">
+      <c r="M28" s="3" t="n">
         <v>15</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>18</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>84</v>
+        <v>840.8</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>20.8</v>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>6.8</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>17.8</v>
@@ -2850,23 +2833,21 @@
       <c r="S28" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="T28" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>6.8</v>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="8" t="n">
+        <v>62.1</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>19</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>26.4</v>
+        <v>26.8</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>13.1</v>
+        <v>12.1</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>78.5</v>
+        <v>77.5</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>2</v>
@@ -2885,19 +2866,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>343.6</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>21.4</v>
+        <v>2343.6</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>10.14</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>14</v>
@@ -2909,16 +2890,18 @@
         <v>4.8</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="L29" s="13" t="n">
-        <v>16.6</v>
+        <v>0.9</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>46.6</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="n">
+        <v>86.5</v>
+      </c>
       <c r="P29" s="3" t="n">
         <v>2.6</v>
       </c>
@@ -2926,13 +2909,13 @@
         <v>22</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>19.7</v>
+        <v>12.7</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>81.5</v>
+        <v>21.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>4.8</v>
@@ -2943,8 +2926,8 @@
       <c r="W29" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X29" s="3" t="n">
-        <v>20.9</v>
+      <c r="X29" s="8" t="n">
+        <v>6.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>88</v>
@@ -2966,74 +2949,68 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>186.9</v>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>131.8</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>106.3</v>
+        <v>78.8</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr"/>
+      <c r="F30" s="11" t="n">
+        <v>60.9</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>700.9</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>119</v>
+        <v>19.3</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>17.9</v>
+        <v>7.9</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>893.9</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>81.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1424.9</v>
+        <v>0.4</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>8.9</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>111.2</v>
+        <v>42.8</v>
       </c>
       <c r="R30" s="3" t="inlineStr"/>
       <c r="S30" s="3" t="n">
-        <v>8109.4</v>
+        <v>2109.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>222.2</v>
+        <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>30.3</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>111.8</v>
+        <v>1681.8</v>
       </c>
       <c r="W30" s="3" t="n">
         <v>91.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>999.8</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>116.1</v>
-      </c>
+        <v>99.90000000000001</v>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
       <c r="Z30" s="3" t="n">
-        <v>120</v>
+        <v>0.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3051,62 +3028,62 @@
       <c r="C31" s="3" t="n">
         <v>2357.7</v>
       </c>
-      <c r="D31" s="12" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E31" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>21.3</v>
+      <c r="D31" s="11" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>21.5</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20.8</v>
+        <v>26.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>9.9</v>
+        <v>2.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L31" s="13" t="n">
-        <v>172.1</v>
-      </c>
-      <c r="M31" s="13" t="n">
-        <v>120810.1</v>
+        <v>1.4</v>
+      </c>
+      <c r="L31" s="8" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>21810.1</v>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
         <v>90.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>126.6</v>
-      </c>
-      <c r="S31" s="13" t="n">
-        <v>19.1</v>
+        <v>20</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>61.1</v>
+        <v>6.1</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="W31" s="13" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="W31" s="8" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3135,73 +3112,73 @@
         <v>266.6</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>17</v>
+        <v>26.3</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>17.1</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>21.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="H32" s="13" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="I32" s="13" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="J32" s="13" t="n">
-        <v>1.4</v>
+        <v>21</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>19.1</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="R32" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="S32" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X32" s="3" t="n">
         <v>18.9</v>
-      </c>
-      <c r="R32" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="S32" s="13" t="n">
-        <v>206.4</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W32" s="13" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X32" s="13" t="n">
-        <v>8.1</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>94</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>182</v>
+        <v>21.1</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3217,7 +3194,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1400.8</v>
+        <v>400.8</v>
       </c>
       <c r="D33" s="12" t="n">
         <v>27.2</v>
@@ -3235,11 +3212,9 @@
         <v>13.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>24.1</v>
-      </c>
+        <v>8.6</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
         <v>5.8</v>
       </c>
@@ -3247,19 +3222,19 @@
         <v>17.1</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>1.8</v>
+        <v>18.1</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>2.8</v>
+        <v>28.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="Q33" s="13" t="n">
-        <v>18.4</v>
+        <v>14.3</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>18.6</v>
@@ -3273,11 +3248,11 @@
       <c r="U33" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="V33" s="13" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="W33" s="13" t="n">
-        <v>88</v>
+      <c r="V33" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>12.7</v>
@@ -3286,7 +3261,7 @@
         <v>86.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>23.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3316,50 +3291,46 @@
       <c r="G34" s="12" t="n">
         <v>7.9</v>
       </c>
-      <c r="H34" s="13" t="n">
-        <v>15.6</v>
+      <c r="H34" s="8" t="n">
+        <v>65.59999999999999</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>39.7</v>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
       <c r="L34" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="M34" s="13" t="n">
+      <c r="M34" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="N34" s="13" t="n">
+      <c r="N34" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>91.8</v>
+        <v>98</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>23.3</v>
+        <v>0.7</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="S34" s="3" t="n">
-        <v>21.4</v>
-      </c>
+      <c r="S34" s="3" t="inlineStr"/>
       <c r="T34" s="3" t="n">
         <v>74.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>18.8</v>
@@ -3371,7 +3342,7 @@
         <v>84</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3408,7 +3379,7 @@
         <v>2</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
@@ -3417,13 +3388,13 @@
         <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>45</v>
+        <v>1.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>0.1</v>
+        <v>1.7</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>4</v>
@@ -3432,7 +3403,7 @@
         <v>22.8</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>21.1</v>
@@ -3441,7 +3412,7 @@
         <v>86</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.1</v>
@@ -3453,10 +3424,10 @@
         <v>21.1</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>89.2</v>
+        <v>89.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>244.1</v>
+        <v>21.1</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3487,13 +3458,13 @@
         <v>12.1</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>13.4</v>
+        <v>13.7</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>4</v>
@@ -3506,10 +3477,10 @@
       </c>
       <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>26.7</v>
@@ -3518,7 +3489,7 @@
         <v>20.8</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>60.2</v>
@@ -3526,11 +3497,11 @@
       <c r="U36" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V36" s="3" t="n">
-        <v>20.8</v>
+      <c r="V36" s="8" t="n">
+        <v>80.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>22.6</v>
@@ -3539,7 +3510,7 @@
         <v>95.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3555,13 +3526,13 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1640.2</v>
+        <v>1645.2</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>131.4</v>
-      </c>
-      <c r="E37" s="12" t="n">
-        <v>82.8</v>
+        <v>131.3</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>107.2</v>
@@ -3570,56 +3541,54 @@
         <v>48.5</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>10.6</v>
+        <v>710.6</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>106.7</v>
+        <v>116.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>1600.6</v>
+        <v>160.6</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="M37" s="3" t="n">
-        <v>11</v>
-      </c>
+      <c r="M37" s="3" t="inlineStr"/>
       <c r="N37" s="3" t="n">
-        <v>86</v>
+        <v>86.8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>298</v>
+        <v>228</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>180.8</v>
+        <v>120.8</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>122.9</v>
+        <v>1812.3</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>146.1</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>100.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>680.5</v>
+        <v>289.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>194.2</v>
+        <v>94.2</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>98.09999999999999</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>921.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>4481.7</v>
+        <v>418.8</v>
       </c>
       <c r="Z37" s="3" t="inlineStr"/>
       <c r="AA37" s="3" t="inlineStr">
@@ -3635,27 +3604,29 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr"/>
+      <c r="C38" s="3" t="n">
+        <v>1292.8</v>
+      </c>
       <c r="D38" s="12" t="n">
         <v>26.3</v>
       </c>
-      <c r="E38" s="12" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="F38" s="12" t="n">
+      <c r="E38" s="9" t="n">
+        <v>634.1</v>
+      </c>
+      <c r="F38" s="9" t="n">
         <v>21.4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="H38" s="13" t="n">
+        <v>97</v>
+      </c>
+      <c r="H38" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="J38" s="13" t="n">
-        <v>23.1</v>
+      <c r="J38" s="3" t="n">
+        <v>33.1</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0.4</v>
@@ -3673,32 +3644,30 @@
       <c r="P38" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q38" s="13" t="n">
-        <v>12.2</v>
+      <c r="Q38" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="R38" s="3" t="n">
-        <v>117.8</v>
-      </c>
-      <c r="S38" s="13" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S38" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>771.1</v>
-      </c>
-      <c r="U38" s="13" t="n">
-        <v>46.4</v>
-      </c>
+        <v>77.09999999999999</v>
+      </c>
+      <c r="U38" s="3" t="inlineStr"/>
       <c r="V38" s="3" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="X38" s="13" t="n">
-        <v>8.6</v>
+        <v>18.3</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>89.09999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="Z38" s="3" t="inlineStr"/>
       <c r="AA38" s="3" t="inlineStr">
@@ -3715,16 +3684,16 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>286.4</v>
+        <v>986.4</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="3" t="n">
         <v>15.8</v>
       </c>
-      <c r="F39" s="9" t="n">
-        <v>1.8</v>
+      <c r="F39" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="n">
@@ -3737,17 +3706,17 @@
         <v>3.8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="13" t="n">
-        <v>7.7</v>
+        <v>80</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>17.7</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>11.1</v>
+        <v>17.1</v>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>88.5</v>
+        <v>88</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>3.6</v>
@@ -3755,11 +3724,11 @@
       <c r="Q39" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="R39" s="13" t="n">
-        <v>20.9</v>
+      <c r="R39" s="8" t="n">
+        <v>22.2</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>74.40000000000001</v>
@@ -3788,7 +3757,7 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>5359</v>
+        <v>359</v>
       </c>
       <c r="D40" s="12" t="n">
         <v>27.5</v>
@@ -3800,16 +3769,18 @@
         <v>21.6</v>
       </c>
       <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="13" t="n">
+      <c r="H40" s="8" t="n">
         <v>13.8</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>85.90000000000001</v>
+        <v>2.9</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L40" s="3" t="n">
         <v>18</v>
       </c>
@@ -3820,10 +3791,10 @@
         <v>15.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>86.2</v>
+        <v>76.2</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q40" s="3" t="n">
         <v>25.8</v>
@@ -3835,13 +3806,13 @@
         <v>20.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="U40" s="3" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="U40" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>21.2</v>
+        <v>0.2</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>19.6</v>
@@ -3853,7 +3824,7 @@
         <v>86.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>32.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3869,44 +3840,44 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>8866.4</v>
-      </c>
-      <c r="D41" s="3" t="n">
+        <v>4866.4</v>
+      </c>
+      <c r="D41" s="9" t="n">
         <v>28.3</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="3" t="n">
         <v>17</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>0.2</v>
+        <v>31.8</v>
       </c>
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="3" t="n">
-        <v>22.1</v>
+        <v>2.1</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>16.3</v>
+        <v>6.3</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>27.7</v>
+        <v>17.7</v>
       </c>
       <c r="M41" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Q41" s="8" t="n">
         <v>26</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3948,7 +3919,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>942.6</v>
+        <v>242.6</v>
       </c>
       <c r="D42" s="12" t="n">
         <v>27.7</v>
@@ -3962,12 +3933,12 @@
       <c r="G42" s="12" t="n">
         <v>10.1</v>
       </c>
-      <c r="H42" s="13" t="n">
+      <c r="H42" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
@@ -3978,30 +3949,28 @@
       <c r="M42" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="N42" s="13" t="n">
+      <c r="N42" s="3" t="n">
         <v>16</v>
       </c>
       <c r="O42" s="3" t="n">
         <v>79.8</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="Q42" s="13" t="n">
-        <v>84.09999999999999</v>
+        <v>4.2</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="S42" s="13" t="n">
-        <v>29.9</v>
+        <v>20.2</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>89.90000000000001</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>55.5</v>
       </c>
-      <c r="U42" s="3" t="n">
-        <v>16.8</v>
-      </c>
+      <c r="U42" s="3" t="inlineStr"/>
       <c r="V42" s="3" t="n">
         <v>22.2</v>
       </c>
@@ -4009,10 +3978,10 @@
         <v>18.8</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>89.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>13.4</v>
+        <v>23.4</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>7.1</v>
@@ -4030,30 +3999,32 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="9" t="n">
-        <v>94.8</v>
+      <c r="C43" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="E43" s="9" t="n">
-        <v>10.9</v>
+        <v>30.9</v>
       </c>
       <c r="F43" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="G43" s="13" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="H43" s="13" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="I43" s="13" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="J43" s="13" t="n">
-        <v>26.1</v>
+      <c r="G43" s="3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>90.2</v>
@@ -4063,37 +4034,35 @@
       </c>
       <c r="N43" s="3" t="inlineStr"/>
       <c r="O43" s="3" t="n">
-        <v>105.5</v>
+        <v>405.5</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="Q43" s="13" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="R43" s="3" t="n">
-        <v>10.2</v>
+      <c r="Q43" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="R43" s="8" t="n">
+        <v>61.6</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>161.6</v>
+        <v>10.9</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>20</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="V43" s="13" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="V43" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="W43" s="13" t="n">
-        <v>19.3</v>
-      </c>
+      <c r="W43" s="3" t="inlineStr"/>
       <c r="X43" s="3" t="n">
-        <v>2011</v>
+        <v>20.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>406.7</v>
+        <v>12</v>
       </c>
       <c r="Z43" s="3" t="inlineStr"/>
       <c r="AA43" s="3" t="inlineStr">
@@ -4112,9 +4081,9 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="14" t="inlineStr"/>
-      <c r="E44" s="14" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
+      <c r="D44" s="15" t="inlineStr"/>
+      <c r="E44" s="15" t="inlineStr"/>
+      <c r="F44" s="15" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -4170,19 +4139,19 @@
         <v>9.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>11</v>
+        <v>2.7</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>81.09999999999999</v>
@@ -4191,10 +4160,10 @@
         <v>9.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>25.1</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>20.8</v>
+        <v>202.8</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>20.8</v>
@@ -4215,7 +4184,7 @@
         <v>20.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4232,26 +4201,26 @@
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="11" t="n">
         <v>0.8</v>
       </c>
       <c r="E46" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>11.4</v>
+      <c r="F46" s="11" t="n">
+        <v>0.8</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>11.4</v>
+        <v>17.1</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>1.4</v>
+        <v>10.4</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>11.4</v>
+        <v>4.6</v>
       </c>
       <c r="K46" s="3" t="n">
         <v>4.8</v>
@@ -4262,35 +4231,31 @@
       <c r="M46" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="N46" s="13" t="n">
-        <v>410.7</v>
+      <c r="N46" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>8.6</v>
+        <v>0.2</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
       <c r="R46" s="3" t="inlineStr"/>
       <c r="S46" s="3" t="inlineStr"/>
       <c r="T46" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="X46" s="3" t="inlineStr"/>
       <c r="Y46" s="3" t="inlineStr"/>
       <c r="Z46" s="3" t="inlineStr"/>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
@@ -816,7 +816,7 @@
       <c r="L4" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="12" t="n">
         <v>16.8</v>
       </c>
       <c r="N4" s="8" t="n">
@@ -828,22 +828,22 @@
       <c r="P4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V4" s="3" t="n">
+      <c r="S4" s="12" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="T4" s="12" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="U4" s="12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V4" s="9" t="n">
         <v>80.3</v>
       </c>
       <c r="W4" s="3" t="n">
@@ -901,7 +901,7 @@
       <c r="L5" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -913,20 +913,20 @@
       <c r="P5" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="12" t="n">
         <v>24.8</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="12" t="n">
         <v>21.3</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>81.09999999999999</v>
+      <c r="S5" s="12" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T5" s="12" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="U5" s="12" t="n">
+        <v>6</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>18</v>
@@ -984,7 +984,7 @@
       <c r="L6" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="12" t="n">
         <v>16.4</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -994,19 +994,19 @@
       <c r="P6" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="12" t="n">
         <v>26.8</v>
       </c>
-      <c r="R6" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="S6" s="3" t="n">
+      <c r="R6" s="12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="S6" s="12" t="n">
         <v>24.3</v>
       </c>
-      <c r="T6" s="3" t="n">
+      <c r="T6" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="U6" s="3" t="n">
+      <c r="U6" s="12" t="n">
         <v>10.9</v>
       </c>
       <c r="V6" s="3" t="n">
@@ -1067,7 +1067,7 @@
       <c r="L7" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1079,19 +1079,19 @@
       <c r="P7" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="12" t="n">
         <v>27.3</v>
       </c>
-      <c r="R7" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="S7" s="3" t="n">
+      <c r="R7" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="S7" s="12" t="n">
         <v>24.9</v>
       </c>
-      <c r="T7" s="3" t="n">
+      <c r="T7" s="12" t="n">
         <v>68.7</v>
       </c>
-      <c r="U7" s="3" t="n">
+      <c r="U7" s="12" t="n">
         <v>11.4</v>
       </c>
       <c r="V7" s="3" t="n">
@@ -1152,7 +1152,7 @@
       <c r="L8" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="12" t="n">
         <v>15.8</v>
       </c>
       <c r="N8" s="8" t="n">
@@ -1164,34 +1164,34 @@
       <c r="P8" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="12" t="n">
         <v>24.5</v>
       </c>
-      <c r="R8" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="S8" s="3" t="n">
+      <c r="R8" s="12" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="S8" s="12" t="n">
         <v>26.8</v>
       </c>
-      <c r="T8" s="3" t="n">
+      <c r="T8" s="12" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="U8" s="3" t="n">
+      <c r="U8" s="12" t="n">
         <v>3.9</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="12" t="n">
         <v>19.6</v>
       </c>
-      <c r="W8" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="X8" s="3" t="n">
+      <c r="W8" s="12" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X8" s="12" t="n">
         <v>19.7</v>
       </c>
-      <c r="Y8" s="3" t="n">
+      <c r="Y8" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="Z8" s="12" t="n">
         <v>3.2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1231,13 +1231,13 @@
       <c r="J9" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="11" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="12" t="n">
         <v>84.5</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1249,11 +1249,11 @@
       <c r="P9" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="12" t="n">
         <v>127.1</v>
       </c>
-      <c r="R9" s="3" t="n">
-        <v>91.2</v>
+      <c r="R9" s="12" t="n">
+        <v>106.9</v>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="n">
@@ -1262,10 +1262,10 @@
       <c r="U9" s="3" t="n">
         <v>38.5</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="11" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="11" t="n">
         <v>12.7</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1317,11 +1317,11 @@
       <c r="K10" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="M10" s="3" t="n">
-        <v>4.3</v>
+      <c r="M10" s="12" t="n">
+        <v>16.9</v>
       </c>
       <c r="N10" s="8" t="n">
         <v>687.8</v>
@@ -1332,10 +1332,10 @@
       <c r="P10" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="Q10" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R10" s="3" t="n">
+      <c r="Q10" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="R10" s="12" t="n">
         <v>22.1</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1347,10 +1347,10 @@
       <c r="U10" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="V10" s="8" t="n">
+      <c r="V10" s="11" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="W10" s="3" t="inlineStr"/>
+      <c r="W10" s="13" t="inlineStr"/>
       <c r="X10" s="3" t="n">
         <v>20.6</v>
       </c>
@@ -1400,7 +1400,7 @@
       <c r="K11" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="12" t="n">
         <v>17.2</v>
       </c>
       <c r="M11" s="3" t="n">
@@ -1415,22 +1415,22 @@
       <c r="P11" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="Q11" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="S11" s="8" t="n">
+      <c r="Q11" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="R11" s="12" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="S11" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="T11" s="3" t="n">
+      <c r="T11" s="12" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U11" s="8" t="n">
+      <c r="U11" s="12" t="n">
         <v>10.6</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="12" t="n">
         <v>21.8</v>
       </c>
       <c r="W11" s="8" t="n">
@@ -1485,7 +1485,7 @@
       <c r="K12" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="12" t="n">
         <v>18.4</v>
       </c>
       <c r="M12" s="3" t="n">
@@ -1500,7 +1500,7 @@
       <c r="P12" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="12" t="n">
         <v>20.3</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1515,7 +1515,7 @@
       <c r="U12" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="12" t="n">
         <v>21.5</v>
       </c>
       <c r="W12" s="3" t="n">
@@ -1568,7 +1568,7 @@
       <c r="K13" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="12" t="n">
         <v>17.7</v>
       </c>
       <c r="M13" s="3" t="n">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="12" t="n">
         <v>24.4</v>
       </c>
       <c r="R13" s="3" t="n">
@@ -1594,7 +1594,7 @@
       <c r="U13" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1649,7 +1649,7 @@
       <c r="K14" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="M14" s="3" t="n">
@@ -1664,7 +1664,7 @@
       <c r="P14" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="12" t="n">
         <v>21</v>
       </c>
       <c r="R14" s="3" t="n">
@@ -1679,19 +1679,19 @@
       <c r="U14" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="12" t="n">
         <v>19.7</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="12" t="n">
         <v>19.4</v>
       </c>
-      <c r="X14" s="3" t="n">
+      <c r="X14" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="Y14" s="3" t="n">
+      <c r="Y14" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="Z14" s="3" t="n">
+      <c r="Z14" s="12" t="n">
         <v>0.7</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -1734,22 +1734,22 @@
       <c r="K15" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="12" t="n">
         <v>17.2</v>
       </c>
-      <c r="M15" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N15" s="3" t="n">
+      <c r="M15" s="12" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N15" s="12" t="n">
         <v>18.5</v>
       </c>
-      <c r="O15" s="3" t="n">
+      <c r="O15" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="P15" s="3" t="n">
+      <c r="P15" s="12" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="12" t="n">
         <v>27.6</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1764,7 +1764,7 @@
       <c r="U15" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="12" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1814,13 +1814,13 @@
         <v>110.8</v>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="11" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="L16" s="3" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="M16" s="3" t="n">
+      <c r="L16" s="12" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="M16" s="11" t="n">
         <v>83.3</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1832,10 +1832,10 @@
       <c r="P16" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="Q16" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="R16" s="3" t="n">
+      <c r="Q16" s="12" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="R16" s="11" t="n">
         <v>7160.3</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1847,10 +1847,10 @@
       <c r="U16" s="3" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="V16" s="3" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="W16" s="3" t="n">
+      <c r="V16" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="W16" s="11" t="n">
         <v>86.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1900,10 +1900,10 @@
       <c r="K17" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="11" t="n">
         <v>17.8</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1915,10 +1915,10 @@
       <c r="P17" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="12" t="n">
         <v>23.9</v>
       </c>
-      <c r="R17" s="8" t="n">
+      <c r="R17" s="11" t="n">
         <v>69.09999999999999</v>
       </c>
       <c r="S17" s="8" t="n">
@@ -1930,10 +1930,10 @@
       <c r="U17" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="W17" s="8" t="n">
+      <c r="W17" s="11" t="n">
         <v>29.4</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -2003,8 +2003,8 @@
       <c r="Q18" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="R18" s="3" t="n">
-        <v>849.1</v>
+      <c r="R18" s="9" t="n">
+        <v>84.91</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>29.3</v>
@@ -2015,20 +2015,20 @@
       <c r="U18" s="8" t="n">
         <v>41.8</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="12" t="n">
         <v>20.9</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="12" t="n">
         <v>18.9</v>
       </c>
-      <c r="X18" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="Y18" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="Z18" s="3" t="n">
-        <v>4.1</v>
+      <c r="X18" s="12" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="Y18" s="12" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="Z18" s="12" t="n">
+        <v>2.9</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2100,20 +2100,20 @@
       <c r="U19" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="12" t="n">
         <v>23.4</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="12" t="n">
         <v>19.9</v>
       </c>
-      <c r="X19" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="Y19" s="3" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="Z19" s="3" t="n">
-        <v>21.6</v>
+      <c r="X19" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="Y19" s="12" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="Z19" s="12" t="n">
+        <v>5.5</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
       <c r="K20" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="9" t="n">
         <v>49.1</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2181,19 +2181,19 @@
       <c r="U20" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="12" t="n">
         <v>20.9</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X20" s="3" t="n">
+      <c r="W20" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="X20" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="Y20" s="3" t="n">
+      <c r="Y20" s="12" t="n">
         <v>93.8</v>
       </c>
-      <c r="Z20" s="3" t="n">
+      <c r="Z20" s="12" t="n">
         <v>1.5</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2266,19 +2266,19 @@
       <c r="U21" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="X21" s="3" t="n">
+      <c r="X21" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="Y21" s="3" t="n">
+      <c r="Y21" s="12" t="n">
         <v>96.8</v>
       </c>
-      <c r="Z21" s="3" t="n">
+      <c r="Z21" s="12" t="n">
         <v>0.8</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2321,19 +2321,19 @@
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="N22" s="3" t="n">
+      <c r="L22" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="M22" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N22" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="P22" s="12" t="n">
         <v>0.7</v>
       </c>
       <c r="Q22" s="3" t="n">
@@ -2351,19 +2351,19 @@
       <c r="U22" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="12" t="n">
         <v>23.1</v>
       </c>
-      <c r="W22" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="X22" s="3" t="n">
+      <c r="W22" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="X22" s="12" t="n">
         <v>19.6</v>
       </c>
-      <c r="Y22" s="3" t="n">
+      <c r="Y22" s="12" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="Z22" s="3" t="n">
+      <c r="Z22" s="12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -2401,13 +2401,13 @@
       <c r="J23" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="11" t="n">
         <v>60.6</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="11" t="n">
         <v>907.6</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="11" t="n">
         <v>81.2</v>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
@@ -2417,10 +2417,10 @@
       <c r="P23" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="11" t="n">
         <v>24.8</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2432,11 +2432,11 @@
       <c r="U23" s="3" t="n">
         <v>93.2</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="12" t="n">
         <v>110.3</v>
       </c>
-      <c r="W23" s="3" t="n">
-        <v>28.6</v>
+      <c r="W23" s="12" t="n">
+        <v>97.5</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>771.3</v>
@@ -2483,10 +2483,10 @@
         <v>29.1</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="11" t="n">
         <v>18.1</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="11" t="n">
         <v>74.09999999999999</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2498,10 +2498,10 @@
       <c r="P24" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q24" s="8" t="n">
+      <c r="Q24" s="11" t="n">
         <v>39.1</v>
       </c>
-      <c r="R24" s="8" t="n">
+      <c r="R24" s="11" t="n">
         <v>10.1</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2513,10 +2513,10 @@
       <c r="U24" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V24" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="W24" s="3" t="n">
+      <c r="V24" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W24" s="12" t="n">
         <v>19.9</v>
       </c>
       <c r="X24" s="8" t="n">
@@ -2563,7 +2563,7 @@
       <c r="L25" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="12" t="n">
         <v>18.2</v>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
@@ -2573,19 +2573,19 @@
       <c r="P25" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="Q25" s="8" t="n">
+      <c r="Q25" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="R25" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S25" s="3" t="n">
+      <c r="R25" s="12" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S25" s="12" t="n">
         <v>22.1</v>
       </c>
-      <c r="T25" s="3" t="n">
+      <c r="T25" s="12" t="n">
         <v>82.5</v>
       </c>
-      <c r="U25" s="3" t="n">
+      <c r="U25" s="12" t="n">
         <v>4.7</v>
       </c>
       <c r="V25" s="3" t="n">
@@ -2646,7 +2646,7 @@
       <c r="L26" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2658,19 +2658,19 @@
       <c r="P26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q26" s="8" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="S26" s="3" t="n">
+      <c r="Q26" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R26" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S26" s="12" t="n">
         <v>24.6</v>
       </c>
-      <c r="T26" s="3" t="n">
+      <c r="T26" s="12" t="n">
         <v>83.90000000000001</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" s="12" t="n">
         <v>4.7</v>
       </c>
       <c r="V26" s="8" t="n">
@@ -2731,7 +2731,7 @@
       <c r="L27" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="12" t="n">
         <v>16.1</v>
       </c>
       <c r="N27" s="3" t="inlineStr"/>
@@ -2812,7 +2812,7 @@
       <c r="L28" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="12" t="n">
         <v>15</v>
       </c>
       <c r="N28" s="3" t="n">
@@ -2892,10 +2892,10 @@
       <c r="K29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="9" t="n">
         <v>46.6</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
@@ -2968,13 +2968,13 @@
       <c r="J30" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="11" t="n">
         <v>7.9</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="11" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="12" t="n">
         <v>81.2</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2986,10 +2986,10 @@
       <c r="P30" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="11" t="n">
         <v>42.8</v>
       </c>
-      <c r="R30" s="3" t="inlineStr"/>
+      <c r="R30" s="13" t="inlineStr"/>
       <c r="S30" s="3" t="n">
         <v>2109.4</v>
       </c>
@@ -2999,10 +2999,10 @@
       <c r="U30" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="11" t="n">
         <v>1681.8</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="11" t="n">
         <v>91.8</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3052,11 +3052,11 @@
       <c r="K31" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="11" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="M31" s="8" t="n">
-        <v>21810.1</v>
+      <c r="M31" s="12" t="n">
+        <v>16.2</v>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
@@ -3065,25 +3065,25 @@
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="R31" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="S31" s="3" t="n">
+      <c r="R31" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="S31" s="12" t="n">
         <v>21.9</v>
       </c>
-      <c r="T31" s="3" t="n">
+      <c r="T31" s="12" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="U31" s="3" t="n">
+      <c r="U31" s="12" t="n">
         <v>6.1</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="11" t="n">
         <v>16.4</v>
       </c>
-      <c r="W31" s="8" t="n">
+      <c r="W31" s="11" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3135,7 +3135,7 @@
       <c r="K32" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="M32" s="3" t="n">
@@ -3218,7 +3218,7 @@
       <c r="K33" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="12" t="n">
         <v>17.1</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3300,8 +3300,8 @@
       <c r="J34" s="3" t="n">
         <v>39.7</v>
       </c>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="n">
+      <c r="K34" s="15" t="inlineStr"/>
+      <c r="L34" s="12" t="n">
         <v>17.5</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3316,7 +3316,7 @@
       <c r="P34" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="9" t="n">
         <v>0.7</v>
       </c>
       <c r="R34" s="3" t="n">
@@ -3384,7 +3384,7 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="M35" s="3" t="n">
@@ -3469,7 +3469,7 @@
       <c r="K36" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="12" t="n">
         <v>17.1</v>
       </c>
       <c r="M36" s="3" t="n">
@@ -3482,22 +3482,22 @@
       <c r="P36" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="12" t="n">
         <v>26.7</v>
       </c>
-      <c r="R36" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S36" s="3" t="n">
+      <c r="R36" s="12" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="S36" s="12" t="n">
         <v>21.1</v>
       </c>
-      <c r="T36" s="3" t="n">
+      <c r="T36" s="12" t="n">
         <v>60.2</v>
       </c>
-      <c r="U36" s="3" t="n">
+      <c r="U36" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="V36" s="8" t="n">
+      <c r="V36" s="9" t="n">
         <v>80.8</v>
       </c>
       <c r="W36" s="3" t="n">
@@ -3549,13 +3549,13 @@
       <c r="J37" s="3" t="n">
         <v>116.7</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="11" t="n">
         <v>160.6</v>
       </c>
-      <c r="L37" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr"/>
+      <c r="L37" s="12" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="M37" s="13" t="inlineStr"/>
       <c r="N37" s="3" t="n">
         <v>86.8</v>
       </c>
@@ -3565,10 +3565,10 @@
       <c r="P37" s="3" t="n">
         <v>120.8</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="11" t="n">
         <v>1812.3</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="11" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3580,10 +3580,10 @@
       <c r="U37" s="3" t="n">
         <v>94.2</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="11" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="11" t="n">
         <v>91.40000000000001</v>
       </c>
       <c r="X37" s="3" t="inlineStr"/>
@@ -3631,7 +3631,7 @@
       <c r="K38" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="12" t="n">
         <v>17.7</v>
       </c>
       <c r="M38" s="3" t="n">
@@ -3644,10 +3644,10 @@
       <c r="P38" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="Q38" s="3" t="n">
+      <c r="Q38" s="11" t="n">
         <v>0.8</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="11" t="n">
         <v>19.1</v>
       </c>
       <c r="S38" s="8" t="n">
@@ -3657,10 +3657,10 @@
         <v>77.09999999999999</v>
       </c>
       <c r="U38" s="3" t="inlineStr"/>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="11" t="n">
         <v>18.3</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3811,7 +3811,7 @@
       <c r="U40" s="8" t="n">
         <v>12.8</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3877,25 +3877,25 @@
       <c r="P41" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q41" s="8" t="n">
+      <c r="Q41" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="R41" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S41" s="3" t="n">
+      <c r="R41" s="12" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S41" s="12" t="n">
         <v>19.5</v>
       </c>
-      <c r="T41" s="3" t="n">
+      <c r="T41" s="12" t="n">
         <v>57.9</v>
       </c>
-      <c r="U41" s="3" t="n">
+      <c r="U41" s="12" t="n">
         <v>14.1</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="W41" s="3" t="inlineStr"/>
+      <c r="W41" s="15" t="inlineStr"/>
       <c r="X41" s="3" t="n">
         <v>20.2</v>
       </c>
@@ -4026,10 +4026,10 @@
       <c r="K43" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="9" t="n">
         <v>90.2</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="9" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="N43" s="3" t="inlineStr"/>
@@ -4042,7 +4042,7 @@
       <c r="Q43" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="9" t="n">
         <v>61.6</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4054,10 +4054,10 @@
       <c r="U43" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="V43" s="8" t="n">
+      <c r="V43" s="9" t="n">
         <v>4.8</v>
       </c>
-      <c r="W43" s="3" t="inlineStr"/>
+      <c r="W43" s="15" t="inlineStr"/>
       <c r="X43" s="3" t="n">
         <v>20.8</v>
       </c>
@@ -4088,19 +4088,19 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
+      <c r="K44" s="15" t="inlineStr"/>
+      <c r="L44" s="15" t="inlineStr"/>
+      <c r="M44" s="15" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="Q44" s="15" t="inlineStr"/>
+      <c r="R44" s="15" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="15" t="inlineStr"/>
+      <c r="W44" s="15" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4141,13 +4141,13 @@
       <c r="J45" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="11" t="n">
         <v>2.7</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="11" t="n">
         <v>15.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4159,10 +4159,10 @@
       <c r="P45" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="11" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="11" t="n">
         <v>202.8</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4174,10 +4174,10 @@
       <c r="U45" s="3" t="n">
         <v>11.1</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="11" t="n">
         <v>18.7</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4225,10 +4225,10 @@
       <c r="K46" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="M46" s="3" t="n">
+      <c r="M46" s="11" t="n">
         <v>15.9</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4240,8 +4240,8 @@
       <c r="P46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
+      <c r="Q46" s="13" t="inlineStr"/>
+      <c r="R46" s="13" t="inlineStr"/>
       <c r="S46" s="3" t="inlineStr"/>
       <c r="T46" s="3" t="n">
         <v>0.1</v>
@@ -4249,10 +4249,10 @@
       <c r="U46" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="11" t="n">
         <v>1.6</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="X46" s="3" t="inlineStr"/>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
@@ -152,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,10 +167,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -789,17 +789,17 @@
       <c r="C4" s="3" t="n">
         <v>389.8</v>
       </c>
-      <c r="D4" s="12" t="n">
-        <v>28.4</v>
+      <c r="D4" s="9" t="n">
+        <v>38.3</v>
       </c>
       <c r="E4" s="12" t="n">
         <v>15.8</v>
       </c>
-      <c r="F4" s="12" t="n">
-        <v>22.1</v>
+      <c r="F4" s="3" t="n">
+        <v>28.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>82.5</v>
+        <v>12.5</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>12.5</v>
@@ -813,50 +813,50 @@
       <c r="K4" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="12" t="n">
         <v>17.9</v>
       </c>
       <c r="M4" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" s="12" t="n">
+      <c r="N4" s="12" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="O4" s="12" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="P4" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q4" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="R4" s="12" t="n">
         <v>21.8</v>
       </c>
-      <c r="S4" s="12" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="T4" s="12" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="U4" s="12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V4" s="9" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="W4" s="3" t="n">
+      <c r="S4" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="V4" s="12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="W4" s="12" t="n">
         <v>18.7</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>33.6</v>
+      <c r="X4" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Y4" s="12" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="Z4" s="12" t="n">
+        <v>2.3</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>9432.6</v>
+        <v>438.6</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>40.1</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E5" s="12" t="n">
         <v>16.9</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>21.1</v>
+      <c r="F5" s="9" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H5" s="13" t="n">
+        <v>121</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>2.8</v>
@@ -895,52 +895,54 @@
       <c r="J5" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K5" s="8" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="L5" s="3" t="n">
+      <c r="K5" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L5" s="12" t="n">
         <v>18.3</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>17.6</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q5" s="12" t="n">
+      <c r="N5" s="12" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="O5" s="12" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="P5" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="R5" s="12" t="n">
         <v>21.3</v>
       </c>
-      <c r="S5" s="12" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="T5" s="12" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="U5" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V5" s="3" t="n">
+      <c r="S5" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V5" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="12" t="n">
         <v>17.2</v>
       </c>
-      <c r="X5" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="Y5" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="X5" s="12" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Y5" s="12" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="Z5" s="12" t="n">
+        <v>1</v>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>2</t>
@@ -955,7 +957,7 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>484.4</v>
+        <v>494.4</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>28.8</v>
@@ -969,29 +971,31 @@
       <c r="G6" s="12" t="n">
         <v>11.9</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>15.2</v>
+      <c r="H6" s="13" t="n">
+        <v>25.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>3.8</v>
+        <v>13.8</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L6" s="12" t="n">
         <v>17.2</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="N6" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O6" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="P6" s="12" t="n">
         <v>1.6</v>
       </c>
       <c r="Q6" s="12" t="n">
@@ -1009,20 +1013,20 @@
       <c r="U6" s="12" t="n">
         <v>10.9</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="12" t="n">
         <v>20.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="12" t="n">
         <v>19.2</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="Y6" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>1.6</v>
+      <c r="X6" s="12" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="Y6" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="Z6" s="12" t="n">
+        <v>1.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1044,10 +1048,10 @@
         <v>28.2</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>12</v>
@@ -1056,7 +1060,7 @@
         <v>12.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.8</v>
@@ -1064,50 +1068,50 @@
       <c r="K7" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>17.9</v>
       </c>
-      <c r="N7" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O7" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" s="12" t="n">
+      <c r="N7" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="O7" s="12" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="P7" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q7" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="S7" s="12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="T7" s="12" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="U7" s="12" t="n">
+      <c r="T7" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="12" t="n">
         <v>20.8</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="12" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>2.1</v>
+      <c r="X7" s="12" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="Y7" s="12" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="Z7" s="12" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1123,7 +1127,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>260.2</v>
+        <v>460.2</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>28.4</v>
@@ -1149,20 +1153,20 @@
       <c r="K8" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>15.8</v>
       </c>
-      <c r="N8" s="8" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>12.2</v>
+      <c r="N8" s="12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O8" s="12" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="P8" s="12" t="n">
+        <v>1.4</v>
       </c>
       <c r="Q8" s="12" t="n">
         <v>24.5</v>
@@ -1183,16 +1187,16 @@
         <v>19.6</v>
       </c>
       <c r="W8" s="12" t="n">
-        <v>17.3</v>
+        <v>18</v>
       </c>
       <c r="X8" s="12" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>86</v>
+        <v>90.5</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1208,22 +1212,22 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3440.5</v>
+        <v>2240.4</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>1824.8</v>
+        <v>142</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>12.4</v>
       </c>
-      <c r="G9" s="3" t="n">
-        <v>99.09999999999999</v>
+      <c r="G9" s="9" t="n">
+        <v>25.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>61.8</v>
+        <v>671.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.2</v>
@@ -1234,48 +1238,48 @@
       <c r="K9" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="L9" s="11" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="M9" s="12" t="n">
+      <c r="L9" s="12" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="M9" s="11" t="n">
         <v>84.5</v>
       </c>
-      <c r="N9" s="3" t="n">
-        <v>12.3</v>
-      </c>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>22.1</v>
+        <v>343.3</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q9" s="12" t="n">
-        <v>127.1</v>
-      </c>
-      <c r="R9" s="12" t="n">
-        <v>106.9</v>
-      </c>
-      <c r="S9" s="3" t="inlineStr"/>
+      <c r="Q9" s="11" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="R9" s="11" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>124.3</v>
+      </c>
       <c r="T9" s="3" t="n">
         <v>384.2</v>
       </c>
       <c r="U9" s="3" t="n">
         <v>38.5</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" s="12" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="W9" s="11" t="n">
+      <c r="W9" s="12" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>445.1</v>
+      </c>
+      <c r="Z9" s="3" t="n">
         <v>12.7</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>162.8</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>445.8</v>
-      </c>
-      <c r="Z9" s="3" t="n">
-        <v>122.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1294,71 +1298,73 @@
         <v>428.1</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="E10" s="9" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E10" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="F10" s="9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I10" s="8" t="n">
+      <c r="F10" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I10" s="3" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>19.9</v>
+        <v>1.1</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>17.9</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>16.9</v>
       </c>
-      <c r="N10" s="8" t="n">
-        <v>687.8</v>
-      </c>
-      <c r="O10" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q10" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="R10" s="12" t="n">
-        <v>22.1</v>
+      <c r="N10" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O10" s="12" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="P10" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q10" s="11" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="R10" s="11" t="n">
+        <v>21.7</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>24.9</v>
+        <v>1041.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="V10" s="11" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="W10" s="13" t="inlineStr"/>
-      <c r="X10" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>2.5</v>
+      <c r="V10" s="12" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="W10" s="12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="X10" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="Y10" s="12" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="Z10" s="12" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1376,45 +1382,41 @@
       <c r="C11" s="3" t="n">
         <v>299.6</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="12" t="n">
         <v>26.5</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>28.7</v>
+      <c r="E11" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>21.7</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L11" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K11" s="15" t="inlineStr"/>
+      <c r="L11" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="12" t="n">
         <v>17</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>41.4</v>
+        <v>8.5</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P11" s="3" t="n">
-        <v>8.4</v>
-      </c>
+      <c r="P11" s="3" t="inlineStr"/>
       <c r="Q11" s="12" t="n">
         <v>26</v>
       </c>
@@ -1431,13 +1433,13 @@
         <v>10.6</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="W11" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W11" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="X11" s="3" t="n">
-        <v>82</v>
+      <c r="X11" s="13" t="n">
+        <v>822</v>
       </c>
       <c r="Y11" s="3" t="n">
         <v>84.5</v>
@@ -1462,13 +1464,13 @@
         <v>343.6</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>9.1</v>
@@ -1480,22 +1482,22 @@
         <v>2.4</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M12" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="M12" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.6</v>
@@ -1503,31 +1505,31 @@
       <c r="Q12" s="12" t="n">
         <v>20.3</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="12" t="n">
         <v>19.5</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>923</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>1.6</v>
+      <c r="S12" s="12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T12" s="12" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="U12" s="12" t="n">
+        <v>1.2</v>
       </c>
       <c r="V12" s="12" t="n">
         <v>21.5</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="Y12" s="3" t="n">
+      <c r="W12" s="12" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="X12" s="12" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="Y12" s="12" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="Z12" s="3" t="n">
+      <c r="Z12" s="12" t="n">
         <v>2.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -1544,13 +1546,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2323.8</v>
+        <v>323.8</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>27.5</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>22.3</v>
@@ -1561,46 +1563,50 @@
       <c r="H13" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I13" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="13" t="n">
+        <v>21</v>
+      </c>
       <c r="K13" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="L13" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="12" t="n">
         <v>16.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Q13" s="12" t="n">
         <v>24.4</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="12" t="n">
         <v>21.4</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>16.8</v>
+      <c r="S13" s="12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="T13" s="12" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="U13" s="12" t="n">
+        <v>5.1</v>
       </c>
       <c r="V13" s="12" t="n">
         <v>19.8</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="X13" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X13" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="Y13" s="3" t="n">
@@ -1634,29 +1640,27 @@
       <c r="F14" s="12" t="n">
         <v>21.1</v>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>98.40000000000001</v>
+      <c r="G14" s="12" t="n">
+        <v>7.4</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I14" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>22.2</v>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="L14" s="3" t="n">
         <v>18.3</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="12" t="n">
         <v>17.2</v>
       </c>
-      <c r="N14" s="8" t="n">
-        <v>18.9</v>
+      <c r="N14" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>89.59999999999999</v>
@@ -1667,17 +1671,17 @@
       <c r="Q14" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="S14" s="8" t="n">
+      <c r="R14" s="12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="S14" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="T14" s="3" t="n">
+      <c r="T14" s="12" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>11.1</v>
+      <c r="U14" s="12" t="n">
+        <v>1.1</v>
       </c>
       <c r="V14" s="12" t="n">
         <v>19.7</v>
@@ -1686,10 +1690,10 @@
         <v>19.4</v>
       </c>
       <c r="X14" s="12" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>97</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z14" s="12" t="n">
         <v>0.7</v>
@@ -1708,7 +1712,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>234.8</v>
+        <v>334.8</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>28.3</v>
@@ -1719,50 +1723,50 @@
       <c r="F15" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="G15" s="3" t="n">
-        <v>18.7</v>
+      <c r="G15" s="12" t="n">
+        <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>144.1</v>
+        <v>14.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="L15" s="12" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="O15" s="12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="O15" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="P15" s="12" t="n">
+      <c r="P15" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q15" s="12" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="R15" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R15" s="12" t="n">
         <v>21.4</v>
       </c>
-      <c r="S15" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="T15" s="3" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>16</v>
+      <c r="S15" s="12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="T15" s="12" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="U15" s="12" t="n">
+        <v>13.7</v>
       </c>
       <c r="V15" s="12" t="n">
         <v>19.2</v>
@@ -1777,7 +1781,7 @@
         <v>21</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1793,75 +1797,75 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>361.8</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>82</v>
-      </c>
-      <c r="F16" s="11" t="n">
+        <v>1361.8</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="F16" s="12" t="n">
         <v>109.9</v>
       </c>
-      <c r="G16" s="9" t="n">
-        <v>248.1</v>
+      <c r="G16" s="12" t="n">
+        <v>48.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>110.8</v>
       </c>
-      <c r="J16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="K16" s="11" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="L16" s="12" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="L16" s="11" t="n">
         <v>88.8</v>
       </c>
-      <c r="M16" s="11" t="n">
-        <v>83.3</v>
+      <c r="M16" s="12" t="n">
+        <v>85.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>95</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>1465.9</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6.9</v>
       </c>
       <c r="Q16" s="12" t="n">
-        <v>119.3</v>
+        <v>120.3</v>
       </c>
       <c r="R16" s="11" t="n">
-        <v>7160.3</v>
+        <v>104.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>112.9</v>
+        <v>2116.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>41.5</v>
+        <v>199.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>35.1</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>102</v>
+        <v>101.9</v>
       </c>
       <c r="W16" s="11" t="n">
-        <v>86.90000000000001</v>
+        <v>969.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>10.9</v>
+        <v>98.7</v>
       </c>
       <c r="Y16" s="3" t="n">
         <v>458.4</v>
       </c>
-      <c r="Z16" s="3" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1876,56 +1880,58 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>312.4</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="E17" s="11" t="n">
+        <v>2312.4</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E17" s="12" t="n">
         <v>17.1</v>
       </c>
-      <c r="F17" s="11" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
+      <c r="F17" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>29.7</v>
+      </c>
       <c r="H17" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>481.6</v>
+        <v>2.2</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L17" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L17" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="M17" s="11" t="n">
-        <v>17.8</v>
+      <c r="M17" s="12" t="n">
+        <v>17.1</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>19.8</v>
+        <v>1.9</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>14.1</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="R17" s="11" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>29.8</v>
+        <v>20.5</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>188.7</v>
+        <v>789.1</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
@@ -1934,13 +1940,13 @@
         <v>20.4</v>
       </c>
       <c r="W17" s="11" t="n">
-        <v>29.4</v>
+        <v>15.4</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>21.5</v>
+        <v>2812.1</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>2.1</v>
@@ -1959,7 +1965,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>254.6</v>
+        <v>354.6</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>27.7</v>
@@ -1970,29 +1976,29 @@
       <c r="F18" s="12" t="n">
         <v>22.4</v>
       </c>
-      <c r="G18" s="8" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="H18" s="8" t="n">
+      <c r="G18" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H18" s="13" t="n">
         <v>15</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>50.6</v>
+        <v>3</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L18" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="L18" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>81.09999999999999</v>
@@ -2001,10 +2007,10 @@
         <v>20.7</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="R18" s="9" t="n">
-        <v>84.91</v>
+        <v>9.6</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>29.3</v>
@@ -2012,23 +2018,23 @@
       <c r="T18" s="3" t="n">
         <v>166.5</v>
       </c>
-      <c r="U18" s="8" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="V18" s="12" t="n">
+      <c r="U18" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V18" s="9" t="n">
+        <v>224.884</v>
+      </c>
+      <c r="W18" s="9" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="X18" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="W18" s="12" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X18" s="12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="Y18" s="12" t="n">
-        <v>88.3</v>
-      </c>
-      <c r="Z18" s="12" t="n">
-        <v>2.9</v>
+      <c r="Y18" s="3" t="n">
+        <v>118.9</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2044,7 +2050,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>19.4</v>
+        <v>219.4</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>27.4</v>
@@ -2059,61 +2065,61 @@
         <v>11.2</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>12.6</v>
+        <v>14.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>22.8</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2.3</v>
+        <v>22.3</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>27.4</v>
+      <c r="M19" s="9" t="n">
+        <v>87.40000000000001</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>13.5</v>
+        <v>1.8</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="P19" s="8" t="n">
-        <v>88.09999999999999</v>
+      <c r="P19" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
+      </c>
+      <c r="S19" s="13" t="n">
+        <v>8.6</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V19" s="12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="V19" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="W19" s="12" t="n">
+      <c r="W19" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="X19" s="12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="Y19" s="12" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="Z19" s="12" t="n">
-        <v>5.5</v>
+      <c r="X19" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>7.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2128,7 +2134,9 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>358.8</v>
+      </c>
       <c r="D20" s="12" t="n">
         <v>26.8</v>
       </c>
@@ -2145,22 +2153,22 @@
         <v>16</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.9</v>
+        <v>19.4</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L20" s="9" t="n">
-        <v>49.1</v>
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>22.3</v>
+        <v>2.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2174,10 +2182,12 @@
       <c r="R20" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="S20" s="3" t="n">
+      <c r="S20" s="13" t="n">
         <v>24.7</v>
       </c>
-      <c r="T20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="n">
+        <v>1891.8</v>
+      </c>
       <c r="U20" s="3" t="n">
         <v>3.1</v>
       </c>
@@ -2210,7 +2220,7 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1254.6</v>
+        <v>2284.2</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>28</v>
@@ -2221,20 +2231,20 @@
       <c r="F21" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>17.1</v>
+      <c r="G21" s="13" t="n">
+        <v>71.8</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>84</v>
+        <v>8</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>28</v>
+        <v>12.5</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>23.5</v>
+        <v>3.5</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18</v>
@@ -2242,8 +2252,8 @@
       <c r="M21" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="N21" s="8" t="n">
-        <v>28</v>
+      <c r="N21" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
@@ -2251,9 +2261,7 @@
       <c r="P21" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="Q21" s="3" t="n">
-        <v>20.9</v>
-      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="3" t="n">
         <v>19.9</v>
       </c>
@@ -2261,10 +2269,10 @@
         <v>28.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>96.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="V21" s="12" t="n">
         <v>22</v>
@@ -2297,14 +2305,14 @@
       <c r="C22" s="3" t="n">
         <v>339.2</v>
       </c>
-      <c r="D22" s="12" t="n">
-        <v>27.6</v>
+      <c r="D22" s="9" t="n">
+        <v>97.59999999999999</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>22.3</v>
+      <c r="F22" s="9" t="n">
+        <v>92.3</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>10.6</v>
@@ -2316,24 +2324,24 @@
         <v>2.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>16.2</v>
+        <v>14.2</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N22" s="12" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="O22" s="12" t="n">
+      <c r="L22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O22" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="P22" s="12" t="n">
+      <c r="P22" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="Q22" s="3" t="n">
@@ -2346,7 +2354,7 @@
         <v>23.6</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>14</v>
+        <v>724</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>8.300000000000001</v>
@@ -2364,7 +2372,7 @@
         <v>69.09999999999999</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2379,72 +2387,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="12" t="n">
-        <v>137.5</v>
+      <c r="C23" s="3" t="n">
+        <v>1542.6</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>137.6</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="F23" s="12" t="n">
-        <v>111.3</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>92.59999999999999</v>
+      <c r="F23" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>35.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>14.2</v>
+        <v>74.8</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>129</v>
+        <v>119.3</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>60.6</v>
+        <v>6.6</v>
       </c>
       <c r="L23" s="11" t="n">
-        <v>907.6</v>
+        <v>0.9</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>87.8</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O23" s="3" t="n">
         <v>46.9</v>
       </c>
-      <c r="P23" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Q23" s="11" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="R23" s="11" t="n">
-        <v>24.8</v>
-      </c>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="14" t="inlineStr"/>
+      <c r="R23" s="14" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>8115.8</v>
+        <v>215.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>393.1</v>
+        <v>293.1</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="V23" s="12" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="V23" s="11" t="n">
         <v>110.3</v>
       </c>
-      <c r="W23" s="12" t="n">
-        <v>97.5</v>
+      <c r="W23" s="11" t="n">
+        <v>99.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>771.3</v>
+        <v>110.9</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="Z23" s="3" t="inlineStr"/>
+        <v>606.8</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2461,70 +2469,74 @@
       <c r="C24" s="3" t="n">
         <v>309.7</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="D24" s="9" t="n">
         <v>27.5</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G24" s="8" t="n">
+      <c r="F24" s="9" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="G24" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H24" s="3" t="n">
-        <v>14.8</v>
+      <c r="H24" s="13" t="n">
+        <v>184.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="11" t="n">
-        <v>18.1</v>
+        <v>9.4</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>48.1</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>74.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>26.2</v>
+        <v>1.6</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>938.1</v>
+        <v>93.8</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" s="13" t="n">
         <v>39.1</v>
       </c>
-      <c r="R24" s="11" t="n">
+      <c r="R24" s="13" t="n">
         <v>10.1</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>874.6</v>
+        <v>78.7</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V24" s="12" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W24" s="12" t="n">
+      <c r="V24" s="11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W24" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="X24" s="8" t="n">
-        <v>21183.4</v>
-      </c>
-      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="X24" s="13" t="n">
+        <v>8181.1</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>82.40000000000001</v>
+      </c>
       <c r="Z24" s="3" t="n">
-        <v>1.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2540,7 +2552,7 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>279.8</v>
+        <v>479.9</v>
       </c>
       <c r="D25" s="12" t="n">
         <v>24.8</v>
@@ -2551,57 +2563,61 @@
       <c r="F25" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G25" s="3" t="inlineStr"/>
+      <c r="G25" s="12" t="n">
+        <v>7.5</v>
+      </c>
       <c r="H25" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L25" s="8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L25" s="13" t="n">
         <v>18.8</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>18.2</v>
       </c>
-      <c r="N25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="O25" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>11.1</v>
+        <v>1.2</v>
       </c>
       <c r="Q25" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="R25" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S25" s="12" t="n">
+      <c r="R25" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="T25" s="12" t="n">
+      <c r="T25" s="3" t="n">
         <v>82.5</v>
       </c>
-      <c r="U25" s="12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V25" s="3" t="n">
+      <c r="U25" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="V25" s="13" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="W25" s="9" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="X25" s="13" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="Y25" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="Z25" s="3" t="n">
         <v>18</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>16.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2617,7 +2633,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>371.4</v>
+        <v>341.1</v>
       </c>
       <c r="D26" s="12" t="n">
         <v>24.8</v>
@@ -2628,20 +2644,20 @@
       <c r="F26" s="12" t="n">
         <v>20.3</v>
       </c>
-      <c r="G26" s="12" t="n">
-        <v>9</v>
+      <c r="G26" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>22.9</v>
+        <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>8.5</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>17</v>
@@ -2650,7 +2666,7 @@
         <v>16.7</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>12.8</v>
+        <v>1.1</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>97</v>
@@ -2673,19 +2689,19 @@
       <c r="U26" s="12" t="n">
         <v>4.7</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="12" t="n">
         <v>20.6</v>
       </c>
-      <c r="W26" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="Y26" s="3" t="n">
+      <c r="W26" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X26" s="12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="Y26" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="Z26" s="3" t="n">
+      <c r="Z26" s="12" t="n">
         <v>1.9</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -2705,19 +2721,19 @@
         <v>370</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>10.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>460.5</v>
+        <v>16</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>2.5</v>
@@ -2726,32 +2742,36 @@
         <v>3.5</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="L27" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L27" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>16.1</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O27" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="Q27" s="3" t="n">
+      <c r="Q27" s="12" t="n">
         <v>25.5</v>
       </c>
-      <c r="R27" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="T27" s="3" t="inlineStr"/>
-      <c r="U27" s="3" t="n">
+      <c r="R27" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="S27" s="12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="T27" s="12" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="U27" s="12" t="n">
         <v>9.9</v>
       </c>
       <c r="V27" s="3" t="n">
@@ -2760,11 +2780,11 @@
       <c r="W27" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X27" s="3" t="n">
-        <v>20.8</v>
+      <c r="X27" s="13" t="n">
+        <v>20.7</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>838.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
         <v>14</v>
@@ -2783,7 +2803,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>453.6</v>
+        <v>45.3</v>
       </c>
       <c r="D28" s="12" t="n">
         <v>28.8</v>
@@ -2794,11 +2814,11 @@
       <c r="F28" s="12" t="n">
         <v>21.9</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>2.8</v>
+      <c r="G28" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H28" s="13" t="n">
+        <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>3.3</v>
@@ -2807,50 +2827,52 @@
         <v>5.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>16.7</v>
+        <v>0.1</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>46.1</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>15</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18</v>
+        <v>1.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>840.8</v>
+        <v>840.6</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>80.09999999999999</v>
-      </c>
-      <c r="Q28" s="8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="R28" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S28" s="3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q28" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="R28" s="12" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="S28" s="12" t="n">
         <v>18.4</v>
       </c>
-      <c r="T28" s="3" t="inlineStr"/>
-      <c r="U28" s="8" t="n">
-        <v>62.1</v>
+      <c r="T28" s="12" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="U28" s="12" t="n">
+        <v>6.2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>26.8</v>
+      <c r="W28" s="9" t="n">
+        <v>86.41</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>77.5</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2866,19 +2888,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2343.6</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>10.14</v>
+        <v>343.6</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>21.2</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>91.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>14</v>
@@ -2887,52 +2909,54 @@
         <v>2.8</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="L29" s="9" t="n">
-        <v>46.6</v>
+      <c r="L29" s="3" t="n">
+        <v>16.6</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="N29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="O29" s="3" t="n">
         <v>86.5</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="12" t="n">
         <v>22</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="S29" s="3" t="n">
+      <c r="S29" s="13" t="n">
         <v>21.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>21.5</v>
+        <v>81.5</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V29" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="W29" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Y29" s="3" t="n">
+      <c r="V29" s="12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="W29" s="12" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="X29" s="12" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="Y29" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="Z29" s="3" t="n">
+      <c r="Z29" s="12" t="n">
         <v>2.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -2949,21 +2973,25 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>78.8</v>
+        <v>178.8</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>112.1</v>
-      </c>
-      <c r="E30" s="13" t="inlineStr"/>
+        <v>131.4</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>81.40000000000001</v>
+      </c>
       <c r="F30" s="11" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="G30" s="3" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="G30" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="n">
+        <v>710.7</v>
+      </c>
       <c r="I30" s="3" t="n">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>19.3</v>
@@ -2978,39 +3006,43 @@
         <v>81.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>18</v>
+        <v>0.8</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.4</v>
+        <v>1434.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q30" s="11" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="R30" s="13" t="inlineStr"/>
+        <v>58.2</v>
+      </c>
+      <c r="Q30" s="12" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="R30" s="11" t="n">
+        <v>200.2</v>
+      </c>
       <c r="S30" s="3" t="n">
-        <v>2109.4</v>
+        <v>109.4</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>322.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>30.3</v>
+        <v>230.3</v>
       </c>
       <c r="V30" s="11" t="n">
-        <v>1681.8</v>
+        <v>111.8</v>
       </c>
       <c r="W30" s="11" t="n">
-        <v>91.8</v>
+        <v>191.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
+        <v>998.1</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>416.1</v>
+      </c>
       <c r="Z30" s="3" t="n">
-        <v>0.4</v>
+        <v>20</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3026,74 +3058,74 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2357.7</v>
-      </c>
-      <c r="D31" s="11" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="G31" s="9" t="n">
+        <v>357.7</v>
+      </c>
+      <c r="D31" s="12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G31" s="3" t="n">
         <v>11</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>26.1</v>
+      <c r="I31" s="13" t="n">
+        <v>96.09999999999999</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>2.9</v>
+        <v>28.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="L31" s="11" t="n">
-        <v>72.09999999999999</v>
+        <v>372.1</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>49</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q31" s="11" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Q31" s="12" t="n">
         <v>22.8</v>
       </c>
-      <c r="R31" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="S31" s="12" t="n">
+      <c r="R31" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="T31" s="12" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="U31" s="12" t="n">
+      <c r="T31" s="3" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="U31" s="3" t="n">
         <v>6.1</v>
       </c>
       <c r="V31" s="11" t="n">
-        <v>16.4</v>
+        <v>1.1</v>
       </c>
       <c r="W31" s="11" t="n">
-        <v>84.09999999999999</v>
+        <v>20.8</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>83.2</v>
+        <v>18.1</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>40.1</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3109,37 +3141,33 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>266.6</v>
+        <v>956.6</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E32" s="3" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="E32" s="12" t="n">
         <v>17.1</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>21.7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>21</v>
+        <v>19.3</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>13.4</v>
+        <v>1311.8</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>19.1</v>
+        <v>12.2</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="15" t="inlineStr"/>
+      <c r="L32" s="9" t="n">
+        <v>4.1</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>15.1</v>
+        <v>15.7</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>8.9</v>
@@ -3147,28 +3175,26 @@
       <c r="O32" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="P32" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="13" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="R32" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="R32" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="S32" s="8" t="n">
-        <v>20.4</v>
+      <c r="S32" s="3" t="n">
+        <v>1844151.8</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>98</v>
       </c>
       <c r="U32" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W32" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="W32" s="13" t="n">
         <v>16.9</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3178,7 +3204,7 @@
         <v>94</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>21.1</v>
+        <v>117.5</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3197,10 +3223,10 @@
         <v>400.8</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>21.8</v>
@@ -3212,31 +3238,33 @@
         <v>13.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr"/>
+        <v>86.09999999999999</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="K33" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="L33" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>18.1</v>
+        <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>28.8</v>
+        <v>11.4</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>7.8</v>
+        <v>78</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="12" t="n">
         <v>18.6</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3246,22 +3274,22 @@
         <v>77.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="V33" s="13" t="n">
         <v>19.6</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="13" t="n">
         <v>28</v>
       </c>
       <c r="X33" s="3" t="n">
         <v>12.7</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>86.8</v>
+        <v>286.5</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>23.2</v>
+        <v>13.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3277,7 +3305,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2350.2</v>
+        <v>350.2</v>
       </c>
       <c r="D34" s="12" t="n">
         <v>24.8</v>
@@ -3288,46 +3316,50 @@
       <c r="F34" s="12" t="n">
         <v>20.9</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>65.59999999999999</v>
+      <c r="G34" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H34" s="13" t="n">
+        <v>15.6</v>
       </c>
       <c r="I34" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N34" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="J34" s="3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="K34" s="15" t="inlineStr"/>
-      <c r="L34" s="12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>11.9</v>
-      </c>
       <c r="O34" s="3" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q34" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="R34" s="3" t="n">
+      <c r="Q34" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R34" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="S34" s="3" t="inlineStr"/>
+      <c r="S34" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="T34" s="3" t="n">
         <v>74.8</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>20.8</v>
@@ -3342,7 +3374,7 @@
         <v>84</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3369,8 +3401,8 @@
       <c r="F35" s="12" t="n">
         <v>20.7</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>8.9</v>
+      <c r="G35" s="12" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>14.4</v>
@@ -3384,17 +3416,17 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="12" t="n">
-        <v>17.6</v>
+      <c r="L35" s="9" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1.5</v>
+        <v>15.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>4</v>
@@ -3402,17 +3434,17 @@
       <c r="Q35" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="R35" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="S35" s="3" t="n">
-        <v>21.1</v>
+      <c r="R35" s="12" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S35" s="13" t="n">
+        <v>28.1</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>86</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>1.1</v>
+        <v>6.7</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>20.1</v>
@@ -3427,7 +3459,7 @@
         <v>89.5</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>21.1</v>
+        <v>12.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3443,13 +3475,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>356.8</v>
+        <v>35.6</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>22.1</v>
@@ -3457,51 +3489,53 @@
       <c r="G36" s="12" t="n">
         <v>12.1</v>
       </c>
-      <c r="H36" s="3" t="n">
-        <v>13.7</v>
+      <c r="H36" s="13" t="n">
+        <v>13.4</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="L36" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
+        <v>13.6</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q36" s="12" t="n">
+      <c r="Q36" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="S36" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="S36" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="T36" s="12" t="n">
-        <v>60.2</v>
-      </c>
-      <c r="U36" s="12" t="n">
+      <c r="T36" s="3" t="n">
+        <v>168.2</v>
+      </c>
+      <c r="U36" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="V36" s="9" t="n">
-        <v>80.8</v>
+      <c r="V36" s="13" t="n">
+        <v>20.8</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>18.8</v>
+        <v>19.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>22.6</v>
@@ -3510,7 +3544,7 @@
         <v>95.2</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.8</v>
+        <v>41.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3526,71 +3560,73 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1645.2</v>
+        <v>164.3</v>
       </c>
       <c r="D37" s="12" t="n">
         <v>131.3</v>
       </c>
-      <c r="E37" s="11" t="n">
-        <v>82.09999999999999</v>
+      <c r="E37" s="12" t="n">
+        <v>82.90000000000001</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>107.2</v>
-      </c>
-      <c r="G37" s="3" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G37" s="12" t="n">
         <v>48.5</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>710.6</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>116.7</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="11" t="n">
-        <v>160.6</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>88.40000000000001</v>
-      </c>
-      <c r="M37" s="13" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="M37" s="11" t="n">
+        <v>17.8</v>
+      </c>
       <c r="N37" s="3" t="n">
-        <v>86.8</v>
+        <v>8.6</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>228</v>
+        <v>899.8</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>120.8</v>
+        <v>12</v>
       </c>
       <c r="Q37" s="11" t="n">
-        <v>1812.3</v>
-      </c>
-      <c r="R37" s="11" t="n">
-        <v>91.09999999999999</v>
+        <v>222.9</v>
+      </c>
+      <c r="R37" s="12" t="n">
+        <v>97.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>100.8</v>
+        <v>103.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>289.4</v>
+        <v>9383.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="V37" s="11" t="n">
-        <v>98.09999999999999</v>
-      </c>
+        <v>34.2</v>
+      </c>
+      <c r="V37" s="14" t="inlineStr"/>
       <c r="W37" s="11" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="X37" s="3" t="inlineStr"/>
+        <v>923.1</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>2.9</v>
+      </c>
       <c r="Y37" s="3" t="n">
-        <v>418.8</v>
-      </c>
-      <c r="Z37" s="3" t="inlineStr"/>
+        <v>218.7</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3605,71 +3641,75 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1292.8</v>
+        <v>329.6</v>
       </c>
       <c r="D38" s="12" t="n">
         <v>26.3</v>
       </c>
-      <c r="E38" s="9" t="n">
-        <v>634.1</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>21.4</v>
+      <c r="E38" s="12" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>21.8</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>97</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I38" s="3" t="n">
-        <v>21.1</v>
-      </c>
+      <c r="I38" s="3" t="inlineStr"/>
       <c r="J38" s="3" t="n">
-        <v>33.1</v>
+        <v>3.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="N38" s="3" t="inlineStr"/>
+        <v>12.6</v>
+      </c>
+      <c r="L38" s="11" t="n">
+        <v>688.9</v>
+      </c>
+      <c r="M38" s="11" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>796.1</v>
+        <v>16.1</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="Q38" s="11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R38" s="11" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="S38" s="8" t="n">
-        <v>11.8</v>
+        <v>225.1</v>
+      </c>
+      <c r="R38" s="12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="S38" s="13" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="U38" s="3" t="inlineStr"/>
-      <c r="V38" s="11" t="n">
-        <v>19.6</v>
+      <c r="U38" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="V38" s="13" t="n">
+        <v>90.40000000000001</v>
       </c>
       <c r="W38" s="11" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="X38" s="3" t="n">
-        <v>20.6</v>
+        <v>89.8</v>
+      </c>
+      <c r="X38" s="13" t="n">
+        <v>0.5</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>8971.799999999999</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3684,64 +3724,66 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>986.4</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>18.7</v>
+        <v>264.4</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E39" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>20.7</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.8</v>
+        <v>33.1</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O39" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>3.6</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R39" s="8" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="R39" s="12" t="n">
         <v>22.2</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="T39" s="3" t="n">
-        <v>74.40000000000001</v>
-      </c>
+        <v>23.1</v>
+      </c>
+      <c r="T39" s="3" t="inlineStr"/>
       <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="n">
-        <v>20</v>
+        <v>18.1</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="inlineStr"/>
+        <v>16.9</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>88.90000000000001</v>
+      </c>
       <c r="Z39" s="3" t="inlineStr"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3757,74 +3799,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>359</v>
+        <v>286.4</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>27.5</v>
+        <v>25.6</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H40" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="L40" s="13" t="n">
+        <v>7.9</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>15.8</v>
+        <v>0.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>76.2</v>
+        <v>82.5</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>20.4</v>
+        <v>22.8</v>
+      </c>
+      <c r="R40" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="S40" s="13" t="n">
+        <v>20.7</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V40" s="9" t="n">
-        <v>0.2</v>
+        <v>74.40000000000001</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>86.2</v>
+        <v>89.7</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>32.4</v>
+        <v>22.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3840,70 +3884,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>4866.4</v>
+        <v>359</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>28.3</v>
+        <v>51.5</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="n">
-        <v>2.1</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H41" s="13" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M41" s="3" t="n">
-        <v>15.7</v>
+        <v>18</v>
+      </c>
+      <c r="M41" s="9" t="n">
+        <v>55.3</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>16.8</v>
+        <v>11.9</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>22</v>
+        <v>76.2</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Q41" s="12" t="n">
-        <v>26</v>
+        <v>4.8</v>
+      </c>
+      <c r="Q41" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="S41" s="12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="T41" s="12" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="U41" s="12" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="W41" s="15" t="inlineStr"/>
+        <v>20.2</v>
+      </c>
+      <c r="S41" s="13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="U41" s="13" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="V41" s="9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>19.6</v>
+      </c>
       <c r="X41" s="3" t="n">
-        <v>20.2</v>
+        <v>21.8</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3919,69 +3967,71 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>242.6</v>
+        <v>4856.1</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>27.7</v>
+        <v>28.6</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="G42" s="12" t="n">
-        <v>10.1</v>
+      <c r="G42" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>18</v>
+        <v>17.7</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>16</v>
+        <v>16.8</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>79.8</v>
+        <v>682</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>4.2</v>
+        <v>13.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="R42" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="R42" s="12" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X42" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="S42" s="3" t="n">
-        <v>89.90000000000001</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="U42" s="3" t="inlineStr"/>
-      <c r="V42" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>19.7</v>
-      </c>
       <c r="Y42" s="3" t="n">
-        <v>23.4</v>
+        <v>28.5</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>7.1</v>
@@ -4000,71 +4050,75 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D43" s="8" t="n">
+        <v>742.6</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E43" s="12" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>88</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="E43" s="9" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L43" s="9" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="M43" s="9" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="3" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="R43" s="9" t="n">
-        <v>61.6</v>
+      <c r="R43" s="12" t="n">
+        <v>20.2</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>10.9</v>
+        <v>1.9</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="U43" s="3" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="V43" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W43" s="15" t="inlineStr"/>
-      <c r="X43" s="3" t="n">
-        <v>20.8</v>
+        <v>55.5</v>
+      </c>
+      <c r="U43" s="13" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X43" s="13" t="n">
+        <v>18.5</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z43" s="3" t="inlineStr"/>
+        <v>20.4</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -4082,8 +4136,8 @@
         <v>0.1</v>
       </c>
       <c r="D44" s="15" t="inlineStr"/>
-      <c r="E44" s="15" t="inlineStr"/>
-      <c r="F44" s="15" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -4095,7 +4149,7 @@
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="15" t="inlineStr"/>
-      <c r="R44" s="15" t="inlineStr"/>
+      <c r="R44" s="12" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
@@ -4118,75 +4172,75 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>362.9</v>
+        <v>1889</v>
       </c>
       <c r="D45" s="11" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="E45" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="F45" s="11" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>10.5</v>
+        <v>134.4</v>
+      </c>
+      <c r="E45" s="14" t="inlineStr"/>
+      <c r="F45" s="12" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>59.5</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>13.9</v>
+        <v>69.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>9.5</v>
+        <v>117.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>5.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="L45" s="11" t="n">
-        <v>18</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>15.9</v>
+        <v>53.7</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1.6</v>
+        <v>71</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>1405.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>9.9</v>
+        <v>19.5</v>
       </c>
       <c r="Q45" s="11" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="R45" s="11" t="n">
-        <v>202.8</v>
+        <v>1268.4</v>
+      </c>
+      <c r="R45" s="12" t="n">
+        <v>101.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>20.8</v>
+        <v>104.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>66</v>
+        <v>330</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>11.1</v>
+        <v>55.6</v>
       </c>
       <c r="V45" s="11" t="n">
-        <v>21</v>
+        <v>104.8</v>
       </c>
       <c r="W45" s="11" t="n">
-        <v>18.7</v>
+        <v>98.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>20.2</v>
+        <v>118.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr"/>
+        <v>108.8</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4200,64 +4254,78 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="n">
+        <v>362.9</v>
+      </c>
       <c r="D46" s="11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E46" s="11" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>439.8</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L46" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="M46" s="11" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="Q46" s="11" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="R46" s="12" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="U46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="F46" s="11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H46" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L46" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M46" s="11" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q46" s="13" t="inlineStr"/>
-      <c r="R46" s="13" t="inlineStr"/>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>0.8</v>
-      </c>
       <c r="V46" s="11" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="W46" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="X46" s="3" t="inlineStr"/>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +146,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,10 +164,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -789,16 +798,16 @@
       <c r="C4" s="3" t="n">
         <v>389.8</v>
       </c>
-      <c r="D4" s="9" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="G4" s="3" t="n">
+      <c r="D4" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G4" s="11" t="n">
         <v>12.5</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -810,52 +819,52 @@
       <c r="J4" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K4" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L4" s="12" t="n">
+      <c r="K4" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="11" t="n">
         <v>17.9</v>
       </c>
-      <c r="M4" s="12" t="n">
+      <c r="M4" s="11" t="n">
         <v>16.8</v>
       </c>
-      <c r="N4" s="12" t="n">
+      <c r="N4" s="11" t="n">
         <v>19.1</v>
       </c>
-      <c r="O4" s="12" t="n">
+      <c r="O4" s="11" t="n">
         <v>93.3</v>
       </c>
-      <c r="P4" s="12" t="n">
+      <c r="P4" s="11" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q4" s="3" t="n">
+      <c r="Q4" s="11" t="n">
         <v>23.7</v>
       </c>
-      <c r="R4" s="12" t="n">
+      <c r="R4" s="11" t="n">
         <v>21.8</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>85.09999999999999</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="V4" s="12" t="n">
+      <c r="S4" s="11" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="T4" s="11" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="U4" s="11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V4" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="W4" s="12" t="n">
+      <c r="W4" s="11" t="n">
         <v>18.7</v>
       </c>
-      <c r="X4" s="12" t="n">
+      <c r="X4" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="Y4" s="12" t="n">
+      <c r="Y4" s="11" t="n">
         <v>90.5</v>
       </c>
-      <c r="Z4" s="12" t="n">
+      <c r="Z4" s="11" t="n">
         <v>2.3</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -872,22 +881,22 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>438.6</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="E5" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>16.9</v>
       </c>
-      <c r="F5" s="9" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>121</v>
+      <c r="F5" s="11" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>2.8</v>
@@ -895,52 +904,52 @@
       <c r="J5" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="11" t="n">
         <v>12.3</v>
       </c>
-      <c r="L5" s="12" t="n">
+      <c r="L5" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="M5" s="12" t="n">
+      <c r="M5" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="N5" s="12" t="n">
+      <c r="N5" s="11" t="n">
         <v>20.1</v>
       </c>
-      <c r="O5" s="12" t="n">
+      <c r="O5" s="11" t="n">
         <v>95.7</v>
       </c>
-      <c r="P5" s="12" t="n">
+      <c r="P5" s="11" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="R5" s="12" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="S5" s="3" t="n">
+      <c r="R5" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S5" s="11" t="n">
         <v>23.3</v>
       </c>
-      <c r="T5" s="3" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V5" s="12" t="n">
+      <c r="T5" s="11" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="U5" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V5" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="W5" s="12" t="n">
+      <c r="W5" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="X5" s="12" t="n">
+      <c r="X5" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="Y5" s="12" t="n">
+      <c r="Y5" s="11" t="n">
         <v>95.09999999999999</v>
       </c>
-      <c r="Z5" s="12" t="n">
+      <c r="Z5" s="11" t="n">
         <v>1</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -957,75 +966,75 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>494.4</v>
-      </c>
-      <c r="D6" s="12" t="n">
+        <v>484.4</v>
+      </c>
+      <c r="D6" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>22.9</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="11" t="n">
         <v>11.9</v>
       </c>
-      <c r="H6" s="13" t="n">
-        <v>25.2</v>
+      <c r="H6" s="3" t="n">
+        <v>15.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>13.8</v>
+        <v>3.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L6" s="12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="M6" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="N6" s="12" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="O6" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="P6" s="12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q6" s="12" t="n">
+      <c r="M6" s="11" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="N6" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="S6" s="12" t="n">
+      <c r="S6" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="T6" s="12" t="n">
+      <c r="T6" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="U6" s="12" t="n">
+      <c r="U6" s="11" t="n">
         <v>10.9</v>
       </c>
-      <c r="V6" s="12" t="n">
+      <c r="V6" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="X6" s="12" t="n">
+      <c r="X6" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="Y6" s="12" t="n">
+      <c r="Y6" s="11" t="n">
         <v>94</v>
       </c>
-      <c r="Z6" s="12" t="n">
+      <c r="Z6" s="11" t="n">
         <v>1.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1042,75 +1051,75 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>384.4</v>
-      </c>
-      <c r="D7" s="12" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="D7" s="11" t="n">
         <v>28.2</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="11" t="n">
         <v>16.2</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="11" t="n">
         <v>12</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="11" t="n">
         <v>17.9</v>
       </c>
-      <c r="N7" s="12" t="n">
+      <c r="N7" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="O7" s="12" t="n">
+      <c r="O7" s="11" t="n">
         <v>93.3</v>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="11" t="n">
         <v>27.3</v>
       </c>
-      <c r="R7" s="12" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="S7" s="3" t="n">
+      <c r="R7" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="S7" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="T7" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="U7" s="3" t="n">
+      <c r="T7" s="11" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="U7" s="11" t="n">
         <v>11.4</v>
       </c>
-      <c r="V7" s="12" t="n">
+      <c r="V7" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="W7" s="12" t="n">
+      <c r="W7" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="X7" s="12" t="n">
+      <c r="X7" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="Y7" s="12" t="n">
+      <c r="Y7" s="11" t="n">
         <v>92.8</v>
       </c>
-      <c r="Z7" s="12" t="n">
+      <c r="Z7" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1127,18 +1136,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>460.2</v>
-      </c>
-      <c r="D8" s="12" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="11" t="n">
         <v>22.7</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="11" t="n">
         <v>11.4</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1150,52 +1159,52 @@
       <c r="J8" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="11" t="n">
         <v>4.1</v>
       </c>
-      <c r="L8" s="12" t="n">
+      <c r="L8" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="M8" s="12" t="n">
+      <c r="M8" s="11" t="n">
         <v>15.8</v>
       </c>
-      <c r="N8" s="12" t="n">
+      <c r="N8" s="11" t="n">
         <v>17.9</v>
       </c>
-      <c r="O8" s="12" t="n">
+      <c r="O8" s="11" t="n">
         <v>92.59999999999999</v>
       </c>
-      <c r="P8" s="12" t="n">
+      <c r="P8" s="11" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q8" s="12" t="n">
+      <c r="Q8" s="11" t="n">
         <v>24.5</v>
       </c>
-      <c r="R8" s="12" t="n">
+      <c r="R8" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="S8" s="12" t="n">
+      <c r="S8" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="T8" s="12" t="n">
+      <c r="T8" s="11" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="U8" s="12" t="n">
+      <c r="U8" s="11" t="n">
         <v>3.9</v>
       </c>
-      <c r="V8" s="12" t="n">
+      <c r="V8" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="W8" s="12" t="n">
+      <c r="W8" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="X8" s="12" t="n">
+      <c r="X8" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="Y8" s="12" t="n">
+      <c r="Y8" s="11" t="n">
         <v>90.5</v>
       </c>
-      <c r="Z8" s="12" t="n">
+      <c r="Z8" s="11" t="n">
         <v>2.2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1212,22 +1221,22 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2240.4</v>
+        <v>140.4</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>142</v>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>82.90000000000001</v>
+      <c r="E9" s="11" t="n">
+        <v>83</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>25.9</v>
+        <v>112.5</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>59.1</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>671.7</v>
+        <v>67.7</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>16.2</v>
@@ -1238,7 +1247,7 @@
       <c r="K9" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="11" t="n">
         <v>89.40000000000001</v>
       </c>
       <c r="M9" s="11" t="n">
@@ -1246,15 +1255,15 @@
       </c>
       <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>343.3</v>
+        <v>345.3</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q9" s="11" t="n">
-        <v>1272.1</v>
-      </c>
-      <c r="R9" s="11" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="R9" s="19" t="n">
         <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1266,14 +1275,14 @@
       <c r="U9" s="3" t="n">
         <v>38.5</v>
       </c>
-      <c r="V9" s="12" t="n">
+      <c r="V9" s="11" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="W9" s="12" t="n">
+      <c r="W9" s="11" t="n">
         <v>92.7</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>63.8</v>
+        <v>3.1</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>445.1</v>
@@ -1295,75 +1304,75 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>428.1</v>
+        <v>28.1</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>28.4</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>16.6</v>
       </c>
       <c r="F10" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="11" t="n">
         <v>11.8</v>
       </c>
-      <c r="H10" s="13" t="n">
-        <v>18.5</v>
+      <c r="H10" s="3" t="n">
+        <v>13.5</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L10" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L10" s="11" t="n">
         <v>17.9</v>
       </c>
-      <c r="M10" s="12" t="n">
+      <c r="M10" s="11" t="n">
         <v>16.9</v>
       </c>
-      <c r="N10" s="12" t="n">
+      <c r="N10" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="O10" s="12" t="n">
+      <c r="O10" s="11" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="P10" s="12" t="n">
+      <c r="P10" s="11" t="n">
         <v>1.3</v>
       </c>
       <c r="Q10" s="11" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="R10" s="11" t="n">
-        <v>21.7</v>
+        <v>25.4</v>
+      </c>
+      <c r="R10" s="19" t="n">
+        <v>21.1</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1041.4</v>
+        <v>1011.4</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>7.7</v>
       </c>
-      <c r="V10" s="12" t="n">
+      <c r="V10" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="W10" s="12" t="n">
+      <c r="W10" s="11" t="n">
         <v>18.5</v>
       </c>
-      <c r="X10" s="12" t="n">
+      <c r="X10" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="Y10" s="12" t="n">
+      <c r="Y10" s="11" t="n">
         <v>92.2</v>
       </c>
-      <c r="Z10" s="12" t="n">
+      <c r="Z10" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1382,69 +1391,71 @@
       <c r="C11" s="3" t="n">
         <v>299.6</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="11" t="n">
         <v>16.8</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <v>21.7</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>19.7</v>
+      <c r="G11" s="11" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="I11" s="13" t="n">
-        <v>92.8</v>
+      <c r="I11" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="K11" s="15" t="inlineStr"/>
-      <c r="L11" s="3" t="n">
+      <c r="K11" s="13" t="inlineStr"/>
+      <c r="L11" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="12" t="n">
+      <c r="N11" s="11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="O11" s="11" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="P11" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q11" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="R11" s="12" t="n">
+      <c r="R11" s="11" t="n">
         <v>19.7</v>
       </c>
-      <c r="S11" s="12" t="n">
+      <c r="S11" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="T11" s="12" t="n">
+      <c r="T11" s="11" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U11" s="12" t="n">
+      <c r="U11" s="11" t="n">
         <v>10.6</v>
       </c>
-      <c r="V11" s="12" t="n">
+      <c r="V11" s="11" t="n">
         <v>21.7</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="X11" s="13" t="n">
-        <v>822</v>
-      </c>
-      <c r="Y11" s="3" t="n">
+      <c r="W11" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="X11" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y11" s="11" t="n">
         <v>84.5</v>
       </c>
-      <c r="Z11" s="3" t="n">
+      <c r="Z11" s="11" t="n">
         <v>4</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1463,16 +1474,16 @@
       <c r="C12" s="3" t="n">
         <v>343.6</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="11" t="n">
         <v>9.1</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1487,49 +1498,49 @@
       <c r="K12" s="3" t="n">
         <v>2.4</v>
       </c>
-      <c r="L12" s="9" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="M12" s="12" t="n">
+      <c r="L12" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="M12" s="11" t="n">
         <v>17.6</v>
       </c>
-      <c r="N12" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q12" s="12" t="n">
+      <c r="N12" s="11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="R12" s="12" t="n">
+      <c r="R12" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="S12" s="12" t="n">
+      <c r="S12" s="11" t="n">
         <v>22.7</v>
       </c>
-      <c r="T12" s="12" t="n">
+      <c r="T12" s="11" t="n">
         <v>95.2</v>
       </c>
-      <c r="U12" s="12" t="n">
+      <c r="U12" s="11" t="n">
         <v>1.2</v>
       </c>
-      <c r="V12" s="12" t="n">
+      <c r="V12" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="W12" s="12" t="n">
+      <c r="W12" s="11" t="n">
         <v>19.7</v>
       </c>
-      <c r="X12" s="12" t="n">
+      <c r="X12" s="11" t="n">
         <v>22.9</v>
       </c>
-      <c r="Y12" s="12" t="n">
+      <c r="Y12" s="11" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="Z12" s="12" t="n">
+      <c r="Z12" s="11" t="n">
         <v>2.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -1548,72 +1559,72 @@
       <c r="C13" s="3" t="n">
         <v>323.8</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="11" t="n">
         <v>27.5</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="13" t="n">
-        <v>21</v>
+      <c r="J13" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="11" t="n">
         <v>17.7</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="M13" s="11" t="n">
         <v>16.9</v>
       </c>
-      <c r="N13" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O13" s="3" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q13" s="12" t="n">
+      <c r="N13" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="O13" s="11" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="P13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="11" t="n">
         <v>24.4</v>
       </c>
-      <c r="R13" s="12" t="n">
+      <c r="R13" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="S13" s="12" t="n">
+      <c r="S13" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="T13" s="12" t="n">
+      <c r="T13" s="11" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="U13" s="12" t="n">
+      <c r="U13" s="11" t="n">
         <v>5.1</v>
       </c>
-      <c r="V13" s="12" t="n">
+      <c r="V13" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="11" t="n">
         <v>19.4</v>
       </c>
-      <c r="X13" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Y13" s="3" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v>0.9</v>
+      <c r="X13" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Y13" s="11" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="Z13" s="11" t="n">
+        <v>0.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1631,16 +1642,16 @@
       <c r="C14" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="F14" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="G14" s="11" t="n">
         <v>7.4</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1648,54 +1659,54 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="M14" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="N14" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O14" s="3" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="P14" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q14" s="12" t="n">
+      <c r="N14" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="O14" s="11" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="P14" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q14" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="R14" s="12" t="n">
+      <c r="R14" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="S14" s="12" t="n">
+      <c r="S14" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="T14" s="12" t="n">
+      <c r="T14" s="11" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="U14" s="12" t="n">
+      <c r="U14" s="11" t="n">
         <v>1.1</v>
       </c>
-      <c r="V14" s="12" t="n">
+      <c r="V14" s="11" t="n">
         <v>19.7</v>
       </c>
-      <c r="W14" s="12" t="n">
+      <c r="W14" s="11" t="n">
         <v>19.4</v>
       </c>
-      <c r="X14" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="Y14" s="12" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="Z14" s="12" t="n">
+      <c r="X14" s="11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Y14" s="11" t="n">
+        <v>97</v>
+      </c>
+      <c r="Z14" s="11" t="n">
         <v>0.7</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -1712,76 +1723,76 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>334.8</v>
-      </c>
-      <c r="D15" s="12" t="n">
+        <v>834.8</v>
+      </c>
+      <c r="D15" s="11" t="n">
         <v>28.3</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="11" t="n">
         <v>11.7</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="L15" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="L15" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="M15" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="P15" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q15" s="12" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="R15" s="12" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S15" s="12" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="T15" s="12" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="U15" s="12" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="V15" s="12" t="n">
+      <c r="N15" s="11" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="P15" s="11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q15" s="11" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="R15" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="S15" s="11" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="T15" s="11" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="U15" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="V15" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="W15" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="X15" s="3" t="n">
+      <c r="W15" s="11" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="X15" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="Y15" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>12</v>
+      <c r="Y15" s="11" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z15" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1797,73 +1808,73 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1361.8</v>
-      </c>
-      <c r="D16" s="12" t="n">
+        <v>1561.8</v>
+      </c>
+      <c r="D16" s="11" t="n">
         <v>134</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="11" t="n">
         <v>85.59999999999999</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="11" t="n">
         <v>109.9</v>
       </c>
-      <c r="G16" s="12" t="n">
-        <v>48.1</v>
+      <c r="G16" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>73</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>110.8</v>
+        <v>10.8</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K16" s="11" t="n">
-        <v>92.59999999999999</v>
+      <c r="K16" s="19" t="n">
+        <v>32.1</v>
       </c>
       <c r="L16" s="11" t="n">
         <v>88.8</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="M16" s="11" t="n">
         <v>85.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>1465.9</v>
+        <v>22.8</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="Q16" s="12" t="n">
-        <v>120.3</v>
-      </c>
-      <c r="R16" s="11" t="n">
+      <c r="Q16" s="11" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="R16" s="19" t="n">
         <v>104.3</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>2116.6</v>
+        <v>114.6</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>199.8</v>
+        <v>393.8</v>
       </c>
       <c r="U16" s="3" t="n">
         <v>35.1</v>
       </c>
-      <c r="V16" s="12" t="n">
+      <c r="V16" s="11" t="n">
         <v>101.9</v>
       </c>
-      <c r="W16" s="11" t="n">
-        <v>969.1</v>
+      <c r="W16" s="19" t="n">
+        <v>96.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>98.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>458.4</v>
+        <v>457.4</v>
       </c>
       <c r="Z16" s="3" t="inlineStr"/>
       <c r="AA16" s="3" t="inlineStr">
@@ -1880,15 +1891,15 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2312.4</v>
-      </c>
-      <c r="D17" s="12" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="D17" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="11" t="n">
         <v>17.1</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="11" t="n">
         <v>22</v>
       </c>
       <c r="G17" s="3" t="n">
@@ -1898,58 +1909,58 @@
         <v>14.6</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.2</v>
+        <v>22.2</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="L17" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="M17" s="11" t="n">
         <v>17.1</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O17" s="3" t="n">
-        <v>93.2</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q17" s="12" t="n">
+      <c r="N17" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="O17" s="11" t="n">
+        <v>95.7</v>
+      </c>
+      <c r="P17" s="11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q17" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="R17" s="11" t="n">
-        <v>20.5</v>
+      <c r="R17" s="19" t="n">
+        <v>20</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>29.9</v>
+        <v>22.9</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>789.1</v>
+        <v>78.8</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="V17" s="12" t="n">
+      <c r="V17" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="W17" s="11" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="X17" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="Y17" s="3" t="n">
-        <v>2812.1</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>2.1</v>
+      <c r="W17" s="19" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="X17" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Y17" s="11" t="n">
+        <v>94</v>
+      </c>
+      <c r="Z17" s="11" t="n">
+        <v>1.4</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1967,19 +1978,19 @@
       <c r="C18" s="3" t="n">
         <v>354.6</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="11" t="n">
         <v>27.7</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>22.4</v>
+      <c r="F18" s="11" t="n">
+        <v>22.3</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="H18" s="13" t="n">
+      <c r="H18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I18" s="3" t="n">
@@ -1988,50 +1999,50 @@
       <c r="J18" s="3" t="n">
         <v>5.5</v>
       </c>
-      <c r="K18" s="3" t="n">
-        <v>10.8</v>
+      <c r="K18" s="11" t="n">
+        <v>0.8</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="11" t="n">
         <v>16.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>18.8</v>
+        <v>1.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>166.5</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v>224.884</v>
-      </c>
-      <c r="W18" s="9" t="n">
-        <v>11.11</v>
+        <v>2.7</v>
+      </c>
+      <c r="Q18" s="11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="R18" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="S18" s="11" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="T18" s="11" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="U18" s="11" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V18" s="17" t="n">
+        <v>224.214</v>
+      </c>
+      <c r="W18" s="17" t="n">
+        <v>28.12</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>118.9</v>
+        <v>18.9</v>
       </c>
       <c r="Z18" s="3" t="n">
         <v>20.7</v>
@@ -2050,40 +2061,40 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>219.4</v>
-      </c>
-      <c r="D19" s="12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D19" s="11" t="n">
         <v>27.4</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="11" t="n">
         <v>16.2</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="11" t="n">
         <v>21.8</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="11" t="n">
         <v>11.2</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>22.8</v>
+        <v>2.2</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>3.3</v>
       </c>
-      <c r="K19" s="3" t="n">
-        <v>22.3</v>
+      <c r="K19" s="11" t="n">
+        <v>2.3</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M19" s="9" t="n">
-        <v>87.40000000000001</v>
+      <c r="M19" s="11" t="n">
+        <v>17.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>1.8</v>
+        <v>15.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
@@ -2091,34 +2102,34 @@
       <c r="P19" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q19" s="3" t="n">
+      <c r="Q19" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="R19" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="S19" s="13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="V19" s="3" t="n">
+      <c r="R19" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="S19" s="11" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="U19" s="11" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="V19" s="11" t="n">
         <v>23.4</v>
       </c>
-      <c r="W19" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="X19" s="3" t="n">
+      <c r="W19" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X19" s="11" t="n">
         <v>21.2</v>
       </c>
-      <c r="Y19" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Z19" s="3" t="n">
+      <c r="Y19" s="11" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="Z19" s="11" t="n">
         <v>7.6</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -2137,16 +2148,16 @@
       <c r="C20" s="3" t="n">
         <v>358.8</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="11" t="n">
         <v>26.8</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="11" t="n">
         <v>17.8</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="11" t="n">
         <v>22.3</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="11" t="n">
         <v>9</v>
       </c>
       <c r="H20" s="3" t="n">
@@ -2156,54 +2167,54 @@
         <v>19.4</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="K20" s="3" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="K20" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="11" t="n">
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q20" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q20" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S20" s="13" t="n">
+      <c r="R20" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="S20" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="T20" s="3" t="n">
-        <v>1891.8</v>
-      </c>
-      <c r="U20" s="3" t="n">
+      <c r="T20" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="U20" s="11" t="n">
         <v>3.1</v>
       </c>
-      <c r="V20" s="12" t="n">
+      <c r="V20" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="W20" s="12" t="n">
+      <c r="W20" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="X20" s="12" t="n">
+      <c r="X20" s="11" t="n">
         <v>23.2</v>
       </c>
-      <c r="Y20" s="12" t="n">
+      <c r="Y20" s="11" t="n">
         <v>93.8</v>
       </c>
-      <c r="Z20" s="12" t="n">
+      <c r="Z20" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2220,73 +2231,73 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2284.2</v>
-      </c>
-      <c r="D21" s="12" t="n">
+        <v>284.6</v>
+      </c>
+      <c r="D21" s="11" t="n">
         <v>28</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="G21" s="13" t="n">
-        <v>71.8</v>
+      <c r="G21" s="11" t="n">
+        <v>11.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>8</v>
+        <v>20.2</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="11" t="n">
         <v>3.5</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="11" t="n">
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>18.2</v>
+        <v>1.2</v>
       </c>
       <c r="Q21" s="3" t="inlineStr"/>
       <c r="R21" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>28.6</v>
+        <v>22.6</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>91.09999999999999</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="V21" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V21" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="W21" s="12" t="n">
+      <c r="W21" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="X21" s="12" t="n">
+      <c r="X21" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="Y21" s="12" t="n">
+      <c r="Y21" s="11" t="n">
         <v>96.8</v>
       </c>
-      <c r="Z21" s="12" t="n">
+      <c r="Z21" s="11" t="n">
         <v>0.8</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -2305,16 +2316,16 @@
       <c r="C22" s="3" t="n">
         <v>339.2</v>
       </c>
-      <c r="D22" s="9" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="E22" s="12" t="n">
+      <c r="D22" s="11" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E22" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="F22" s="9" t="n">
-        <v>92.3</v>
-      </c>
-      <c r="G22" s="12" t="n">
+      <c r="F22" s="11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G22" s="11" t="n">
         <v>10.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2324,19 +2335,19 @@
         <v>2.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="K22" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K22" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="11" t="n">
         <v>17.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2344,34 +2355,34 @@
       <c r="P22" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="11" t="n">
         <v>25.1</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="S22" s="3" t="n">
+      <c r="R22" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="S22" s="11" t="n">
         <v>23.6</v>
       </c>
-      <c r="T22" s="3" t="n">
-        <v>724</v>
-      </c>
-      <c r="U22" s="3" t="n">
+      <c r="T22" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="U22" s="11" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="V22" s="12" t="n">
+      <c r="V22" s="11" t="n">
         <v>23.1</v>
       </c>
-      <c r="W22" s="12" t="n">
+      <c r="W22" s="11" t="n">
         <v>17.2</v>
       </c>
-      <c r="X22" s="12" t="n">
+      <c r="X22" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="Y22" s="12" t="n">
+      <c r="Y22" s="11" t="n">
         <v>69.09999999999999</v>
       </c>
-      <c r="Z22" s="12" t="n">
+      <c r="Z22" s="11" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -2388,70 +2399,70 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1542.6</v>
+        <v>1548.6</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>137.6</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="11" t="n">
         <v>85</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>35.3</v>
+        <v>111.3</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>52.6</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>74.8</v>
+        <v>74.2</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>119.3</v>
+        <v>19.3</v>
       </c>
       <c r="K23" s="11" t="n">
         <v>6.6</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="L23" s="19" t="n">
         <v>0.9</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>87.8</v>
+        <v>87.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.9</v>
+        <v>9.4</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>46.9</v>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="14" t="inlineStr"/>
-      <c r="R23" s="14" t="inlineStr"/>
+      <c r="Q23" s="12" t="inlineStr"/>
+      <c r="R23" s="12" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>215.8</v>
+        <v>115.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>293.1</v>
+        <v>93.7</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="V23" s="11" t="n">
+      <c r="V23" s="19" t="n">
         <v>110.3</v>
       </c>
-      <c r="W23" s="11" t="n">
+      <c r="W23" s="19" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>110.9</v>
+        <v>103.4</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>606.8</v>
+        <v>16.8</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>22.1</v>
+        <v>22.7</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2469,38 +2480,38 @@
       <c r="C24" s="3" t="n">
         <v>309.7</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="11" t="n">
         <v>27.5</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="F24" s="9" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="G24" s="3" t="n">
+      <c r="F24" s="11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G24" s="11" t="n">
         <v>10.5</v>
       </c>
-      <c r="H24" s="13" t="n">
-        <v>184.8</v>
+      <c r="H24" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>9.9</v>
+        <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L24" s="11" t="n">
         <v>48.1</v>
       </c>
       <c r="M24" s="11" t="n">
         <v>17.4</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>93.8</v>
@@ -2508,14 +2519,14 @@
       <c r="P24" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q24" s="13" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R24" s="13" t="n">
-        <v>10.1</v>
+      <c r="Q24" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>78.7</v>
@@ -2523,20 +2534,20 @@
       <c r="U24" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V24" s="11" t="n">
+      <c r="V24" s="19" t="n">
         <v>28.1</v>
       </c>
-      <c r="W24" s="11" t="n">
+      <c r="W24" s="19" t="n">
         <v>19.9</v>
       </c>
-      <c r="X24" s="13" t="n">
-        <v>8181.1</v>
+      <c r="X24" s="3" t="n">
+        <v>2.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>16.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2554,30 +2565,30 @@
       <c r="C25" s="3" t="n">
         <v>479.9</v>
       </c>
-      <c r="D25" s="12" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>7.5</v>
+      <c r="D25" s="11" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>7.3</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L25" s="13" t="n">
+      <c r="K25" s="11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L25" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="M25" s="11" t="n">
         <v>18.2</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2589,29 +2600,29 @@
       <c r="P25" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q25" s="12" t="n">
+      <c r="Q25" s="11" t="n">
         <v>22.2</v>
       </c>
-      <c r="R25" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="S25" s="3" t="n">
+      <c r="R25" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="S25" s="11" t="n">
         <v>22.1</v>
       </c>
-      <c r="T25" s="3" t="n">
+      <c r="T25" s="11" t="n">
         <v>82.5</v>
       </c>
-      <c r="U25" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="V25" s="13" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="W25" s="9" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="X25" s="13" t="n">
-        <v>54.4</v>
+      <c r="U25" s="11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="W25" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>55.5</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>21.1</v>
@@ -2633,36 +2644,36 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>341.1</v>
-      </c>
-      <c r="D26" s="12" t="n">
+        <v>341.4</v>
+      </c>
+      <c r="D26" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="11" t="n">
         <v>15.8</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="G26" s="3" t="n">
-        <v>19</v>
+      <c r="G26" s="11" t="n">
+        <v>9</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K26" s="3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K26" s="11" t="n">
         <v>2.6</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="M26" s="11" t="n">
         <v>16.7</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2674,34 +2685,34 @@
       <c r="P26" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q26" s="12" t="n">
+      <c r="Q26" s="11" t="n">
         <v>23.7</v>
       </c>
-      <c r="R26" s="12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S26" s="12" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="T26" s="12" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="U26" s="12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="V26" s="12" t="n">
+      <c r="R26" s="11" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="S26" s="11" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="T26" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="U26" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V26" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="W26" s="12" t="n">
+      <c r="W26" s="11" t="n">
         <v>19.3</v>
       </c>
-      <c r="X26" s="12" t="n">
+      <c r="X26" s="11" t="n">
         <v>22.4</v>
       </c>
-      <c r="Y26" s="12" t="n">
+      <c r="Y26" s="11" t="n">
         <v>92</v>
       </c>
-      <c r="Z26" s="12" t="n">
+      <c r="Z26" s="11" t="n">
         <v>1.9</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -2720,16 +2731,16 @@
       <c r="C27" s="3" t="n">
         <v>370</v>
       </c>
-      <c r="D27" s="12" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G27" s="12" t="n">
+      <c r="D27" s="11" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G27" s="11" t="n">
         <v>10.1</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2741,13 +2752,13 @@
       <c r="J27" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K27" s="3" t="n">
+      <c r="K27" s="11" t="n">
         <v>1.2</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="M27" s="11" t="n">
         <v>16.1</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2757,21 +2768,21 @@
         <v>93</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="Q27" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q27" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="R27" s="12" t="n">
+      <c r="R27" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="S27" s="12" t="n">
+      <c r="S27" s="11" t="n">
         <v>22.7</v>
       </c>
-      <c r="T27" s="12" t="n">
+      <c r="T27" s="11" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="U27" s="12" t="n">
+      <c r="U27" s="11" t="n">
         <v>9.9</v>
       </c>
       <c r="V27" s="3" t="n">
@@ -2780,14 +2791,14 @@
       <c r="W27" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="X27" s="13" t="n">
+      <c r="X27" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2803,21 +2814,21 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="D28" s="12" t="n">
+        <v>453.6</v>
+      </c>
+      <c r="D28" s="11" t="n">
         <v>28.8</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="H28" s="13" t="n">
+      <c r="H28" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2826,52 +2837,52 @@
       <c r="J28" s="3" t="n">
         <v>5.3</v>
       </c>
-      <c r="K28" s="3" t="n">
+      <c r="K28" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="L28" s="9" t="n">
+      <c r="L28" s="17" t="n">
         <v>46.1</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="M28" s="11" t="n">
         <v>15</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>1.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>840.6</v>
+        <v>24</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q28" s="12" t="n">
+      <c r="Q28" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="R28" s="12" t="n">
+      <c r="R28" s="11" t="n">
         <v>16.2</v>
       </c>
-      <c r="S28" s="12" t="n">
+      <c r="S28" s="11" t="n">
         <v>18.4</v>
       </c>
-      <c r="T28" s="12" t="n">
+      <c r="T28" s="11" t="n">
         <v>74.7</v>
       </c>
-      <c r="U28" s="12" t="n">
+      <c r="U28" s="11" t="n">
         <v>6.2</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="W28" s="9" t="n">
-        <v>86.41</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="Y28" s="3" t="n">
+      <c r="W28" s="11" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="X28" s="11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y28" s="11" t="n">
         <v>77.5</v>
       </c>
-      <c r="Z28" s="3" t="n">
+      <c r="Z28" s="11" t="n">
         <v>5</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -2890,16 +2901,16 @@
       <c r="C29" s="3" t="n">
         <v>343.6</v>
       </c>
-      <c r="D29" s="12" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="E29" s="12" t="n">
+      <c r="D29" s="11" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="E29" s="11" t="n">
         <v>16.5</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="G29" s="3" t="n">
+      <c r="F29" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G29" s="11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2911,17 +2922,17 @@
       <c r="J29" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K29" s="3" t="n">
+      <c r="K29" s="11" t="n">
         <v>0.9</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="M29" s="11" t="n">
         <v>15.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>86.5</v>
@@ -2929,34 +2940,34 @@
       <c r="P29" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q29" s="12" t="n">
+      <c r="Q29" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="R29" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="S29" s="13" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="T29" s="3" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V29" s="12" t="n">
+      <c r="R29" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="S29" s="11" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="T29" s="11" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="U29" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V29" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="W29" s="12" t="n">
+      <c r="W29" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="X29" s="12" t="n">
+      <c r="X29" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="Y29" s="12" t="n">
+      <c r="Y29" s="11" t="n">
         <v>88</v>
       </c>
-      <c r="Z29" s="12" t="n">
+      <c r="Z29" s="11" t="n">
         <v>2.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -2973,25 +2984,25 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>178.8</v>
+        <v>1788.4</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>131.4</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="11" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="F30" s="11" t="n">
         <v>106.4</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="G30" s="11" t="n">
         <v>50</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>710.7</v>
+        <v>70.7</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>19.3</v>
@@ -2999,47 +3010,47 @@
       <c r="K30" s="11" t="n">
         <v>7.9</v>
       </c>
-      <c r="L30" s="11" t="n">
+      <c r="L30" s="19" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="M30" s="11" t="n">
         <v>81.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>1434.5</v>
+        <v>454.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="Q30" s="12" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="Q30" s="11" t="n">
         <v>114.2</v>
       </c>
-      <c r="R30" s="11" t="n">
-        <v>200.2</v>
+      <c r="R30" s="19" t="n">
+        <v>100.2</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>109.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>322.2</v>
+        <v>92.2</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>230.3</v>
-      </c>
-      <c r="V30" s="11" t="n">
-        <v>111.8</v>
-      </c>
-      <c r="W30" s="11" t="n">
-        <v>191.8</v>
+        <v>30.3</v>
+      </c>
+      <c r="V30" s="19" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="W30" s="19" t="n">
+        <v>91.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>998.1</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>416.1</v>
+        <v>16.1</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>20</v>
@@ -3060,72 +3071,72 @@
       <c r="C31" s="3" t="n">
         <v>357.7</v>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="D31" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="11" t="n">
         <v>16.3</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="11" t="n">
         <v>21.3</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>11</v>
+      <c r="G31" s="11" t="n">
+        <v>10</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="I31" s="13" t="n">
-        <v>96.09999999999999</v>
+      <c r="I31" s="3" t="n">
+        <v>2.6</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>28.9</v>
+        <v>8.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L31" s="11" t="n">
-        <v>372.1</v>
-      </c>
-      <c r="M31" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L31" s="19" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="M31" s="11" t="n">
         <v>16.2</v>
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>49</v>
+        <v>129</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q31" s="12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q31" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="R31" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="S31" s="3" t="n">
+      <c r="R31" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="S31" s="11" t="n">
         <v>21.9</v>
       </c>
-      <c r="T31" s="3" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="U31" s="3" t="n">
+      <c r="T31" s="11" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="U31" s="11" t="n">
         <v>6.1</v>
       </c>
-      <c r="V31" s="11" t="n">
+      <c r="V31" s="19" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="W31" s="19" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="X31" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="W31" s="11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>11.1</v>
-      </c>
       <c r="Y31" s="3" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3143,58 +3154,58 @@
       <c r="C32" s="3" t="n">
         <v>956.6</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="D32" s="11" t="n">
         <v>26.4</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="11" t="n">
         <v>17.1</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="11" t="n">
         <v>21.7</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>19.3</v>
+      <c r="G32" s="11" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1311.8</v>
+        <v>131.5</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
-      <c r="K32" s="15" t="inlineStr"/>
-      <c r="L32" s="9" t="n">
+      <c r="K32" s="13" t="inlineStr"/>
+      <c r="L32" s="17" t="n">
         <v>4.1</v>
       </c>
-      <c r="M32" s="3" t="n">
+      <c r="M32" s="11" t="n">
         <v>15.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>8.9</v>
+        <v>2.5</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="13" t="n">
+      <c r="Q32" s="11" t="n">
         <v>18.3</v>
       </c>
-      <c r="R32" s="12" t="n">
+      <c r="R32" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>1844151.8</v>
-      </c>
-      <c r="T32" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>0.7</v>
+      <c r="S32" s="11" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="T32" s="11" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="U32" s="11" t="n">
+        <v>0.4</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W32" s="13" t="n">
+      <c r="W32" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3204,7 +3215,7 @@
         <v>94</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>117.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3222,16 +3233,16 @@
       <c r="C33" s="3" t="n">
         <v>400.8</v>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D33" s="11" t="n">
         <v>27.3</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="11" t="n">
         <v>16.2</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G33" s="12" t="n">
+      <c r="F33" s="11" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G33" s="11" t="n">
         <v>11.1</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3241,7 +3252,7 @@
         <v>86.09999999999999</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>18.9</v>
+        <v>3.9</v>
       </c>
       <c r="K33" s="3" t="n">
         <v>5.8</v>
@@ -3249,11 +3260,11 @@
       <c r="L33" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="M33" s="3" t="n">
+      <c r="M33" s="11" t="n">
         <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>11.4</v>
+        <v>1.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>78</v>
@@ -3261,35 +3272,35 @@
       <c r="P33" s="3" t="n">
         <v>4.3</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="11" t="n">
         <v>21.4</v>
       </c>
-      <c r="R33" s="12" t="n">
+      <c r="R33" s="11" t="n">
         <v>18.6</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="T33" s="3" t="n">
-        <v>77.40000000000001</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="V33" s="13" t="n">
+      <c r="S33" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="T33" s="11" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="U33" s="11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V33" s="11" t="n">
         <v>19.6</v>
       </c>
-      <c r="W33" s="13" t="n">
-        <v>28</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="Y33" s="3" t="n">
-        <v>286.5</v>
-      </c>
-      <c r="Z33" s="3" t="n">
-        <v>13.2</v>
+      <c r="W33" s="11" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X33" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y33" s="11" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z33" s="11" t="n">
+        <v>3.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3307,34 +3318,34 @@
       <c r="C34" s="3" t="n">
         <v>350.2</v>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="D34" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="11" t="n">
         <v>20.9</v>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H34" s="13" t="n">
+      <c r="G34" s="11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H34" s="3" t="n">
         <v>15.6</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>12.6</v>
+        <v>2.1</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="M34" s="13" t="n">
+      <c r="M34" s="11" t="n">
         <v>16.6</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3344,25 +3355,25 @@
         <v>91</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="R34" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="S34" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="T34" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q34" s="11" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R34" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="S34" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="T34" s="11" t="n">
         <v>74.8</v>
       </c>
-      <c r="U34" s="3" t="n">
+      <c r="U34" s="11" t="n">
         <v>7.2</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>18.8</v>
@@ -3392,16 +3403,16 @@
       <c r="C35" s="3" t="n">
         <v>268.8</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D35" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="11" t="n">
         <v>16.6</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3416,50 +3427,50 @@
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L35" s="9" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="M35" s="3" t="n">
+      <c r="L35" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M35" s="11" t="n">
         <v>15.4</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="Q35" s="3" t="n">
+      <c r="Q35" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="R35" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S35" s="13" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="T35" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="U35" s="3" t="n">
+      <c r="R35" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="S35" s="11" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="T35" s="11" t="n">
+        <v>76</v>
+      </c>
+      <c r="U35" s="11" t="n">
         <v>6.7</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="11" t="n">
         <v>20.1</v>
       </c>
-      <c r="W35" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="X35" s="3" t="n">
+      <c r="W35" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X35" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="Y35" s="3" t="n">
+      <c r="Y35" s="11" t="n">
         <v>89.5</v>
       </c>
-      <c r="Z35" s="3" t="n">
-        <v>12.5</v>
+      <c r="Z35" s="11" t="n">
+        <v>2.5</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3475,21 +3486,21 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="D36" s="12" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="D36" s="11" t="n">
         <v>28.1</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F36" s="11" t="n">
         <v>22.1</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="G36" s="11" t="n">
         <v>12.1</v>
       </c>
-      <c r="H36" s="13" t="n">
+      <c r="H36" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I36" s="3" t="n">
@@ -3504,47 +3515,47 @@
       <c r="L36" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="M36" s="3" t="n">
+      <c r="M36" s="11" t="n">
         <v>14.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>13.6</v>
+        <v>13.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="11" t="n">
         <v>26.7</v>
       </c>
-      <c r="R36" s="12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="S36" s="3" t="n">
+      <c r="R36" s="11" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="S36" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="T36" s="3" t="n">
-        <v>168.2</v>
-      </c>
-      <c r="U36" s="3" t="n">
+      <c r="T36" s="11" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="U36" s="11" t="n">
         <v>13.9</v>
       </c>
-      <c r="V36" s="13" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="W36" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="X36" s="3" t="n">
+      <c r="V36" s="11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="W36" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="X36" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="Y36" s="3" t="n">
+      <c r="Y36" s="11" t="n">
         <v>95.2</v>
       </c>
-      <c r="Z36" s="3" t="n">
-        <v>41.8</v>
+      <c r="Z36" s="11" t="n">
+        <v>1.1</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3560,72 +3571,72 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>164.3</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>131.3</v>
-      </c>
-      <c r="E37" s="12" t="n">
+        <v>643.2</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>131.4</v>
+      </c>
+      <c r="E37" s="11" t="n">
         <v>82.90000000000001</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F37" s="11" t="n">
         <v>107.1</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="G37" s="11" t="n">
         <v>48.5</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>710.6</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>10.5</v>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="11" t="n">
+      <c r="K37" s="19" t="n">
         <v>1.6</v>
       </c>
-      <c r="L37" s="11" t="n">
-        <v>88.5</v>
+      <c r="L37" s="19" t="n">
+        <v>88.3</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>17.8</v>
+        <v>77</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>899.8</v>
+        <v>39.8</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="11" t="n">
-        <v>222.9</v>
-      </c>
-      <c r="R37" s="12" t="n">
-        <v>97.2</v>
+        <v>112.5</v>
+      </c>
+      <c r="R37" s="19" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>103.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>9383.4</v>
+        <v>385.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="V37" s="14" t="inlineStr"/>
-      <c r="W37" s="11" t="n">
-        <v>923.1</v>
+        <v>24.2</v>
+      </c>
+      <c r="V37" s="12" t="inlineStr"/>
+      <c r="W37" s="19" t="n">
+        <v>23.1</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>2.9</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>218.7</v>
+        <v>48.7</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3641,18 +3652,18 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>329.6</v>
-      </c>
-      <c r="D38" s="12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="D38" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="E38" s="12" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="G38" s="3" t="n">
+      <c r="E38" s="11" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G38" s="11" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3663,52 +3674,52 @@
         <v>3.3</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="L38" s="11" t="n">
-        <v>688.9</v>
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="19" t="n">
+        <v>17.7</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>16.2</v>
+        <v>1.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>16.1</v>
+        <v>10.1</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>4.2</v>
       </c>
       <c r="Q38" s="11" t="n">
-        <v>225.1</v>
-      </c>
-      <c r="R38" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R38" s="19" t="n">
         <v>19.4</v>
       </c>
-      <c r="S38" s="13" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="T38" s="3" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="V38" s="13" t="n">
-        <v>90.40000000000001</v>
-      </c>
-      <c r="W38" s="11" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="X38" s="13" t="n">
-        <v>0.5</v>
+      <c r="S38" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="T38" s="11" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="U38" s="11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>196.1</v>
+      </c>
+      <c r="W38" s="19" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>8971.799999999999</v>
+        <v>89.7</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>14.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3726,13 +3737,13 @@
       <c r="C39" s="3" t="n">
         <v>264.4</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D39" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="E39" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="11" t="n">
         <v>20.7</v>
       </c>
       <c r="G39" s="3" t="inlineStr"/>
@@ -3745,41 +3756,47 @@
       <c r="J39" s="3" t="n">
         <v>33.1</v>
       </c>
-      <c r="K39" s="3" t="n">
+      <c r="K39" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="M39" s="13" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O39" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R39" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="S39" s="3" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="T39" s="3" t="inlineStr"/>
-      <c r="U39" s="3" t="inlineStr"/>
+      <c r="M39" s="11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="N39" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="O39" s="11" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="P39" s="11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q39" s="11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="R39" s="11" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S39" s="11" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="T39" s="11" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="U39" s="11" t="n">
+        <v>4.1</v>
+      </c>
       <c r="V39" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="11" t="n">
         <v>16.9</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>88.90000000000001</v>
@@ -3801,16 +3818,16 @@
       <c r="C40" s="3" t="n">
         <v>286.4</v>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="D40" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="11" t="n">
         <v>15.8</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="H40" s="3" t="n">
@@ -3822,53 +3839,53 @@
       <c r="J40" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K40" s="3" t="n">
+      <c r="K40" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="13" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M40" s="3" t="n">
+      <c r="L40" s="11" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M40" s="11" t="n">
         <v>15.8</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O40" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="P40" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q40" s="3" t="n">
+      <c r="N40" s="11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="O40" s="11" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="P40" s="11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q40" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="R40" s="12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="S40" s="13" t="n">
+      <c r="R40" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S40" s="11" t="n">
         <v>20.7</v>
       </c>
-      <c r="T40" s="3" t="n">
+      <c r="T40" s="11" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="U40" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V40" s="3" t="n">
+      <c r="U40" s="11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="V40" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="W40" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X40" s="3" t="n">
+      <c r="W40" s="11" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="X40" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="Y40" s="3" t="n">
+      <c r="Y40" s="11" t="n">
         <v>89.7</v>
       </c>
-      <c r="Z40" s="3" t="n">
-        <v>22.4</v>
+      <c r="Z40" s="11" t="n">
+        <v>2.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3886,62 +3903,62 @@
       <c r="C41" s="3" t="n">
         <v>359</v>
       </c>
-      <c r="D41" s="9" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="E41" s="3" t="n">
+      <c r="D41" s="11" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="E41" s="11" t="n">
         <v>15.6</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G41" s="13" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H41" s="13" t="n">
+      <c r="F41" s="11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H41" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="I41" s="3" t="inlineStr"/>
       <c r="J41" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K41" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K41" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="9" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="O41" s="3" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q41" s="3" t="n">
+      <c r="M41" s="11" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="O41" s="11" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="P41" s="11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q41" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="R41" s="12" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S41" s="13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="T41" s="3" t="n">
+      <c r="R41" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S41" s="11" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="T41" s="11" t="n">
         <v>61.4</v>
       </c>
-      <c r="U41" s="13" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V41" s="9" t="n">
+      <c r="U41" s="11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V41" s="17" t="n">
         <v>4.4</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="11" t="n">
         <v>19.6</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -3951,7 +3968,7 @@
         <v>86.2</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>9.4</v>
+        <v>3.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3969,17 +3986,17 @@
       <c r="C42" s="3" t="n">
         <v>4856.1</v>
       </c>
-      <c r="D42" s="12" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="F42" s="12" t="n">
+      <c r="D42" s="11" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F42" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="G42" s="3" t="n">
-        <v>22.9</v>
+      <c r="G42" s="11" t="n">
+        <v>11.3</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>14.1</v>
@@ -3988,50 +4005,50 @@
       <c r="J42" s="3" t="n">
         <v>6.3</v>
       </c>
-      <c r="K42" s="3" t="n">
+      <c r="K42" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="11" t="n">
         <v>17.7</v>
       </c>
-      <c r="M42" s="3" t="n">
+      <c r="M42" s="11" t="n">
         <v>15.7</v>
       </c>
-      <c r="N42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>682</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="Q42" s="3" t="n">
+      <c r="N42" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O42" s="11" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="P42" s="11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q42" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="R42" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="T42" s="3" t="n">
+      <c r="R42" s="11" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="S42" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T42" s="11" t="n">
         <v>57.9</v>
       </c>
-      <c r="U42" s="3" t="n">
+      <c r="U42" s="11" t="n">
         <v>14.1</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>23.3</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="11" t="n">
         <v>19.4</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>28.5</v>
+        <v>70.5</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>7.1</v>
@@ -4050,71 +4067,71 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>742.6</v>
-      </c>
-      <c r="D43" s="12" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D43" s="11" t="n">
         <v>27.5</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="E43" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="F43" s="11" t="n">
         <v>22.6</v>
       </c>
-      <c r="G43" s="13" t="n">
-        <v>88.5</v>
+      <c r="G43" s="11" t="n">
+        <v>10.1</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K43" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K43" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="9" t="n">
-        <v>88</v>
-      </c>
-      <c r="M43" s="3" t="n">
+      <c r="L43" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="M43" s="11" t="n">
         <v>15.7</v>
       </c>
-      <c r="N43" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="R43" s="12" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="S43" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="U43" s="13" t="n">
-        <v>16.6</v>
+      <c r="N43" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="O43" s="11" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="P43" s="11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q43" s="11" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="R43" s="11" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="S43" s="11" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="T43" s="11" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="U43" s="11" t="n">
+        <v>12.1</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>22.2</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="X43" s="13" t="n">
-        <v>18.5</v>
+      <c r="X43" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>20.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>7.1</v>
@@ -4135,26 +4152,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="15" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="12" t="inlineStr"/>
+      <c r="D44" s="11" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="15" t="inlineStr"/>
-      <c r="M44" s="15" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr"/>
+      <c r="L44" s="11" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="15" t="inlineStr"/>
-      <c r="R44" s="12" t="inlineStr"/>
+      <c r="Q44" s="11" t="inlineStr"/>
+      <c r="R44" s="11" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="15" t="inlineStr"/>
-      <c r="W44" s="15" t="inlineStr"/>
+      <c r="V44" s="13" t="inlineStr"/>
+      <c r="W44" s="11" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4172,53 +4189,55 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1889</v>
+        <v>839</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>134.4</v>
       </c>
-      <c r="E45" s="14" t="inlineStr"/>
-      <c r="F45" s="12" t="n">
-        <v>107.1</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>59.5</v>
+      <c r="E45" s="11" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>52.5</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>69.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>117.4</v>
+        <v>17.4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>26.1</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="L45" s="11" t="n">
-        <v>90.90000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>53.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>71</v>
+        <v>21.6</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>1405.5</v>
+        <v>405.5</v>
       </c>
       <c r="P45" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="Q45" s="11" t="n">
-        <v>1268.4</v>
-      </c>
-      <c r="R45" s="12" t="n">
-        <v>101.8</v>
+        <v>125.4</v>
+      </c>
+      <c r="R45" s="19" t="n">
+        <v>101</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>104.8</v>
+        <v>104.2</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>330</v>
@@ -4226,20 +4245,20 @@
       <c r="U45" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="V45" s="11" t="n">
+      <c r="V45" s="19" t="n">
         <v>104.8</v>
       </c>
-      <c r="W45" s="11" t="n">
-        <v>98.5</v>
+      <c r="W45" s="19" t="n">
+        <v>93.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>118.2</v>
+        <v>1.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>108.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>11.4</v>
+        <v>21.1</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4255,76 +4274,76 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>362.9</v>
+        <v>367.9</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F46" s="12" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="F46" s="11" t="n">
         <v>21.6</v>
       </c>
-      <c r="G46" s="3" t="n">
-        <v>11.8</v>
+      <c r="G46" s="11" t="n">
+        <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>439.8</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>5.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>11.1</v>
+        <v>1.5</v>
       </c>
       <c r="L46" s="11" t="n">
         <v>18</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O46" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>9.9</v>
+        <v>15.9</v>
+      </c>
+      <c r="N46" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O46" s="11" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="P46" s="11" t="n">
+        <v>2.6</v>
       </c>
       <c r="Q46" s="11" t="n">
         <v>25.1</v>
       </c>
-      <c r="R46" s="12" t="n">
-        <v>20.4</v>
+      <c r="R46" s="19" t="n">
+        <v>18.9</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>11.1</v>
+        <v>1.5</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="V46" s="11" t="n">
+      <c r="V46" s="19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W46" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z46" s="3" t="n">
         <v>11.4</v>
-      </c>
-      <c r="W46" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Y46" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>11.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>32.6</v>
+        <v>431.6</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>28.2</v>
@@ -896,7 +896,7 @@
         <v>11.3</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>2.8</v>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>60.2</v>
+        <v>460.2</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>28.4</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>140.4</v>
+        <v>2140.4</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>142</v>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>28.1</v>
+        <v>428.1</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>28.4</v>
@@ -1352,7 +1352,7 @@
         <v>21.1</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1011.4</v>
+        <v>1214.1</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>76.8</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>21.2</v>
+        <v>121.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>834.8</v>
+        <v>334.8</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>28.3</v>
@@ -1768,16 +1768,16 @@
         <v>27.6</v>
       </c>
       <c r="R15" s="11" t="n">
-        <v>19</v>
+        <v>21.4</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>21.9</v>
+        <v>25.5</v>
       </c>
       <c r="T15" s="11" t="n">
-        <v>59.3</v>
+        <v>69</v>
       </c>
       <c r="U15" s="11" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="V15" s="11" t="n">
         <v>19.2</v>
@@ -1819,8 +1819,8 @@
       <c r="F16" s="11" t="n">
         <v>109.9</v>
       </c>
-      <c r="G16" s="3" t="n">
-        <v>28.4</v>
+      <c r="G16" s="11" t="n">
+        <v>48.4</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>73</v>
@@ -1841,10 +1841,10 @@
         <v>85.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>22.8</v>
+        <v>465.9</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6.9</v>
@@ -1936,13 +1936,13 @@
         <v>23.9</v>
       </c>
       <c r="R17" s="19" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>78.8</v>
+        <v>788.1</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
@@ -2009,7 +2009,7 @@
         <v>16.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>87.09999999999999</v>
@@ -2033,10 +2033,10 @@
         <v>11.7</v>
       </c>
       <c r="V18" s="17" t="n">
-        <v>224.214</v>
+        <v>226.214</v>
       </c>
       <c r="W18" s="17" t="n">
-        <v>28.12</v>
+        <v>14.214</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>20.9</v>
@@ -2061,7 +2061,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>19.4</v>
+        <v>319.4</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>27.4</v>
@@ -2094,7 +2094,7 @@
         <v>17.4</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>94</v>
@@ -2167,7 +2167,7 @@
         <v>19.4</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>23.1</v>
+        <v>3.1</v>
       </c>
       <c r="K20" s="11" t="n">
         <v>0</v>
@@ -2187,19 +2187,19 @@
       <c r="P20" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q20" s="11" t="n">
+      <c r="Q20" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="R20" s="11" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="S20" s="11" t="n">
+      <c r="R20" s="3" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="S20" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="T20" s="11" t="n">
-        <v>89</v>
-      </c>
-      <c r="U20" s="11" t="n">
+      <c r="T20" s="3" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="U20" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="V20" s="11" t="n">
@@ -2246,7 +2246,7 @@
         <v>11.1</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>20.2</v>
+        <v>14</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.5</v>
@@ -2264,7 +2264,7 @@
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
@@ -2347,7 +2347,7 @@
         <v>17.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2408,7 +2408,7 @@
         <v>85</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>111.3</v>
+        <v>111.2</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>52.6</v>
@@ -2432,7 +2432,7 @@
         <v>87.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>46.9</v>
@@ -2444,7 +2444,7 @@
         <v>115.8</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>93.7</v>
+        <v>393.7</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>33.2</v>
@@ -2456,7 +2456,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>103.4</v>
+        <v>1103.4</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>16.8</v>
@@ -2535,13 +2535,13 @@
         <v>6.6</v>
       </c>
       <c r="V24" s="19" t="n">
-        <v>28.1</v>
+        <v>22.1</v>
       </c>
       <c r="W24" s="19" t="n">
         <v>19.9</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>2.1</v>
+        <v>228.1</v>
       </c>
       <c r="Y24" s="3" t="n">
         <v>83.40000000000001</v>
@@ -2592,7 +2592,7 @@
         <v>18.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>2.5</v>
+        <v>21.5</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>9.4</v>
@@ -2615,14 +2615,14 @@
       <c r="U25" s="11" t="n">
         <v>4.7</v>
       </c>
-      <c r="V25" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W25" s="17" t="n">
-        <v>0.5</v>
+      <c r="V25" s="17" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>21.4</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>55.5</v>
+        <v>262.4</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>21.1</v>
@@ -2671,7 +2671,7 @@
         <v>2.6</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>17</v>
+        <v>28.2</v>
       </c>
       <c r="M26" s="11" t="n">
         <v>16.7</v>
@@ -2689,16 +2689,16 @@
         <v>23.7</v>
       </c>
       <c r="R26" s="11" t="n">
-        <v>21.6</v>
+        <v>20.8</v>
       </c>
       <c r="S26" s="11" t="n">
-        <v>25.8</v>
+        <v>24.6</v>
       </c>
       <c r="T26" s="11" t="n">
-        <v>88</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="U26" s="11" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="V26" s="11" t="n">
         <v>20.6</v>
@@ -2859,16 +2859,16 @@
         <v>20.8</v>
       </c>
       <c r="R28" s="11" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="S28" s="11" t="n">
-        <v>18.4</v>
+        <v>20.2</v>
       </c>
       <c r="T28" s="11" t="n">
-        <v>74.7</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="U28" s="11" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="V28" s="11" t="n">
         <v>19</v>
@@ -2932,7 +2932,7 @@
         <v>15.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.4</v>
+        <v>18.4</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>86.5</v>
@@ -3011,13 +3011,13 @@
         <v>7.9</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>85.90000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="M30" s="11" t="n">
         <v>81.2</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>454.5</v>
@@ -3035,13 +3035,13 @@
         <v>109.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>92.2</v>
+        <v>392.2</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="V30" s="19" t="n">
-        <v>101.8</v>
+        <v>161.8</v>
       </c>
       <c r="W30" s="19" t="n">
         <v>91.8</v>
@@ -3050,7 +3050,7 @@
         <v>99.90000000000001</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>16.1</v>
+        <v>116.1</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>20</v>
@@ -3072,7 +3072,7 @@
         <v>357.7</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>16.3</v>
@@ -3087,13 +3087,13 @@
         <v>14.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.6</v>
+        <v>26.1</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>8.9</v>
+        <v>3.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="L31" s="19" t="n">
         <v>172.1</v>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>1.8</v>
@@ -3127,10 +3127,10 @@
         <v>25.1</v>
       </c>
       <c r="W31" s="19" t="n">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>1.1</v>
+        <v>21.1</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>18.4</v>
@@ -3167,7 +3167,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>131.5</v>
+        <v>130.1</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>2.2</v>
@@ -3181,7 +3181,7 @@
         <v>15.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>72</v>
@@ -3205,7 +3205,7 @@
       <c r="V32" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="11" t="n">
         <v>16.9</v>
       </c>
       <c r="X32" s="3" t="n">
@@ -3340,21 +3340,21 @@
         <v>3.7</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="L34" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L34" s="11" t="n">
         <v>17.5</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="O34" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="N34" s="11" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="O34" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="P34" s="3" t="n">
+      <c r="P34" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="Q34" s="11" t="n">
@@ -3375,7 +3375,7 @@
       <c r="V34" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="11" t="n">
         <v>18.8</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3428,16 +3428,16 @@
         <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>18.6</v>
+        <v>17.6</v>
       </c>
       <c r="M35" s="11" t="n">
         <v>15.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.8</v>
+        <v>10.2</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>4</v>
@@ -3519,7 +3519,7 @@
         <v>14.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>13.1</v>
+        <v>19.1</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>77</v>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>643.2</v>
+        <v>1643.2</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>131.4</v>
@@ -3598,14 +3598,14 @@
       <c r="L37" s="19" t="n">
         <v>88.3</v>
       </c>
-      <c r="M37" s="11" t="n">
+      <c r="M37" s="19" t="n">
         <v>77</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>8</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>39.8</v>
+        <v>839.8</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>2</v>
@@ -3623,17 +3623,17 @@
         <v>385.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>24.2</v>
+        <v>34.2</v>
       </c>
       <c r="V37" s="12" t="inlineStr"/>
-      <c r="W37" s="19" t="n">
-        <v>23.1</v>
+      <c r="W37" s="11" t="n">
+        <v>90.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>2.9</v>
+        <v>29.4</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>48.7</v>
+        <v>148.7</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>1.1</v>
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>28.6</v>
+        <v>328.6</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>26.3</v>
@@ -3686,7 +3686,7 @@
         <v>1.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>4.2</v>
@@ -3707,19 +3707,19 @@
         <v>4.7</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>196.1</v>
-      </c>
-      <c r="W38" s="19" t="n">
-        <v>185.1</v>
+        <v>19.6</v>
+      </c>
+      <c r="W38" s="11" t="n">
+        <v>18.3</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>89.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3777,18 +3777,14 @@
       <c r="Q39" s="11" t="n">
         <v>23.7</v>
       </c>
-      <c r="R39" s="11" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="S39" s="11" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="T39" s="11" t="n">
-        <v>85.90000000000001</v>
-      </c>
-      <c r="U39" s="11" t="n">
-        <v>4.1</v>
-      </c>
+      <c r="R39" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr"/>
       <c r="V39" s="3" t="n">
         <v>18.1</v>
       </c>
@@ -4067,7 +4063,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>28.8</v>
+        <v>442.6</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>27.5</v>
@@ -4109,31 +4105,31 @@
       <c r="Q43" s="11" t="n">
         <v>27.1</v>
       </c>
-      <c r="R43" s="11" t="n">
+      <c r="R43" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="S43" s="11" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="T43" s="11" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="U43" s="11" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="V43" s="3" t="n">
+      <c r="S43" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="V43" s="11" t="n">
         <v>22.2</v>
       </c>
       <c r="W43" s="11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="X43" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="X43" s="11" t="n">
         <v>19.7</v>
       </c>
-      <c r="Y43" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z43" s="3" t="n">
+      <c r="Y43" s="11" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="Z43" s="11" t="n">
         <v>7.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -4166,7 +4162,7 @@
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
       <c r="Q44" s="11" t="inlineStr"/>
-      <c r="R44" s="11" t="inlineStr"/>
+      <c r="R44" s="13" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
@@ -4189,7 +4185,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>839</v>
+        <v>1839</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>134.4</v>
@@ -4222,7 +4218,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>21.6</v>
+        <v>11.6</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>405.5</v>
@@ -4252,13 +4248,13 @@
         <v>93.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.2</v>
+        <v>21.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4286,7 +4282,7 @@
         <v>21.6</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>439.8</v>
@@ -4298,7 +4294,7 @@
         <v>5.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="L46" s="11" t="n">
         <v>18</v>
@@ -4319,31 +4315,31 @@
         <v>25.1</v>
       </c>
       <c r="R46" s="19" t="n">
-        <v>18.9</v>
+        <v>20.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>1.5</v>
+        <v>11.4</v>
       </c>
       <c r="U46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="V46" s="19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W46" s="11" t="n">
-        <v>18.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="W46" s="19" t="n">
+        <v>18.3</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>11.4</v>
+        <v>0.1</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -173,16 +173,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -890,7 +887,7 @@
         <v>16.9</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>11.3</v>
@@ -1051,7 +1048,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>374.4</v>
+        <v>37.4</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>28.2</v>
@@ -1221,18 +1218,18 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2140.4</v>
+        <v>214</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>142</v>
       </c>
-      <c r="E9" s="11" t="n">
-        <v>83</v>
+      <c r="E9" s="17" t="n">
+        <v>82.8</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="G9" s="3" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="G9" s="11" t="n">
         <v>59.1</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1263,7 +1260,7 @@
       <c r="Q9" s="11" t="n">
         <v>127.1</v>
       </c>
-      <c r="R9" s="19" t="n">
+      <c r="R9" s="17" t="n">
         <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1282,7 +1279,7 @@
         <v>92.7</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>3.1</v>
+        <v>103.1</v>
       </c>
       <c r="Y9" s="3" t="n">
         <v>445.1</v>
@@ -1348,11 +1345,11 @@
       <c r="Q10" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="R10" s="19" t="n">
+      <c r="R10" s="17" t="n">
         <v>21.1</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1214.1</v>
+        <v>42</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>76.8</v>
@@ -1576,7 +1573,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>4</v>
@@ -1659,7 +1656,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="n">
-        <v>121.2</v>
+        <v>21.2</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0.7</v>
@@ -1831,7 +1828,7 @@
       <c r="J16" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K16" s="19" t="n">
+      <c r="K16" s="17" t="n">
         <v>32.1</v>
       </c>
       <c r="L16" s="11" t="n">
@@ -1841,7 +1838,7 @@
         <v>85.3</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>465.9</v>
@@ -1852,7 +1849,7 @@
       <c r="Q16" s="11" t="n">
         <v>119.3</v>
       </c>
-      <c r="R16" s="19" t="n">
+      <c r="R16" s="17" t="n">
         <v>104.3</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1867,7 +1864,7 @@
       <c r="V16" s="11" t="n">
         <v>101.9</v>
       </c>
-      <c r="W16" s="19" t="n">
+      <c r="W16" s="17" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1902,8 +1899,8 @@
       <c r="F17" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="G17" s="3" t="n">
-        <v>29.7</v>
+      <c r="G17" s="11" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>14.6</v>
@@ -1915,7 +1912,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="11" t="n">
         <v>17.8</v>
@@ -1935,14 +1932,14 @@
       <c r="Q17" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="R17" s="19" t="n">
+      <c r="R17" s="17" t="n">
         <v>20.5</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>788.1</v>
+        <v>78.8</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>7</v>
@@ -1950,7 +1947,7 @@
       <c r="V17" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="W17" s="19" t="n">
+      <c r="W17" s="17" t="n">
         <v>19.4</v>
       </c>
       <c r="X17" s="11" t="n">
@@ -2009,7 +2006,7 @@
         <v>16.8</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>87.09999999999999</v>
@@ -2032,13 +2029,13 @@
       <c r="U18" s="11" t="n">
         <v>11.7</v>
       </c>
-      <c r="V18" s="17" t="n">
-        <v>226.214</v>
-      </c>
-      <c r="W18" s="17" t="n">
-        <v>14.214</v>
-      </c>
-      <c r="X18" s="3" t="n">
+      <c r="V18" s="11" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="W18" s="11" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="X18" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="Y18" s="3" t="n">
@@ -2179,7 +2176,7 @@
         <v>17.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>97</v>
@@ -2187,19 +2184,19 @@
       <c r="P20" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q20" s="3" t="n">
+      <c r="Q20" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="S20" s="3" t="n">
+      <c r="R20" s="11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="S20" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="T20" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="U20" s="3" t="n">
+      <c r="T20" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="U20" s="11" t="n">
         <v>3.1</v>
       </c>
       <c r="V20" s="11" t="n">
@@ -2242,11 +2239,11 @@
       <c r="F21" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="G21" s="11" t="n">
-        <v>11.1</v>
+      <c r="G21" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>2.5</v>
@@ -2264,7 +2261,7 @@
         <v>17.4</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>94</v>
@@ -2347,7 +2344,7 @@
         <v>17.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>97</v>
@@ -2408,7 +2405,7 @@
         <v>85</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>111.2</v>
+        <v>111.3</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>52.6</v>
@@ -2425,14 +2422,14 @@
       <c r="K23" s="11" t="n">
         <v>6.6</v>
       </c>
-      <c r="L23" s="19" t="n">
+      <c r="L23" s="17" t="n">
         <v>0.9</v>
       </c>
       <c r="M23" s="11" t="n">
         <v>87.2</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>9.9</v>
+        <v>9.1</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>46.9</v>
@@ -2449,17 +2446,17 @@
       <c r="U23" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="V23" s="19" t="n">
+      <c r="V23" s="11" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="W23" s="11" t="n">
+        <v>95.3</v>
+      </c>
+      <c r="X23" s="3" t="n">
         <v>110.3</v>
       </c>
-      <c r="W23" s="19" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>1103.4</v>
-      </c>
       <c r="Y23" s="3" t="n">
-        <v>16.8</v>
+        <v>116.8</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>22.7</v>
@@ -2502,7 +2499,7 @@
         <v>3.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="11" t="n">
         <v>48.1</v>
@@ -2534,19 +2531,19 @@
       <c r="U24" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="V24" s="19" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W24" s="19" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>228.1</v>
-      </c>
-      <c r="Y24" s="3" t="n">
+      <c r="V24" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="W24" s="11" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="X24" s="11" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="Y24" s="11" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="Z24" s="3" t="n">
+      <c r="Z24" s="11" t="n">
         <v>4.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -2615,14 +2612,14 @@
       <c r="U25" s="11" t="n">
         <v>4.7</v>
       </c>
-      <c r="V25" s="17" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>21.4</v>
+      <c r="V25" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="W25" s="19" t="n">
+        <v>0.2</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>262.4</v>
+        <v>20</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>21.1</v>
@@ -2671,7 +2668,7 @@
         <v>2.6</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>28.2</v>
+        <v>17</v>
       </c>
       <c r="M26" s="11" t="n">
         <v>16.7</v>
@@ -2840,7 +2837,7 @@
       <c r="K28" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="L28" s="17" t="n">
+      <c r="L28" s="19" t="n">
         <v>46.1</v>
       </c>
       <c r="M28" s="11" t="n">
@@ -2850,7 +2847,7 @@
         <v>1.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>3.1</v>
@@ -2859,16 +2856,16 @@
         <v>20.8</v>
       </c>
       <c r="R28" s="11" t="n">
-        <v>17.7</v>
+        <v>16.2</v>
       </c>
       <c r="S28" s="11" t="n">
-        <v>20.2</v>
+        <v>18.4</v>
       </c>
       <c r="T28" s="11" t="n">
-        <v>82.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="U28" s="11" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="V28" s="11" t="n">
         <v>19</v>
@@ -2984,7 +2981,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1788.4</v>
+        <v>178.8</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>131.4</v>
@@ -3010,8 +3007,8 @@
       <c r="K30" s="11" t="n">
         <v>7.9</v>
       </c>
-      <c r="L30" s="19" t="n">
-        <v>28.8</v>
+      <c r="L30" s="17" t="n">
+        <v>85.90000000000001</v>
       </c>
       <c r="M30" s="11" t="n">
         <v>81.2</v>
@@ -3023,34 +3020,34 @@
         <v>454.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>28.9</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q30" s="11" t="n">
         <v>114.2</v>
       </c>
-      <c r="R30" s="19" t="n">
+      <c r="R30" s="17" t="n">
         <v>100.2</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>109.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>392.2</v>
+        <v>39.2</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="V30" s="19" t="n">
-        <v>161.8</v>
-      </c>
-      <c r="W30" s="19" t="n">
+      <c r="V30" s="17" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="W30" s="17" t="n">
         <v>91.8</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>116.1</v>
+        <v>20.8</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>20</v>
@@ -3072,7 +3069,7 @@
         <v>357.7</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="E31" s="11" t="n">
         <v>16.3</v>
@@ -3087,16 +3084,16 @@
         <v>14.1</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>26.1</v>
+        <v>2.6</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L31" s="19" t="n">
-        <v>172.1</v>
+        <v>0</v>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>17.2</v>
       </c>
       <c r="M31" s="11" t="n">
         <v>16.2</v>
@@ -3111,7 +3108,7 @@
       <c r="Q31" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="R31" s="19" t="n">
+      <c r="R31" s="17" t="n">
         <v>19</v>
       </c>
       <c r="S31" s="11" t="n">
@@ -3123,14 +3120,14 @@
       <c r="U31" s="11" t="n">
         <v>6.1</v>
       </c>
-      <c r="V31" s="19" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="W31" s="19" t="n">
+      <c r="V31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="17" t="n">
         <v>20.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="3" t="n">
         <v>18.4</v>
@@ -3167,21 +3164,21 @@
         <v>9.300000000000001</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>130.1</v>
+        <v>130</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="13" t="inlineStr"/>
-      <c r="L32" s="17" t="n">
+      <c r="L32" s="19" t="n">
         <v>4.1</v>
       </c>
       <c r="M32" s="11" t="n">
         <v>15.7</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>72</v>
@@ -3264,7 +3261,7 @@
         <v>14.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>78</v>
@@ -3342,19 +3339,19 @@
       <c r="K34" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L34" s="11" t="n">
+      <c r="L34" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="N34" s="11" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="O34" s="11" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O34" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P34" s="11" t="n">
+      <c r="P34" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="Q34" s="11" t="n">
@@ -3434,7 +3431,7 @@
         <v>15.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>10.2</v>
+        <v>1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>80</v>
@@ -3519,7 +3516,7 @@
         <v>14.6</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>19.1</v>
+        <v>1.4</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>77</v>
@@ -3542,20 +3539,20 @@
       <c r="U36" s="11" t="n">
         <v>13.9</v>
       </c>
-      <c r="V36" s="11" t="n">
-        <v>20.2</v>
+      <c r="V36" s="3" t="n">
+        <v>20.8</v>
       </c>
       <c r="W36" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="X36" s="11" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="X36" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="Y36" s="11" t="n">
+      <c r="Y36" s="3" t="n">
         <v>95.2</v>
       </c>
-      <c r="Z36" s="11" t="n">
-        <v>1.1</v>
+      <c r="Z36" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3592,13 +3589,13 @@
         <v>10.5</v>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="19" t="n">
+      <c r="K37" s="17" t="n">
         <v>1.6</v>
       </c>
-      <c r="L37" s="19" t="n">
+      <c r="L37" s="17" t="n">
         <v>88.3</v>
       </c>
-      <c r="M37" s="19" t="n">
+      <c r="M37" s="11" t="n">
         <v>77</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3613,7 +3610,7 @@
       <c r="Q37" s="11" t="n">
         <v>112.5</v>
       </c>
-      <c r="R37" s="19" t="n">
+      <c r="R37" s="17" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3627,16 +3624,16 @@
       </c>
       <c r="V37" s="12" t="inlineStr"/>
       <c r="W37" s="11" t="n">
-        <v>90.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>29.4</v>
+        <v>2.9</v>
       </c>
       <c r="Y37" s="3" t="n">
         <v>148.7</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3676,7 +3673,7 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="19" t="n">
+      <c r="L38" s="17" t="n">
         <v>17.7</v>
       </c>
       <c r="M38" s="11" t="n">
@@ -3686,7 +3683,7 @@
         <v>1.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>4.2</v>
@@ -3694,7 +3691,7 @@
       <c r="Q38" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="R38" s="19" t="n">
+      <c r="R38" s="17" t="n">
         <v>19.4</v>
       </c>
       <c r="S38" s="11" t="n">
@@ -3951,7 +3948,7 @@
       <c r="U41" s="11" t="n">
         <v>12.8</v>
       </c>
-      <c r="V41" s="17" t="n">
+      <c r="V41" s="19" t="n">
         <v>4.4</v>
       </c>
       <c r="W41" s="11" t="n">
@@ -4063,7 +4060,7 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>442.6</v>
+        <v>942.6</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>27.5</v>
@@ -4146,7 +4143,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="11" t="inlineStr"/>
       <c r="E44" s="11" t="inlineStr"/>
@@ -4185,7 +4182,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1839</v>
+        <v>189</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>134.4</v>
@@ -4218,7 +4215,7 @@
         <v>79.59999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>11.6</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>405.5</v>
@@ -4229,11 +4226,11 @@
       <c r="Q45" s="11" t="n">
         <v>125.4</v>
       </c>
-      <c r="R45" s="19" t="n">
-        <v>101</v>
+      <c r="R45" s="17" t="n">
+        <v>101.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>104.2</v>
+        <v>104.8</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>330</v>
@@ -4241,20 +4238,20 @@
       <c r="U45" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="V45" s="19" t="n">
+      <c r="V45" s="17" t="n">
         <v>104.8</v>
       </c>
-      <c r="W45" s="19" t="n">
+      <c r="W45" s="17" t="n">
         <v>93.5</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>21.2</v>
+        <v>28.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>108.7</v>
+        <v>1088.7</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>21.4</v>
+        <v>1.1</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4282,7 +4279,7 @@
         <v>21.6</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>439.8</v>
@@ -4294,7 +4291,7 @@
         <v>5.2</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="11" t="n">
         <v>18</v>
@@ -4314,32 +4311,32 @@
       <c r="Q46" s="11" t="n">
         <v>25.1</v>
       </c>
-      <c r="R46" s="19" t="n">
+      <c r="R46" s="17" t="n">
         <v>20.8</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>11.4</v>
+        <v>1</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V46" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="17" t="n">
         <v>0.4</v>
       </c>
-      <c r="W46" s="19" t="n">
+      <c r="W46" s="17" t="n">
         <v>18.3</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
@@ -173,7 +173,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -826,13 +826,13 @@
         <v>16.8</v>
       </c>
       <c r="N4" s="11" t="n">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="O4" s="11" t="n">
-        <v>93.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="P4" s="11" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" s="11" t="n">
         <v>23.7</v>
@@ -841,13 +841,13 @@
         <v>21.8</v>
       </c>
       <c r="S4" s="11" t="n">
-        <v>26.1</v>
+        <v>24.8</v>
       </c>
       <c r="T4" s="11" t="n">
-        <v>89.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="U4" s="11" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="V4" s="11" t="n">
         <v>20.3</v>
@@ -856,13 +856,13 @@
         <v>18.7</v>
       </c>
       <c r="X4" s="11" t="n">
-        <v>21.6</v>
+        <v>20.5</v>
       </c>
       <c r="Y4" s="11" t="n">
-        <v>90.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Z4" s="11" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -911,19 +911,19 @@
         <v>17.6</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>95.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="P5" s="11" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="Q5" s="11" t="n">
         <v>24.8</v>
       </c>
       <c r="R5" s="11" t="n">
-        <v>20</v>
+        <v>21.3</v>
       </c>
       <c r="S5" s="11" t="n">
         <v>23.3</v>
@@ -941,13 +941,13 @@
         <v>17.2</v>
       </c>
       <c r="X5" s="11" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="Y5" s="11" t="n">
-        <v>95.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Z5" s="11" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -996,19 +996,19 @@
         <v>16.4</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>18.6</v>
+        <v>18.1</v>
       </c>
       <c r="O6" s="11" t="n">
-        <v>95</v>
+        <v>92.3</v>
       </c>
       <c r="P6" s="11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" s="11" t="n">
         <v>26.8</v>
       </c>
       <c r="R6" s="11" t="n">
-        <v>20.6</v>
+        <v>22.3</v>
       </c>
       <c r="S6" s="11" t="n">
         <v>24.3</v>
@@ -1026,13 +1026,13 @@
         <v>19.2</v>
       </c>
       <c r="X6" s="11" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="Y6" s="11" t="n">
-        <v>94</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Z6" s="11" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1081,19 +1081,19 @@
         <v>17.9</v>
       </c>
       <c r="N7" s="11" t="n">
-        <v>20.5</v>
+        <v>19.7</v>
       </c>
       <c r="O7" s="11" t="n">
-        <v>93.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="P7" s="11" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" s="11" t="n">
         <v>27.3</v>
       </c>
       <c r="R7" s="11" t="n">
-        <v>21</v>
+        <v>22.7</v>
       </c>
       <c r="S7" s="11" t="n">
         <v>24.9</v>
@@ -1111,13 +1111,13 @@
         <v>19.6</v>
       </c>
       <c r="X7" s="11" t="n">
-        <v>22.8</v>
+        <v>22</v>
       </c>
       <c r="Y7" s="11" t="n">
-        <v>92.8</v>
+        <v>89.5</v>
       </c>
       <c r="Z7" s="11" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1166,19 +1166,19 @@
         <v>15.8</v>
       </c>
       <c r="N8" s="11" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="O8" s="11" t="n">
-        <v>92.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="P8" s="11" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" s="11" t="n">
         <v>24.5</v>
       </c>
       <c r="R8" s="11" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="S8" s="11" t="n">
         <v>26.8</v>
@@ -1196,13 +1196,13 @@
         <v>18</v>
       </c>
       <c r="X8" s="11" t="n">
-        <v>20.6</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" s="11" t="n">
-        <v>90.5</v>
+        <v>85.7</v>
       </c>
       <c r="Z8" s="11" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       <c r="D9" s="11" t="n">
         <v>142</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="18" t="n">
         <v>82.8</v>
       </c>
       <c r="F9" s="11" t="n">
@@ -1260,7 +1260,7 @@
       <c r="Q9" s="11" t="n">
         <v>127.1</v>
       </c>
-      <c r="R9" s="17" t="n">
+      <c r="R9" s="11" t="n">
         <v>110.9</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1334,19 +1334,19 @@
         <v>16.9</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>19.2</v>
+        <v>18.6</v>
       </c>
       <c r="O10" s="11" t="n">
-        <v>93.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="P10" s="11" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" s="11" t="n">
         <v>25.4</v>
       </c>
-      <c r="R10" s="17" t="n">
-        <v>21.1</v>
+      <c r="R10" s="11" t="n">
+        <v>22.2</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>42</v>
@@ -1364,13 +1364,13 @@
         <v>18.5</v>
       </c>
       <c r="X10" s="11" t="n">
-        <v>21.3</v>
+        <v>20.4</v>
       </c>
       <c r="Y10" s="11" t="n">
-        <v>92.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="Z10" s="11" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1417,19 +1417,19 @@
         <v>17</v>
       </c>
       <c r="N11" s="11" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="O11" s="11" t="n">
-        <v>98.7</v>
+        <v>98</v>
       </c>
       <c r="P11" s="11" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="Q11" s="11" t="n">
         <v>26</v>
       </c>
       <c r="R11" s="11" t="n">
-        <v>19.7</v>
+        <v>21.5</v>
       </c>
       <c r="S11" s="11" t="n">
         <v>23</v>
@@ -1444,7 +1444,7 @@
         <v>21.7</v>
       </c>
       <c r="W11" s="11" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="X11" s="11" t="n">
         <v>22</v>
@@ -1502,13 +1502,13 @@
         <v>17.6</v>
       </c>
       <c r="N12" s="11" t="n">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="O12" s="11" t="n">
-        <v>95.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="P12" s="11" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="Q12" s="11" t="n">
         <v>20.3</v>
@@ -1517,19 +1517,19 @@
         <v>19.5</v>
       </c>
       <c r="S12" s="11" t="n">
-        <v>22.7</v>
+        <v>22.1</v>
       </c>
       <c r="T12" s="11" t="n">
-        <v>95.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U12" s="11" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="V12" s="11" t="n">
         <v>21.5</v>
       </c>
       <c r="W12" s="11" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="X12" s="11" t="n">
         <v>22.9</v>
@@ -1585,13 +1585,13 @@
         <v>16.9</v>
       </c>
       <c r="N13" s="11" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="O13" s="11" t="n">
-        <v>95.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P13" s="11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q13" s="11" t="n">
         <v>24.4</v>
@@ -1600,13 +1600,13 @@
         <v>21.4</v>
       </c>
       <c r="S13" s="11" t="n">
-        <v>25.5</v>
+        <v>23.4</v>
       </c>
       <c r="T13" s="11" t="n">
-        <v>83.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="U13" s="11" t="n">
-        <v>5.1</v>
+        <v>7.1</v>
       </c>
       <c r="V13" s="11" t="n">
         <v>19.8</v>
@@ -1615,13 +1615,13 @@
         <v>19.4</v>
       </c>
       <c r="X13" s="11" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="Y13" s="11" t="n">
-        <v>97.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Z13" s="11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1668,19 +1668,19 @@
         <v>17.2</v>
       </c>
       <c r="N14" s="11" t="n">
-        <v>19.6</v>
+        <v>18.9</v>
       </c>
       <c r="O14" s="11" t="n">
-        <v>93.3</v>
+        <v>89.7</v>
       </c>
       <c r="P14" s="11" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" s="11" t="n">
         <v>21</v>
       </c>
       <c r="R14" s="11" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="S14" s="11" t="n">
         <v>23.8</v>
@@ -1753,13 +1753,13 @@
         <v>16.6</v>
       </c>
       <c r="N15" s="11" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="O15" s="11" t="n">
-        <v>96.3</v>
+        <v>94.2</v>
       </c>
       <c r="P15" s="11" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="Q15" s="11" t="n">
         <v>27.6</v>
@@ -1768,19 +1768,19 @@
         <v>21.4</v>
       </c>
       <c r="S15" s="11" t="n">
-        <v>25.5</v>
+        <v>21.2</v>
       </c>
       <c r="T15" s="11" t="n">
-        <v>69</v>
+        <v>57.5</v>
       </c>
       <c r="U15" s="11" t="n">
-        <v>11.5</v>
+        <v>15.7</v>
       </c>
       <c r="V15" s="11" t="n">
         <v>19.2</v>
       </c>
       <c r="W15" s="11" t="n">
-        <v>17.7</v>
+        <v>18.1</v>
       </c>
       <c r="X15" s="11" t="n">
         <v>20.3</v>
@@ -1828,7 +1828,7 @@
       <c r="J16" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K16" s="17" t="n">
+      <c r="K16" s="18" t="n">
         <v>32.1</v>
       </c>
       <c r="L16" s="11" t="n">
@@ -1849,7 +1849,7 @@
       <c r="Q16" s="11" t="n">
         <v>119.3</v>
       </c>
-      <c r="R16" s="17" t="n">
+      <c r="R16" s="11" t="n">
         <v>104.3</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1864,7 +1864,7 @@
       <c r="V16" s="11" t="n">
         <v>101.9</v>
       </c>
-      <c r="W16" s="17" t="n">
+      <c r="W16" s="11" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1921,19 +1921,19 @@
         <v>17.1</v>
       </c>
       <c r="N17" s="11" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="O17" s="11" t="n">
-        <v>95.7</v>
+        <v>93.3</v>
       </c>
       <c r="P17" s="11" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" s="11" t="n">
         <v>23.9</v>
       </c>
-      <c r="R17" s="17" t="n">
-        <v>20.5</v>
+      <c r="R17" s="11" t="n">
+        <v>20.9</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>22.9</v>
@@ -1947,17 +1947,17 @@
       <c r="V17" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="W17" s="17" t="n">
+      <c r="W17" s="11" t="n">
         <v>19.4</v>
       </c>
       <c r="X17" s="11" t="n">
-        <v>22.5</v>
+        <v>21.8</v>
       </c>
       <c r="Y17" s="11" t="n">
-        <v>94</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="Z17" s="11" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -2017,8 +2017,8 @@
       <c r="Q18" s="11" t="n">
         <v>26.7</v>
       </c>
-      <c r="R18" s="11" t="n">
-        <v>20</v>
+      <c r="R18" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="S18" s="11" t="n">
         <v>23.3</v>
@@ -2035,7 +2035,7 @@
       <c r="W18" s="11" t="n">
         <v>18.2</v>
       </c>
-      <c r="X18" s="11" t="n">
+      <c r="X18" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="Y18" s="3" t="n">
@@ -2084,26 +2084,26 @@
       <c r="K19" s="11" t="n">
         <v>2.3</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="11" t="n">
         <v>18</v>
       </c>
       <c r="M19" s="11" t="n">
         <v>17.4</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="N19" s="11" t="n">
         <v>19.5</v>
       </c>
-      <c r="O19" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="P19" s="3" t="n">
+      <c r="O19" s="11" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="P19" s="11" t="n">
         <v>1.2</v>
       </c>
       <c r="Q19" s="11" t="n">
         <v>23.8</v>
       </c>
-      <c r="R19" s="11" t="n">
-        <v>18.7</v>
+      <c r="R19" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="S19" s="11" t="n">
         <v>21.6</v>
@@ -2118,7 +2118,7 @@
         <v>23.4</v>
       </c>
       <c r="W19" s="11" t="n">
-        <v>18.4</v>
+        <v>19.9</v>
       </c>
       <c r="X19" s="11" t="n">
         <v>21.2</v>
@@ -2188,13 +2188,13 @@
         <v>22.8</v>
       </c>
       <c r="R20" s="11" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="S20" s="11" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="T20" s="11" t="n">
-        <v>89</v>
+        <v>88.8</v>
       </c>
       <c r="U20" s="11" t="n">
         <v>3.1</v>
@@ -2203,7 +2203,7 @@
         <v>20.9</v>
       </c>
       <c r="W20" s="11" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="X20" s="11" t="n">
         <v>23.2</v>
@@ -2337,26 +2337,26 @@
       <c r="K22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="11" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="11" t="n">
         <v>17.7</v>
       </c>
-      <c r="N22" s="3" t="n">
+      <c r="N22" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="O22" s="3" t="n">
+      <c r="O22" s="11" t="n">
         <v>97</v>
       </c>
-      <c r="P22" s="3" t="n">
+      <c r="P22" s="11" t="n">
         <v>0.7</v>
       </c>
       <c r="Q22" s="11" t="n">
         <v>25.1</v>
       </c>
-      <c r="R22" s="11" t="n">
-        <v>20.2</v>
+      <c r="R22" s="3" t="n">
+        <v>21.5</v>
       </c>
       <c r="S22" s="11" t="n">
         <v>23.6</v>
@@ -2371,7 +2371,7 @@
         <v>23.1</v>
       </c>
       <c r="W22" s="11" t="n">
-        <v>17.2</v>
+        <v>19</v>
       </c>
       <c r="X22" s="11" t="n">
         <v>19.6</v>
@@ -2422,7 +2422,7 @@
       <c r="K23" s="11" t="n">
         <v>6.6</v>
       </c>
-      <c r="L23" s="17" t="n">
+      <c r="L23" s="18" t="n">
         <v>0.9</v>
       </c>
       <c r="M23" s="11" t="n">
@@ -2450,7 +2450,7 @@
         <v>112.5</v>
       </c>
       <c r="W23" s="11" t="n">
-        <v>95.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>110.3</v>
@@ -2501,7 +2501,7 @@
       <c r="K24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="11" t="n">
+      <c r="L24" s="18" t="n">
         <v>48.1</v>
       </c>
       <c r="M24" s="11" t="n">
@@ -2535,7 +2535,7 @@
         <v>22.5</v>
       </c>
       <c r="W24" s="11" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="X24" s="11" t="n">
         <v>22.8</v>
@@ -2601,7 +2601,7 @@
         <v>22.2</v>
       </c>
       <c r="R25" s="11" t="n">
-        <v>19.1</v>
+        <v>20</v>
       </c>
       <c r="S25" s="11" t="n">
         <v>22.1</v>
@@ -2686,7 +2686,7 @@
         <v>23.7</v>
       </c>
       <c r="R26" s="11" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="S26" s="11" t="n">
         <v>24.6</v>
@@ -2701,13 +2701,13 @@
         <v>20.6</v>
       </c>
       <c r="W26" s="11" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="X26" s="11" t="n">
         <v>22.4</v>
       </c>
       <c r="Y26" s="11" t="n">
-        <v>92</v>
+        <v>92.2</v>
       </c>
       <c r="Z26" s="11" t="n">
         <v>1.9</v>
@@ -2771,7 +2771,7 @@
         <v>25.5</v>
       </c>
       <c r="R27" s="11" t="n">
-        <v>19.5</v>
+        <v>21.2</v>
       </c>
       <c r="S27" s="11" t="n">
         <v>22.7</v>
@@ -2856,7 +2856,7 @@
         <v>20.8</v>
       </c>
       <c r="R28" s="11" t="n">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="S28" s="11" t="n">
         <v>18.4</v>
@@ -2871,13 +2871,13 @@
         <v>19</v>
       </c>
       <c r="W28" s="11" t="n">
-        <v>15.1</v>
+        <v>16.4</v>
       </c>
       <c r="X28" s="11" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="Y28" s="11" t="n">
-        <v>77.5</v>
+        <v>77.2</v>
       </c>
       <c r="Z28" s="11" t="n">
         <v>5</v>
@@ -2944,25 +2944,25 @@
         <v>19.7</v>
       </c>
       <c r="S29" s="11" t="n">
-        <v>22.9</v>
+        <v>21.4</v>
       </c>
       <c r="T29" s="11" t="n">
-        <v>86.8</v>
+        <v>80.8</v>
       </c>
       <c r="U29" s="11" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="V29" s="11" t="n">
         <v>20.2</v>
       </c>
       <c r="W29" s="11" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="X29" s="11" t="n">
         <v>20.9</v>
       </c>
       <c r="Y29" s="11" t="n">
-        <v>88</v>
+        <v>88.2</v>
       </c>
       <c r="Z29" s="11" t="n">
         <v>2.8</v>
@@ -3007,7 +3007,7 @@
       <c r="K30" s="11" t="n">
         <v>7.9</v>
       </c>
-      <c r="L30" s="17" t="n">
+      <c r="L30" s="18" t="n">
         <v>85.90000000000001</v>
       </c>
       <c r="M30" s="11" t="n">
@@ -3025,7 +3025,7 @@
       <c r="Q30" s="11" t="n">
         <v>114.2</v>
       </c>
-      <c r="R30" s="17" t="n">
+      <c r="R30" s="11" t="n">
         <v>100.2</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3037,10 +3037,10 @@
       <c r="U30" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="V30" s="17" t="n">
+      <c r="V30" s="18" t="n">
         <v>101.8</v>
       </c>
-      <c r="W30" s="17" t="n">
+      <c r="W30" s="18" t="n">
         <v>91.8</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3092,7 +3092,7 @@
       <c r="K31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="17" t="n">
+      <c r="L31" s="18" t="n">
         <v>17.2</v>
       </c>
       <c r="M31" s="11" t="n">
@@ -3108,8 +3108,8 @@
       <c r="Q31" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="R31" s="17" t="n">
-        <v>19</v>
+      <c r="R31" s="11" t="n">
+        <v>20</v>
       </c>
       <c r="S31" s="11" t="n">
         <v>21.9</v>
@@ -3120,10 +3120,10 @@
       <c r="U31" s="11" t="n">
         <v>6.1</v>
       </c>
-      <c r="V31" s="17" t="n">
+      <c r="V31" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="17" t="n">
+      <c r="W31" s="18" t="n">
         <v>20.4</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3191,13 +3191,13 @@
         <v>18</v>
       </c>
       <c r="S32" s="11" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="T32" s="11" t="n">
-        <v>98.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="U32" s="11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="V32" s="3" t="n">
         <v>20.4</v>
@@ -3276,19 +3276,19 @@
         <v>18.6</v>
       </c>
       <c r="S33" s="11" t="n">
-        <v>21.4</v>
+        <v>19.5</v>
       </c>
       <c r="T33" s="11" t="n">
-        <v>84.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="U33" s="11" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="V33" s="11" t="n">
         <v>19.6</v>
       </c>
       <c r="W33" s="11" t="n">
-        <v>17.3</v>
+        <v>18</v>
       </c>
       <c r="X33" s="11" t="n">
         <v>19.7</v>
@@ -3358,7 +3358,7 @@
         <v>23.3</v>
       </c>
       <c r="R34" s="11" t="n">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="S34" s="11" t="n">
         <v>21.4</v>
@@ -3443,7 +3443,7 @@
         <v>22.8</v>
       </c>
       <c r="R35" s="11" t="n">
-        <v>18.4</v>
+        <v>19.7</v>
       </c>
       <c r="S35" s="11" t="n">
         <v>21.1</v>
@@ -3458,7 +3458,7 @@
         <v>20.1</v>
       </c>
       <c r="W35" s="11" t="n">
-        <v>18.4</v>
+        <v>18.9</v>
       </c>
       <c r="X35" s="11" t="n">
         <v>21.1</v>
@@ -3528,7 +3528,7 @@
         <v>26.7</v>
       </c>
       <c r="R36" s="11" t="n">
-        <v>18.4</v>
+        <v>20.8</v>
       </c>
       <c r="S36" s="11" t="n">
         <v>21.1</v>
@@ -3589,10 +3589,10 @@
         <v>10.5</v>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="17" t="n">
+      <c r="K37" s="18" t="n">
         <v>1.6</v>
       </c>
-      <c r="L37" s="17" t="n">
+      <c r="L37" s="18" t="n">
         <v>88.3</v>
       </c>
       <c r="M37" s="11" t="n">
@@ -3610,7 +3610,7 @@
       <c r="Q37" s="11" t="n">
         <v>112.5</v>
       </c>
-      <c r="R37" s="17" t="n">
+      <c r="R37" s="11" t="n">
         <v>97.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="V37" s="12" t="inlineStr"/>
       <c r="W37" s="11" t="n">
-        <v>90.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>2.9</v>
@@ -3673,7 +3673,7 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="17" t="n">
+      <c r="L38" s="18" t="n">
         <v>17.7</v>
       </c>
       <c r="M38" s="11" t="n">
@@ -3691,17 +3691,17 @@
       <c r="Q38" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="R38" s="17" t="n">
+      <c r="R38" s="11" t="n">
         <v>19.4</v>
       </c>
       <c r="S38" s="11" t="n">
-        <v>22.5</v>
+        <v>20.4</v>
       </c>
       <c r="T38" s="11" t="n">
-        <v>82.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="U38" s="11" t="n">
-        <v>4.7</v>
+        <v>6.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>19.6</v>
@@ -3763,13 +3763,13 @@
         <v>17.1</v>
       </c>
       <c r="N39" s="11" t="n">
-        <v>19.5</v>
+        <v>18.3</v>
       </c>
       <c r="O39" s="11" t="n">
-        <v>89.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="P39" s="11" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q39" s="11" t="n">
         <v>23.7</v>
@@ -3788,7 +3788,7 @@
       <c r="W39" s="11" t="n">
         <v>16.9</v>
       </c>
-      <c r="X39" s="3" t="n">
+      <c r="X39" s="11" t="n">
         <v>18.5</v>
       </c>
       <c r="Y39" s="3" t="n">
@@ -3842,19 +3842,19 @@
         <v>15.8</v>
       </c>
       <c r="N40" s="11" t="n">
-        <v>17.9</v>
+        <v>16.6</v>
       </c>
       <c r="O40" s="11" t="n">
-        <v>88.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="P40" s="11" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" s="11" t="n">
         <v>22.8</v>
       </c>
-      <c r="R40" s="11" t="n">
-        <v>18.1</v>
+      <c r="R40" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="S40" s="11" t="n">
         <v>20.7</v>
@@ -3869,7 +3869,7 @@
         <v>20</v>
       </c>
       <c r="W40" s="11" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="X40" s="11" t="n">
         <v>21</v>
@@ -3925,19 +3925,19 @@
         <v>15.3</v>
       </c>
       <c r="N41" s="11" t="n">
-        <v>17.4</v>
+        <v>15.5</v>
       </c>
       <c r="O41" s="11" t="n">
-        <v>84.2</v>
+        <v>75.3</v>
       </c>
       <c r="P41" s="11" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="Q41" s="11" t="n">
         <v>25.8</v>
       </c>
-      <c r="R41" s="11" t="n">
-        <v>17.8</v>
+      <c r="R41" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="S41" s="11" t="n">
         <v>20.4</v>
@@ -4008,19 +4008,19 @@
         <v>15.7</v>
       </c>
       <c r="N42" s="11" t="n">
-        <v>17.8</v>
+        <v>16.5</v>
       </c>
       <c r="O42" s="11" t="n">
-        <v>88.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="P42" s="11" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="Q42" s="11" t="n">
         <v>26</v>
       </c>
-      <c r="R42" s="11" t="n">
-        <v>17.1</v>
+      <c r="R42" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="S42" s="11" t="n">
         <v>19.5</v>
@@ -4091,34 +4091,34 @@
         <v>15.7</v>
       </c>
       <c r="N43" s="11" t="n">
-        <v>17.8</v>
+        <v>16.3</v>
       </c>
       <c r="O43" s="11" t="n">
-        <v>86.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="P43" s="11" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q43" s="11" t="n">
         <v>27.1</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="11" t="n">
         <v>20.3</v>
       </c>
-      <c r="S43" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="T43" s="3" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="U43" s="3" t="n">
+      <c r="S43" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="T43" s="11" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="U43" s="11" t="n">
         <v>16.6</v>
       </c>
       <c r="V43" s="11" t="n">
         <v>22.2</v>
       </c>
       <c r="W43" s="11" t="n">
-        <v>17.3</v>
+        <v>18.8</v>
       </c>
       <c r="X43" s="11" t="n">
         <v>19.7</v>
@@ -4226,7 +4226,7 @@
       <c r="Q45" s="11" t="n">
         <v>125.4</v>
       </c>
-      <c r="R45" s="17" t="n">
+      <c r="R45" s="18" t="n">
         <v>101.8</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4238,10 +4238,10 @@
       <c r="U45" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="V45" s="17" t="n">
+      <c r="V45" s="18" t="n">
         <v>104.8</v>
       </c>
-      <c r="W45" s="17" t="n">
+      <c r="W45" s="11" t="n">
         <v>93.5</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4300,18 +4300,18 @@
         <v>15.9</v>
       </c>
       <c r="N46" s="11" t="n">
-        <v>18.1</v>
+        <v>16.6</v>
       </c>
       <c r="O46" s="11" t="n">
-        <v>87.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="P46" s="11" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="Q46" s="11" t="n">
         <v>25.1</v>
       </c>
-      <c r="R46" s="17" t="n">
+      <c r="R46" s="18" t="n">
         <v>20.8</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4323,11 +4323,11 @@
       <c r="U46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="17" t="n">
+      <c r="V46" s="18" t="n">
         <v>0.4</v>
       </c>
-      <c r="W46" s="17" t="n">
-        <v>18.3</v>
+      <c r="W46" s="11" t="n">
+        <v>18.7</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>0</v>

--- a/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
+++ b/results/02_post_QA_QC_transcribed_hydroclimate_data/905/905_197311_SF.JPG_post_QA_QC.xlsx
@@ -1206,7 +1206,7 @@
       <c r="J9" s="3" t="n">
         <v>28.8</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="11" t="n">
         <v>16.6</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1542,7 +1542,7 @@
       <c r="J13" s="8" t="n">
         <v>39.4</v>
       </c>
-      <c r="K13" s="3" t="n"/>
+      <c r="K13" s="10" t="n"/>
       <c r="L13" s="3" t="n">
         <v>17.2</v>
       </c>
@@ -1710,7 +1710,7 @@
       <c r="J15" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="K15" s="3" t="n"/>
+      <c r="K15" s="10" t="n"/>
       <c r="L15" s="3" t="n">
         <v>18.3</v>
       </c>
@@ -1791,7 +1791,7 @@
       <c r="J16" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2385,7 +2385,7 @@
       <c r="J23" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="11" t="n">
         <v>616.3</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -2980,7 +2980,7 @@
       <c r="J30" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="11" t="n">
         <v>7.9</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3575,7 +3575,7 @@
       <c r="J37" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="11" t="n">
         <v>736.1</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4223,7 +4223,7 @@
       <c r="J45" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="11" t="n">
         <v>5.1</v>
       </c>
       <c r="L45" s="3" t="n">
